--- a/OECD_salaries/matrix_L_Lc.xlsx
+++ b/OECD_salaries/matrix_L_Lc.xlsx
@@ -1102,142 +1102,142 @@
         </is>
       </c>
       <c r="AW4" t="n">
-        <v>1.164862836025811</v>
+        <v>1.179675089853306</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.05984906868477</v>
+        <v>0.07366907381395621</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002711394709355906</v>
+        <v>0.02076705212931099</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00289010681151487</v>
+        <v>0.01969204373811191</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.001847361584978919</v>
+        <v>0.02918060778897433</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.2670908835813617</v>
+        <v>0.2869059556609621</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.007446839710897581</v>
+        <v>0.03148582835041019</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.3699636678780201</v>
+        <v>0.3931183056667535</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.06781954022753407</v>
+        <v>0.09033604825895956</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.002316975724965778</v>
+        <v>0.01334097861999337</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.021474821956798</v>
+        <v>0.03695549682872482</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.005507293884148159</v>
+        <v>0.02642445762395945</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0156615299690185</v>
+        <v>0.03711695612913241</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.004431812578888815</v>
+        <v>0.02698543191318313</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002315579794745839</v>
+        <v>0.01625979782151188</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.002995335866687903</v>
+        <v>0.02763397706965724</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002360302754970228</v>
+        <v>0.02451928937506269</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.002873361618867098</v>
+        <v>0.02326903141296523</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002981347597232783</v>
+        <v>0.02646593469889503</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001986150877371958</v>
+        <v>0.01579428604948149</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.002173791461287496</v>
+        <v>0.02224517501263712</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.01380520693289433</v>
+        <v>0.03285434946808188</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003479614405569501</v>
+        <v>0.02093216655869854</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.003780402367391536</v>
+        <v>0.02138585889968942</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.01889562428907745</v>
+        <v>0.04362596176285191</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003671250317656739</v>
+        <v>0.03346597035298921</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.003219261085106988</v>
+        <v>0.02616524671738951</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.003071414537796273</v>
+        <v>0.02363397496529468</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003508874826852022</v>
+        <v>0.02467955548946803</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004123740517035611</v>
+        <v>0.028002886408546</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.002880305536917252</v>
+        <v>0.03297011947623511</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.05556963792846386</v>
+        <v>0.08404830470738953</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.005156312669422155</v>
+        <v>0.03179703730192196</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002047330509909388</v>
+        <v>0.008545077620529119</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.002515570211064945</v>
+        <v>0.03213401898847582</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002493132712907616</v>
+        <v>0.02919882742184133</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.002108499092952365</v>
+        <v>0.009523578690473464</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.003574098715786103</v>
+        <v>0.03140643285653726</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002895363131642121</v>
+        <v>0.03079252280647696</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.004039265751665329</v>
+        <v>0.03784510382794101</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002548484509694457</v>
+        <v>0.0389159681452136</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.003583035886377563</v>
+        <v>0.03501634894686648</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.007271035564334858</v>
+        <v>0.03282967411149543</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.005478724996131851</v>
+        <v>0.03554198334170445</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>0.05221131017310715</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>0.05095696649447664</v>
       </c>
     </row>
     <row r="5">
@@ -1392,142 +1392,142 @@
         </is>
       </c>
       <c r="AW5" t="n">
-        <v>0.002108761734896007</v>
+        <v>0.002935177319347849</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.016398153521233</v>
+        <v>1.017169208875061</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.939294625707664e-05</v>
+        <v>0.001086766763446008</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.666338074277454e-05</v>
+        <v>0.001004088750765986</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.378770207169989e-05</v>
+        <v>0.001588783215901749</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.01814606622159836</v>
+        <v>0.0192516025271687</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0001685885435588507</v>
+        <v>0.001509788544417497</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0007234707757886029</v>
+        <v>0.002015330457900449</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0002209915999740681</v>
+        <v>0.001477248302115173</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.243960072891402e-05</v>
+        <v>0.0006674984500839217</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0001691185931999228</v>
+        <v>0.001032827190216076</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0008088207915176546</v>
+        <v>0.00197584576276304</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0001128685968390015</v>
+        <v>0.001309924680016669</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.746457680103135e-05</v>
+        <v>0.001355791818605261</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.000722956664949e-05</v>
+        <v>0.0008279927559099469</v>
       </c>
       <c r="BL5" t="n">
-        <v>7.312443588020643e-05</v>
+        <v>0.001447780670305231</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.564750846092888e-05</v>
+        <v>0.001321957126954817</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.87622078634095e-05</v>
+        <v>0.001216691625592512</v>
       </c>
       <c r="BO5" t="n">
-        <v>8.352899310148063e-05</v>
+        <v>0.001393797437138358</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.49897928103311e-05</v>
+        <v>0.0008153828897249557</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.105583188007221e-05</v>
+        <v>0.001190892445640797</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.000142260354037453</v>
+        <v>0.001205063384883597</v>
       </c>
       <c r="BS5" t="n">
-        <v>5.868011285452288e-05</v>
+        <v>0.00103240506084538</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0001043377017192811</v>
+        <v>0.001086593597353063</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0001027584660638199</v>
+        <v>0.001482530682709512</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0001354760207525685</v>
+        <v>0.001797803797358283</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.081008487454605e-05</v>
+        <v>0.001341028500516834</v>
       </c>
       <c r="BX5" t="n">
-        <v>7.017375086481334e-05</v>
+        <v>0.001217414447076399</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.000169805895843305</v>
+        <v>0.001350975259857548</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0001285301375959368</v>
+        <v>0.001460812080504114</v>
       </c>
       <c r="CA5" t="n">
-        <v>7.014764286312973e-05</v>
+        <v>0.001748939504136202</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.00476024765793246</v>
+        <v>0.006349149274432521</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0001546334176734477</v>
+        <v>0.001640991285543721</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.427291583427605e-05</v>
+        <v>0.0004267997492642844</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0001051005513264179</v>
+        <v>0.001757593679111374</v>
       </c>
       <c r="CF5" t="n">
-        <v>9.997149969346691e-05</v>
+        <v>0.001589954223329333</v>
       </c>
       <c r="CG5" t="n">
-        <v>4.99408939617864e-05</v>
+        <v>0.0004636481805576781</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0001452030104815127</v>
+        <v>0.001698043986167019</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0001235063788014129</v>
+        <v>0.001679964145845013</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0001168666426891748</v>
+        <v>0.002002985511367482</v>
       </c>
       <c r="CK5" t="n">
-        <v>8.929474847142063e-05</v>
+        <v>0.002118334730753054</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0001530611023626327</v>
+        <v>0.001906810402548358</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0002951235574948605</v>
+        <v>0.001721108924660149</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0001639116279130956</v>
+        <v>0.001841221881000064</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>0.002913009790016779</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>0.002843026573664196</v>
       </c>
     </row>
     <row r="6">
@@ -1682,142 +1682,142 @@
         </is>
       </c>
       <c r="AW6" t="n">
-        <v>0.01855142267865651</v>
+        <v>0.02511694378633653</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0136106306633896</v>
+        <v>0.01973633823231444</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.045210820135344</v>
+        <v>1.053213977607822</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.02106572238697907</v>
+        <v>0.02851316913115505</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.02724310831149247</v>
+        <v>0.03935855049765322</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.01197900241748155</v>
+        <v>0.02076201920236364</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.008606313268919497</v>
+        <v>0.01926157810289366</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01594557264779309</v>
+        <v>0.02620884958816207</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.01576358930831247</v>
+        <v>0.02574401568185767</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.3643205315302415</v>
+        <v>0.3692069130722647</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0474075753825413</v>
+        <v>0.05426937364879205</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.009939008581761406</v>
+        <v>0.01921052672112892</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.01251904245034434</v>
+        <v>0.02202914502953613</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.02438812946902756</v>
+        <v>0.0343850054015093</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.02532410581177745</v>
+        <v>0.03150487066033061</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.009565103598576359</v>
+        <v>0.0204861640102189</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.004511064053453639</v>
+        <v>0.01433301931248164</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.007289814647784244</v>
+        <v>0.01633018096191422</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.008475362392705214</v>
+        <v>0.01888488913433515</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.004948108111368785</v>
+        <v>0.01106855433015461</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.004955716891685047</v>
+        <v>0.01385234355643475</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.01032922405279958</v>
+        <v>0.01877274310496635</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.03287116435139168</v>
+        <v>0.04060699583785751</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.01093176543886039</v>
+        <v>0.01873537168402137</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.01509235921278847</v>
+        <v>0.02605406393207508</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.009248827954313978</v>
+        <v>0.02245531668773601</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.02602871884406698</v>
+        <v>0.03619951086260729</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.02881639276956923</v>
+        <v>0.03793073323976114</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0393933596673865</v>
+        <v>0.04877724900476434</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.009917926123128501</v>
+        <v>0.02050234077129433</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.02132939734081711</v>
+        <v>0.03466668623996189</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.006679930431386955</v>
+        <v>0.01930307948305633</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.00724863146000899</v>
+        <v>0.01905711394590195</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.004169971650322396</v>
+        <v>0.007050093494302243</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.003937464347909564</v>
+        <v>0.01706582097003781</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.006404293165094016</v>
+        <v>0.01824157359174347</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.005751064081279411</v>
+        <v>0.00903779290591551</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.006324775598745454</v>
+        <v>0.01866143816240716</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.009290813183168482</v>
+        <v>0.02165620961929144</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.007137922973727635</v>
+        <v>0.02212233696213859</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.007368664354438346</v>
+        <v>0.02348852593816321</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.005892525428780378</v>
+        <v>0.01982531936996172</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.00735894546362018</v>
+        <v>0.01868779405204141</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.01231108305188883</v>
+        <v>0.0256366012027537</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>0.02314262657077014</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>0.02258663961603357</v>
       </c>
     </row>
     <row r="7">
@@ -1972,142 +1972,142 @@
         </is>
       </c>
       <c r="AW7" t="n">
-        <v>0.007196858280661197</v>
+        <v>0.008538982482395367</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.002211981234418677</v>
+        <v>0.003464198727312448</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.008556909869992498</v>
+        <v>0.01019291577994807</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.008947627019654</v>
+        <v>1.010470034510629</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.008377162623389146</v>
+        <v>0.01085380201058673</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.003526126108476582</v>
+        <v>0.0053215509038426</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.003275549316092894</v>
+        <v>0.00545369916513313</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.004622965401980432</v>
+        <v>0.006720985063307323</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.006669790412265402</v>
+        <v>0.008709989744484777</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.01134750656554415</v>
+        <v>0.01234638096087355</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01265803403022228</v>
+        <v>0.01406072322571966</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.003545474153803304</v>
+        <v>0.005440758424096284</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.005745795749729454</v>
+        <v>0.007689851464907554</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.078000600479722</v>
+        <v>0.08004416243172344</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.2013373516871043</v>
+        <v>0.2026008239922601</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.02593920498902825</v>
+        <v>0.0281716887853138</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.002923544688202976</v>
+        <v>0.004931349346095505</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.01819559897466256</v>
+        <v>0.02004363117557091</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.01555848574483039</v>
+        <v>0.01768640179892672</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.007266754568001636</v>
+        <v>0.008517896535397954</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.00685799561104921</v>
+        <v>0.008676644544579688</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.04538556410872403</v>
+        <v>0.04711158875807906</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.005960429044530781</v>
+        <v>0.007541788161079521</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.004086701911082264</v>
+        <v>0.005681915547694164</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.01209546921144663</v>
+        <v>0.01433626151943402</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.001874042638255657</v>
+        <v>0.00457371382327733</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.002137359634431018</v>
+        <v>0.00421647352272848</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.003145492283164394</v>
+        <v>0.005008646285301504</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.002483488688110338</v>
+        <v>0.004401743885151401</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.003322332081398123</v>
+        <v>0.005485998731388174</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.001560537325438026</v>
+        <v>0.004286946687845493</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.002096375655132297</v>
+        <v>0.004676800508922725</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.002328193977968978</v>
+        <v>0.004742084645616405</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.001235408222430603</v>
+        <v>0.001824162895114077</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001297860237182894</v>
+        <v>0.003981559651528615</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.00162783779944849</v>
+        <v>0.004047615343798542</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.00135221230162818</v>
+        <v>0.002024085596639205</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.00201987279735167</v>
+        <v>0.004541734066817439</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.001932521990677332</v>
+        <v>0.004460257040001139</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.003600209091826913</v>
+        <v>0.006663323859537519</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.001260749789372196</v>
+        <v>0.004555972819698705</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.002547177488990758</v>
+        <v>0.005395320026277075</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.002640620853862913</v>
+        <v>0.004956464732655167</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.002516465377776294</v>
+        <v>0.005240468563144671</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>0.004730817052129199</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>0.004617162166924801</v>
       </c>
     </row>
     <row r="8">
@@ -2262,142 +2262,142 @@
         </is>
       </c>
       <c r="AW8" t="n">
-        <v>0.002601866748582832</v>
+        <v>0.003593191203083292</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.001485860157159148</v>
+        <v>0.002410777405097072</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.08378350483302997</v>
+        <v>0.08499189721888417</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.03914774946994531</v>
+        <v>0.04027223539573961</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.029945521891854</v>
+        <v>1.031774825905846</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001748225838392371</v>
+        <v>0.00307436875688163</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.001305496644781119</v>
+        <v>0.002914329276016055</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.002081981670268662</v>
+        <v>0.003631628263042098</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.002215132356335111</v>
+        <v>0.003722071496148912</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.02977283062669435</v>
+        <v>0.03051062271313831</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.005052566048302025</v>
+        <v>0.00608862522953385</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001557985960142687</v>
+        <v>0.002957887431961632</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.001782325756136809</v>
+        <v>0.003218250962520316</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.005557085993879329</v>
+        <v>0.007066508843633606</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.00983665845628239</v>
+        <v>0.01076988877287072</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.00216810058692303</v>
+        <v>0.003817065547598278</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0009202236189635096</v>
+        <v>0.002403235291547166</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001739005775283704</v>
+        <v>0.003104005758964512</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001824578056701594</v>
+        <v>0.003396306827276002</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0009996513486342962</v>
+        <v>0.001923774188181636</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.00121688661909059</v>
+        <v>0.00256018343143511</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.00297394501798934</v>
+        <v>0.004248827358808005</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.004646648919028344</v>
+        <v>0.005814677899920314</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.002159283706384447</v>
+        <v>0.003337545961161375</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.03182716028964128</v>
+        <v>0.03348226211218065</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.001642732958979806</v>
+        <v>0.003636773496632146</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.003526530466126029</v>
+        <v>0.005062212810947528</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.004141492860661025</v>
+        <v>0.005517662161857153</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.003860346564260146</v>
+        <v>0.005277214902035676</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.002937404871949722</v>
+        <v>0.004535539872235679</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.002262210161586137</v>
+        <v>0.004276000144988029</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001282127388959459</v>
+        <v>0.003188089785925375</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001180553319746029</v>
+        <v>0.002963509655856641</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0008070675921308411</v>
+        <v>0.001241935619976853</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0009141675672586176</v>
+        <v>0.002896410980000844</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.001365192833061254</v>
+        <v>0.00315249735455471</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.002521263763207239</v>
+        <v>0.00301752515750266</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001215758426050805</v>
+        <v>0.003078464384298743</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001421817705643447</v>
+        <v>0.003288862175637242</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.001847325175063676</v>
+        <v>0.004109813678176488</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001387993819597165</v>
+        <v>0.003821922936421774</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.001115327948500456</v>
+        <v>0.003219032913709141</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001732387895883347</v>
+        <v>0.0034429245711669</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001829465706564171</v>
+        <v>0.003841478431097154</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>0.003494292575518536</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>0.00341034440817979</v>
       </c>
     </row>
     <row r="9">
@@ -2552,142 +2552,142 @@
         </is>
       </c>
       <c r="AW9" t="n">
-        <v>0.05098092119134693</v>
+        <v>0.0821168187938888</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.07149887786792665</v>
+        <v>0.1005490325290782</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.003958770847528869</v>
+        <v>0.04191242105643788</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.003385613671019077</v>
+        <v>0.03870389769203936</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.003138307760350159</v>
+        <v>0.06059378785568598</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.136833711282259</v>
+        <v>1.178485715254282</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.008940254707873451</v>
+        <v>0.05947108529350763</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01893180252505444</v>
+        <v>0.06760369537877722</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.008380421912851597</v>
+        <v>0.05571094275039969</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002593583013867532</v>
+        <v>0.02576643903612798</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.007691864464414903</v>
+        <v>0.04023280747309209</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.009044268856054907</v>
+        <v>0.05301290968028073</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.004784665385830202</v>
+        <v>0.04988475344266626</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.004818572326874547</v>
+        <v>0.05222710247613695</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.00252493219635869</v>
+        <v>0.03183618689704509</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.003561093336415309</v>
+        <v>0.0553524154738641</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.004086960496422178</v>
+        <v>0.05066595829206028</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.003709183887769322</v>
+        <v>0.04658162542435325</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.004018970242152307</v>
+        <v>0.0533844285816561</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.002105686402105474</v>
+        <v>0.03113088998070119</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.003547618369516426</v>
+        <v>0.04573839840031458</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.006474537516584741</v>
+        <v>0.04651652966033895</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.00301129320992129</v>
+        <v>0.03969719415864725</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.004985486569168666</v>
+        <v>0.04199279809782573</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.004270077896015446</v>
+        <v>0.05625414893795735</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.006587225052930288</v>
+        <v>0.06921681288746702</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.002616062657862088</v>
+        <v>0.05084936107123379</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.003279028632795616</v>
+        <v>0.04650228036564616</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.006489608125026824</v>
+        <v>0.05099115076425578</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.004985498947535686</v>
+        <v>0.05518033424897698</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.003077092572129416</v>
+        <v>0.06632697855201447</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.1486790753796989</v>
+        <v>0.2085422712857558</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.007281941569165723</v>
+        <v>0.06328171607177029</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.003133333641393759</v>
+        <v>0.01679183497681752</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.00466082475042435</v>
+        <v>0.06691988397393156</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.004675809279799545</v>
+        <v>0.06081215325188759</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.00226443636317111</v>
+        <v>0.01785120403215105</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.006469084782563321</v>
+        <v>0.06497366591778587</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.005608102743115019</v>
+        <v>0.06424894951453085</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.005073985855978776</v>
+        <v>0.07613509005858479</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.004394728370747544</v>
+        <v>0.08084050493689096</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.007851410403606743</v>
+        <v>0.07392538052038665</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.01591123652179252</v>
+        <v>0.0696364266199819</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.007871439290690332</v>
+        <v>0.07106550444430164</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>0.1097500776166084</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>0.1071134014705555</v>
       </c>
     </row>
     <row r="10">
@@ -2842,142 +2842,142 @@
         </is>
       </c>
       <c r="AW10" t="n">
-        <v>0.00114746727867102</v>
+        <v>0.002831026199674554</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.003286817064539615</v>
+        <v>0.004857597122356908</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0002961937735061071</v>
+        <v>0.002348397541951182</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0002947381265944092</v>
+        <v>0.00220444418026768</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0002577269485390229</v>
+        <v>0.003364420300046795</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0008361766895241129</v>
+        <v>0.003088355308554859</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.045178101747702</v>
+        <v>1.047910370195656</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0008320821616770911</v>
+        <v>0.003463835402326353</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.001805161585793515</v>
+        <v>0.004364385077885566</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0002493519283987605</v>
+        <v>0.00150233872130953</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0009520304202691726</v>
+        <v>0.002711561993743179</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0004882780513271238</v>
+        <v>0.002865720270882163</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002898393786644799</v>
+        <v>0.005337014845699557</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001130008861592434</v>
+        <v>0.003693450419735911</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0003068216921173223</v>
+        <v>0.001891719772367906</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0004976080698872067</v>
+        <v>0.003298032953348778</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0003451469483261743</v>
+        <v>0.002863734601435893</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0004905761340647186</v>
+        <v>0.002808745416848647</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0004766345412163469</v>
+        <v>0.003145889779585161</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.001530692214252427</v>
+        <v>0.003100123134230119</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0003196144664310799</v>
+        <v>0.00260092541534521</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.005295672844099919</v>
+        <v>0.007460796006724509</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0002416615454448994</v>
+        <v>0.002225316444548801</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0009610124501063397</v>
+        <v>0.002962046441859355</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0017722377169613</v>
+        <v>0.004583084787116038</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0003257300184263361</v>
+        <v>0.003712194178335468</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.0002842200184329325</v>
+        <v>0.002892257881026245</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0004353391979640126</v>
+        <v>0.002772477249307079</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0002677270061280581</v>
+        <v>0.002673983927482291</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0004472893952355744</v>
+        <v>0.003161390136405333</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0002276471115640811</v>
+        <v>0.003647651607763305</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.001143170381747023</v>
+        <v>0.004380052092817288</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0005832148816050908</v>
+        <v>0.00361119631774488</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0002180422728692361</v>
+        <v>0.0009565753983415558</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0002573064421667931</v>
+        <v>0.003623735632904685</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0002275316611198378</v>
+        <v>0.00326289758803682</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0001969151609549223</v>
+        <v>0.001039712182376857</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0004672748550221266</v>
+        <v>0.003630694479119874</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0002990864136364342</v>
+        <v>0.003469874099845894</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0007395269051295743</v>
+        <v>0.004581894240860157</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0005452055059460212</v>
+        <v>0.004678729156167264</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0009793766307277054</v>
+        <v>0.004552083069328798</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.001102702474735395</v>
+        <v>0.004007694141493491</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.001468628996609501</v>
+        <v>0.004885615187338601</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>0.005934330996681687</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>0.005791762450749606</v>
       </c>
     </row>
     <row r="11">
@@ -3132,142 +3132,142 @@
         </is>
       </c>
       <c r="AW11" t="n">
-        <v>0.003616124839592082</v>
+        <v>0.005094465045820766</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.002541866655325251</v>
+        <v>0.0039211752649873</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.002076775348879874</v>
+        <v>0.003878824154191636</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.001834302303111843</v>
+        <v>0.003511223262635293</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.001140617851894656</v>
+        <v>0.00386861841823043</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.00410257296651994</v>
+        <v>0.006080220533578129</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.005728547577390062</v>
+        <v>0.008127764052934184</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.111143722377634</v>
+        <v>1.113454676024688</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.07551279205122376</v>
+        <v>0.07776005701943138</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.001815983076593635</v>
+        <v>0.002916236076785266</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.00252954155586747</v>
+        <v>0.004074593669425179</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.002348863127038273</v>
+        <v>0.004436505191302208</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.004614510792116868</v>
+        <v>0.006755874253995408</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.004595021716730045</v>
+        <v>0.006845990586570426</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.001782018806712963</v>
+        <v>0.003173724511561398</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.003051293291071723</v>
+        <v>0.005510358220784291</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.001533514218314625</v>
+        <v>0.003745096684512981</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.002056069768761053</v>
+        <v>0.004091664016654086</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.002940373906684428</v>
+        <v>0.005284258216486299</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.001430662460436563</v>
+        <v>0.002808786386457816</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.002011532758438372</v>
+        <v>0.004014761547531874</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.03088969657634113</v>
+        <v>0.03279090037907887</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.002793696850011183</v>
+        <v>0.004535552603345787</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.004544828574702777</v>
+        <v>0.006301944982767327</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.03320081376934469</v>
+        <v>0.03566903046525512</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.002154039724841828</v>
+        <v>0.005127708220840732</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.002587703160524148</v>
+        <v>0.004877832233844725</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.003016395053000085</v>
+        <v>0.005068645856760438</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.002150535915969784</v>
+        <v>0.004263480291705449</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.00304305766236508</v>
+        <v>0.005426320997772813</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.00197807233491702</v>
+        <v>0.004981192742012992</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.002179590862856422</v>
+        <v>0.005021910378130119</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.003348773935974686</v>
+        <v>0.006007657236650165</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.001417000935195555</v>
+        <v>0.002065509995019052</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.00144700844410537</v>
+        <v>0.00440308414897182</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.001561723510821704</v>
+        <v>0.004227091164068546</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.002493748878743432</v>
+        <v>0.003233812506403783</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.001799509574284728</v>
+        <v>0.004577321720407243</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.001594315094417197</v>
+        <v>0.00437859716703046</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.002693728983625437</v>
+        <v>0.006067727985765731</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.001542095848307476</v>
+        <v>0.005171760441143183</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.001959446383620845</v>
+        <v>0.00509665501192819</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.003511539651685229</v>
+        <v>0.006062425115894507</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.002656191312667216</v>
+        <v>0.005656661332969181</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>0.005210961137157177</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>0.005085771094227568</v>
       </c>
     </row>
     <row r="12">
@@ -3422,142 +3422,142 @@
         </is>
       </c>
       <c r="AW12" t="n">
-        <v>0.005536991677285392</v>
+        <v>0.009687294279698111</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.008303756930704998</v>
+        <v>0.01217603753843755</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.003613870570058617</v>
+        <v>0.008672954950533895</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.002827120497826853</v>
+        <v>0.007534920091605884</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.002623756023970674</v>
+        <v>0.01028236383436755</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.01873455878708701</v>
+        <v>0.02428662035561822</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.009816014191759027</v>
+        <v>0.01655159125328279</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.007474401853518428</v>
+        <v>0.01396218923494493</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.11524377429516</v>
+        <v>1.121552761635535</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.003125195112952491</v>
+        <v>0.006214053056995554</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.007561991934808944</v>
+        <v>0.01189958201099327</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.009303411578903825</v>
+        <v>0.01516427246580619</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.009784083625023945</v>
+        <v>0.0157957623381518</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.007762364764774083</v>
+        <v>0.01408175046441688</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.002467842111604628</v>
+        <v>0.006374926410799829</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.004886122882941465</v>
+        <v>0.0117897189119797</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.005795408411773987</v>
+        <v>0.01200422044721796</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.008197526662347509</v>
+        <v>0.01391226814667669</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.005059681943128662</v>
+        <v>0.01163991909675462</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.002533105533447478</v>
+        <v>0.006402060252066875</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.003335572806119943</v>
+        <v>0.008959451275753309</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.008937342936478984</v>
+        <v>0.01427479574806729</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.002308409912083273</v>
+        <v>0.007198507898753256</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.005705812545514654</v>
+        <v>0.01063875340067551</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.004788445868684443</v>
+        <v>0.01171773462995548</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.009219728912714107</v>
+        <v>0.01756802658172024</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.00284788870073452</v>
+        <v>0.009277213028664716</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.003949032238217308</v>
+        <v>0.009710535453623074</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.003579872431722175</v>
+        <v>0.009511767204265836</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.004919270624939779</v>
+        <v>0.01161006072961441</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.007104781435147564</v>
+        <v>0.01553576260471546</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.007345475262356526</v>
+        <v>0.0153250228870689</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.03227408425759978</v>
+        <v>0.03973865177447495</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.01025501708739144</v>
+        <v>0.01207564594354618</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.007211030995471037</v>
+        <v>0.01550993853998952</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.00642210284037517</v>
+        <v>0.01390487457387009</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.002010056496410041</v>
+        <v>0.004087716284656799</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.009167937352322667</v>
+        <v>0.01696638653911462</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.006009295403066267</v>
+        <v>0.01382590830659868</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.004865639098662673</v>
+        <v>0.01433782742183856</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.006741864660191065</v>
+        <v>0.01693181034526504</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.005947372323533944</v>
+        <v>0.01475479370023531</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.01591773491751859</v>
+        <v>0.02307910855530414</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.01537748366679534</v>
+        <v>0.02380102412199842</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>0.01462928862889189</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>0.01427782922950751</v>
       </c>
     </row>
     <row r="13">
@@ -3712,142 +3712,142 @@
         </is>
       </c>
       <c r="AW13" t="n">
-        <v>0.03351623691616657</v>
+        <v>0.04268061665898943</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.03134125070737939</v>
+        <v>0.03989172361492114</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.01860780393402301</v>
+        <v>0.02977888586590589</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02543084431996732</v>
+        <v>0.03582624614088926</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.02684349758241421</v>
+        <v>0.04375464768386085</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.01582594685831029</v>
+        <v>0.02808558318939943</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.009295973281252175</v>
+        <v>0.02416895770965661</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.02318178528422566</v>
+        <v>0.03750761955460456</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0131625266711772</v>
+        <v>0.02709354841071012</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.052800796278895</v>
+        <v>1.059621375374595</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.02581734652847234</v>
+        <v>0.03539528009980863</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.009800110179497459</v>
+        <v>0.02274161347041572</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0124420569776128</v>
+        <v>0.0257165846197468</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.01660861997440055</v>
+        <v>0.03056260257297636</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01572153613870037</v>
+        <v>0.02434885988714956</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.008369339881472216</v>
+        <v>0.0236133309013971</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.00475097626342343</v>
+        <v>0.01846079858132854</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.007510881353279859</v>
+        <v>0.02012973499156881</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.006971502061721477</v>
+        <v>0.02150147682515278</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.005618231111021806</v>
+        <v>0.01416136004542827</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.004670555774184303</v>
+        <v>0.01708877267558421</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.01588864891143667</v>
+        <v>0.02767440265294871</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.01041922183620892</v>
+        <v>0.02121716098006915</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0217768413097632</v>
+        <v>0.03266938278837702</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.01888954064253206</v>
+        <v>0.03419026438230133</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.01113904971188656</v>
+        <v>0.0295731200373657</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.06544097854328235</v>
+        <v>0.0796377191849572</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.07110444541476198</v>
+        <v>0.08382655471946156</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1063893487442146</v>
+        <v>0.1194877036107859</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.01655878435105663</v>
+        <v>0.03133287365796986</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.03426402621118643</v>
+        <v>0.05288067189807979</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.008831262966569312</v>
+        <v>0.02645108773941663</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.007026045153700066</v>
+        <v>0.02350873036822303</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.005775720485053648</v>
+        <v>0.009795893423490401</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.004979178784951828</v>
+        <v>0.02330418962737376</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.006328109192293099</v>
+        <v>0.02285099156109756</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.00499881788937926</v>
+        <v>0.009586546809390377</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.006932035617792189</v>
+        <v>0.02415197271619142</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.01574702069961233</v>
+        <v>0.03300706552356724</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.009673489752285465</v>
+        <v>0.03058924918116483</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.01000229656667594</v>
+        <v>0.03250295272665554</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.007749065623245855</v>
+        <v>0.02719693769026689</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.008573820520078922</v>
+        <v>0.02438701627567389</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01708140305540297</v>
+        <v>0.03568161872778186</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>0.03230327260585455</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>0.03152720692855419</v>
       </c>
     </row>
     <row r="14">
@@ -4002,142 +4002,142 @@
         </is>
       </c>
       <c r="AW14" t="n">
-        <v>0.04281365764468286</v>
+        <v>0.04736282197185913</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.01038829872557446</v>
+        <v>0.01463272196239405</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.008002232074526598</v>
+        <v>0.01354751597224856</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.01614148142943075</v>
+        <v>0.02130172057899645</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.00669942525291818</v>
+        <v>0.01509405783383822</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.01661319550543197</v>
+        <v>0.0226988337948342</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.04322087909925007</v>
+        <v>0.05060377375214064</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02701597353602152</v>
+        <v>0.03412726486709995</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.03158601036996624</v>
+        <v>0.03850131821589355</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.01425322069785136</v>
+        <v>0.0176389310223436</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.135369164441689</v>
+        <v>1.140123615365103</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.08405200612500204</v>
+        <v>0.09047612066010589</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.1130038511674115</v>
+        <v>0.1195932777630306</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0193665880807583</v>
+        <v>0.02629329361248763</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.02035593089709582</v>
+        <v>0.02463850260809265</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.01194099617993357</v>
+        <v>0.01950805713743563</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.005990745425962422</v>
+        <v>0.01279625069426856</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.01549271475043959</v>
+        <v>0.0217566671871683</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.008875536354635078</v>
+        <v>0.01608816227406396</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.00956202723264738</v>
+        <v>0.0138028049482703</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.004718843422715413</v>
+        <v>0.01088320052273938</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.01313329455242745</v>
+        <v>0.01898369927095301</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.005656165886359642</v>
+        <v>0.0110162230793998</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.005885314031950329</v>
+        <v>0.01129233147528628</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.01127592787002178</v>
+        <v>0.01887115074055476</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.004456072755931352</v>
+        <v>0.01360667732303296</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.006278708918402673</v>
+        <v>0.01332591864799291</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.006487787806581488</v>
+        <v>0.01280299597554692</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.007263943850482581</v>
+        <v>0.01376591892963261</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.006507073651320968</v>
+        <v>0.01384087713040113</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.005881543996978419</v>
+        <v>0.01512277830056791</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.006596683252090299</v>
+        <v>0.01534309932793089</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.007608208170877265</v>
+        <v>0.01579015236112173</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.003314029595911496</v>
+        <v>0.005309628625397215</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.004140083545427757</v>
+        <v>0.01323655138710038</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.003580688956379856</v>
+        <v>0.01178258686585498</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.002185990885797466</v>
+        <v>0.004463322612695211</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.005592659359921806</v>
+        <v>0.01414057266803265</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.007656258756624454</v>
+        <v>0.01622408139187607</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.005482584441212273</v>
+        <v>0.01586509033247844</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.003490856674199957</v>
+        <v>0.01466009946132927</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.006147386389075935</v>
+        <v>0.01580123840410913</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.005748789503805338</v>
+        <v>0.01359840159417573</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.01418927426921176</v>
+        <v>0.02342235277415239</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>0.01603522546135117</v>
       </c>
       <c r="CP14" t="n">
-        <v>0</v>
+        <v>0.01564998931948509</v>
       </c>
     </row>
     <row r="15">
@@ -4292,142 +4292,142 @@
         </is>
       </c>
       <c r="AW15" t="n">
-        <v>0.0008578365227878205</v>
+        <v>0.002348233390155604</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.001078806670085441</v>
+        <v>0.002469364284843116</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.0004255441704967351</v>
+        <v>0.002242289655037148</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.0004652958946272923</v>
+        <v>0.002155893048358842</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.0003443892349559703</v>
+        <v>0.003094638116176912</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.0009482388301587134</v>
+        <v>0.002942015178987244</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0009646153353296907</v>
+        <v>0.003383398714299088</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.000750549463193966</v>
+        <v>0.003080350182737918</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0008132812527658552</v>
+        <v>0.003078873877961554</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0004049717402267095</v>
+        <v>0.001514197896620612</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.001870509430897492</v>
+        <v>0.003428162277153215</v>
       </c>
       <c r="BH15" t="n">
-        <v>1.03969485369868</v>
+        <v>1.041799521609121</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.001521630067888115</v>
+        <v>0.003680457502894587</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.0007637282712231784</v>
+        <v>0.003033055005365684</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.0005100042632125591</v>
+        <v>0.00191306007814933</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0005768871843325272</v>
+        <v>0.003056007113869675</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0004501138386922854</v>
+        <v>0.002679732951843612</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.0004858400129777682</v>
+        <v>0.002538035629053944</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0005342176939578482</v>
+        <v>0.002897217643551877</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0003685729253995891</v>
+        <v>0.00175793619478289</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.0003978556064599351</v>
+        <v>0.002417421805976578</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.0007779221424535203</v>
+        <v>0.002694631286863882</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.0003012480009616121</v>
+        <v>0.002057309526744711</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.001002694072308096</v>
+        <v>0.002774140711685256</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.000606368860900033</v>
+        <v>0.003094715194220756</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0003788118195161529</v>
+        <v>0.003376732184770331</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.0003117356428001962</v>
+        <v>0.002620541952987829</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0004196851444926835</v>
+        <v>0.002488673159626394</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0003725427225021479</v>
+        <v>0.002502719298401668</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.0003452467721057801</v>
+        <v>0.002747946904482969</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.0002889837044585244</v>
+        <v>0.003316596177017992</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0005538506317001367</v>
+        <v>0.003419350794500242</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.0005729112741682079</v>
+        <v>0.003253479201176373</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0003008566152243177</v>
+        <v>0.0009546546159472003</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0003319918135088825</v>
+        <v>0.003312175908937216</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.0003642724672721956</v>
+        <v>0.00305137763024171</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.000194619434617252</v>
+        <v>0.0009407186800213951</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0004123023668787174</v>
+        <v>0.00321276906816571</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.0003586725643040207</v>
+        <v>0.003165661957819285</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.008917895649669336</v>
+        <v>0.0123194114321022</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.0003262370533857935</v>
+        <v>0.003985503517198173</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.004465303775793811</v>
+        <v>0.007628098031276007</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0007016094535187019</v>
+        <v>0.003273298763498423</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.000836610448538737</v>
+        <v>0.003861550918971455</v>
       </c>
       <c r="CO15" t="n">
-        <v>0</v>
+        <v>0.005253459333698819</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>0.005127248298497451</v>
       </c>
     </row>
     <row r="16">
@@ -4582,142 +4582,142 @@
         </is>
       </c>
       <c r="AW16" t="n">
-        <v>0.01337949744647278</v>
+        <v>0.01629562765582844</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.01464784410745788</v>
+        <v>0.01736862751557528</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.004686474592213902</v>
+        <v>0.008241142819298582</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.006291783083216975</v>
+        <v>0.009599627818931051</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.003845954231711954</v>
+        <v>0.009227127542911556</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0148125339442928</v>
+        <v>0.01871358310027105</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.01996977232039842</v>
+        <v>0.02470239584889343</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.01563544657595651</v>
+        <v>0.0201939654569306</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.0204053743471508</v>
+        <v>0.02483826282208091</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.005278323160220501</v>
+        <v>0.007448649718528758</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.01076140712600714</v>
+        <v>0.01380913127258121</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.008837278435899442</v>
+        <v>0.01295529948698892</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.070661636502333</v>
+        <v>1.074885626795017</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.01354264374220319</v>
+        <v>0.01798283842405256</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.006586675205872792</v>
+        <v>0.00933191275765006</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.0117909208253797</v>
+        <v>0.01664159964618735</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.008878741814327551</v>
+        <v>0.01324124404012759</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.008248516913461951</v>
+        <v>0.01226386997986787</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.008793531433490849</v>
+        <v>0.01341700836677712</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.02881743624368668</v>
+        <v>0.03153588277985885</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.004195306076636083</v>
+        <v>0.008146815995336679</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.01697149288593447</v>
+        <v>0.02072175133114631</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.003908408607482155</v>
+        <v>0.007344341798798783</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.004213458365202974</v>
+        <v>0.007679494273123702</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.01832943095279583</v>
+        <v>0.02319816227719235</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.004512912854415581</v>
+        <v>0.01037868346476332</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.007135863280919597</v>
+        <v>0.01165330422306276</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.006037946481537338</v>
+        <v>0.01008615577788536</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.004386729277399807</v>
+        <v>0.008554660920475052</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.01122331663057412</v>
+        <v>0.01592447146621359</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.008103231030154702</v>
+        <v>0.01402709761009831</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.005834522069754522</v>
+        <v>0.01144119756177495</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.003255274643054896</v>
+        <v>0.008500109278264469</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.001550803478471345</v>
+        <v>0.002830033287972719</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.002185034141685477</v>
+        <v>0.008016101732070638</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.002056541091837644</v>
+        <v>0.007314166569332231</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.001912990851608012</v>
+        <v>0.00337281849640377</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.002964462173413185</v>
+        <v>0.008443892335085927</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.002902207412472928</v>
+        <v>0.008394399959970321</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.00345712514257111</v>
+        <v>0.01011257588051525</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.00199025044459333</v>
+        <v>0.009150019572430683</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.002662328748307827</v>
+        <v>0.008850693791423699</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.00809862029311062</v>
+        <v>0.0131304215871872</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.005602636749284014</v>
+        <v>0.01152127525455041</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>0.01027898796759895</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>0.01003204178798521</v>
       </c>
     </row>
     <row r="17">
@@ -4872,142 +4872,142 @@
         </is>
       </c>
       <c r="AW17" t="n">
-        <v>0.002303630226316824</v>
+        <v>0.004078615380589711</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.002063058437563487</v>
+        <v>0.003719140234565083</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.00351446331950345</v>
+        <v>0.00567811270360792</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.005395941645215344</v>
+        <v>0.007409354928235213</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.009197435533720736</v>
+        <v>0.01247283891224793</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.004022860978227555</v>
+        <v>0.006397344914416442</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.003699603102055283</v>
+        <v>0.006580248306748426</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.00487490468208069</v>
+        <v>0.007649576167339738</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.005014482478235683</v>
+        <v>0.007712685462555395</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.002872339271557397</v>
+        <v>0.004193369933549859</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.004816573920136576</v>
+        <v>0.006671657447316686</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.002652321556636431</v>
+        <v>0.005158871575293556</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.007930457382608995</v>
+        <v>0.01050150857821509</v>
       </c>
       <c r="BJ17" t="n">
-        <v>1.160863967198502</v>
+        <v>1.163566617312368</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.008969452694939326</v>
+        <v>0.01064041919832936</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.007932393015177111</v>
+        <v>0.01088489591352399</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.001535681552055752</v>
+        <v>0.004191041954494176</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.007476784941790914</v>
+        <v>0.009920843186916188</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.004446960580987502</v>
+        <v>0.007261170622561592</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01325250506413574</v>
+        <v>0.01490716445791374</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.006289925719127451</v>
+        <v>0.008695124026169223</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.004055168487471782</v>
+        <v>0.006337869391423655</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.002532326738046135</v>
+        <v>0.004623704683411622</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.002741138277571238</v>
+        <v>0.004850839093055534</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.03607722590850644</v>
+        <v>0.03904071697389913</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.001491886633350059</v>
+        <v>0.005062253868096397</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.002231911176884004</v>
+        <v>0.004981579412507937</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.002739246544331934</v>
+        <v>0.005203303663370833</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.001519409818350938</v>
+        <v>0.00405633933087685</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.003133496997025972</v>
+        <v>0.005994987891509046</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.00124049820499135</v>
+        <v>0.004846227195267303</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.002537475075182319</v>
+        <v>0.005950136735911377</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.001550500164300759</v>
+        <v>0.004742917150430551</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.0009675890992487978</v>
+        <v>0.00174622851441743</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.001249067531548455</v>
+        <v>0.004798311791386334</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.001386010522847849</v>
+        <v>0.004586213017009381</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.002670910095508414</v>
+        <v>0.003559475492552929</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.001531557138849996</v>
+        <v>0.004866767329273282</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.001614567269253045</v>
+        <v>0.004957545646878388</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.002158391772864013</v>
+        <v>0.006209420158683444</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.001308752506987167</v>
+        <v>0.005666748548851375</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.001516586712254621</v>
+        <v>0.005283310175257663</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.002301154282939161</v>
+        <v>0.005363902498908041</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.001937282899489236</v>
+        <v>0.005539829674201665</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>0.00625659683676097</v>
       </c>
       <c r="CP17" t="n">
-        <v>0</v>
+        <v>0.00610628605800612</v>
       </c>
     </row>
     <row r="18">
@@ -5162,142 +5162,142 @@
         </is>
       </c>
       <c r="AW18" t="n">
-        <v>0.008284595888258077</v>
+        <v>0.01031112808324188</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.004776827627956761</v>
+        <v>0.006667605740140563</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.01697627247784164</v>
+        <v>0.01944654955311146</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.01147683924035704</v>
+        <v>0.01377558908061655</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.02719073703780315</v>
+        <v>0.03093032346880245</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.004578523740926321</v>
+        <v>0.007289514383059233</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.006894182958629084</v>
+        <v>0.01018306694483219</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.007604828049690598</v>
+        <v>0.0107727199511214</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.007611873038816383</v>
+        <v>0.01069245948944797</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.007699076051551962</v>
+        <v>0.009207320309620222</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.01644231087862565</v>
+        <v>0.01856029281394759</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.008962427295824183</v>
+        <v>0.01182420013877888</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.01769090478135948</v>
+        <v>0.0206263197679607</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.01081220974848493</v>
+        <v>0.01389787356620307</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.182890601524262</v>
+        <v>1.184798373771092</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.1399053423247624</v>
+        <v>0.1432762675208856</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.008838646763724952</v>
+        <v>0.01187031907482717</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.09762089845146714</v>
+        <v>0.1004113233224802</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.07639269789597042</v>
+        <v>0.07960573167203761</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.03263937019812378</v>
+        <v>0.03452852432718866</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.03079884308952895</v>
+        <v>0.03354490087643894</v>
       </c>
       <c r="BR18" t="n">
-        <v>0.03457239341865672</v>
+        <v>0.03717859373658113</v>
       </c>
       <c r="BS18" t="n">
-        <v>0.002613228601012337</v>
+        <v>0.005000992086222106</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.005020675344444048</v>
+        <v>0.007429358377127714</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.01476839217400546</v>
+        <v>0.01815186275634127</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.002147377034015415</v>
+        <v>0.006223728958261624</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.003009967024822222</v>
+        <v>0.006149312270387872</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.004257741002253798</v>
+        <v>0.007070998944152992</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.003437535405240994</v>
+        <v>0.006333993057949852</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.004400670785583264</v>
+        <v>0.007667685954337413</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.002485658076364789</v>
+        <v>0.006602383147326845</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.002707750123836313</v>
+        <v>0.006604046782659562</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.003329231149557017</v>
+        <v>0.006974070536878756</v>
       </c>
       <c r="CD18" t="n">
-        <v>0.001817937541608985</v>
+        <v>0.002706924043453268</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.002151187785449646</v>
+        <v>0.006203423232663482</v>
       </c>
       <c r="CF18" t="n">
-        <v>0.001834010708893822</v>
+        <v>0.005487738949535065</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.00176684752900067</v>
+        <v>0.002781338484107798</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.002763239472623662</v>
+        <v>0.006571108406997702</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.003562218064527719</v>
+        <v>0.007378956076721218</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.002893283164348902</v>
+        <v>0.007518414493979279</v>
       </c>
       <c r="CK18" t="n">
-        <v>0.001664656202070607</v>
+        <v>0.006640257977211994</v>
       </c>
       <c r="CL18" t="n">
-        <v>0.00298324025606438</v>
+        <v>0.007283775586740717</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.004291248455161302</v>
+        <v>0.007788042695861698</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.004449844963353963</v>
+        <v>0.008562936842074756</v>
       </c>
       <c r="CO18" t="n">
-        <v>0</v>
+        <v>0.007143268150839198</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>0.006971655655001407</v>
       </c>
     </row>
     <row r="19">
@@ -5452,142 +5452,142 @@
         </is>
       </c>
       <c r="AW19" t="n">
-        <v>0.005593261897739774</v>
+        <v>0.008655786527266889</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.007209286103872398</v>
+        <v>0.01006665720898823</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.009431443411903521</v>
+        <v>0.0131645616932198</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.008393625640039421</v>
+        <v>0.01186752949428959</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.006875140692719983</v>
+        <v>0.01252645754696433</v>
       </c>
       <c r="BB19" t="n">
-        <v>0.007988833188729783</v>
+        <v>0.01208572127790023</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.005552589080305068</v>
+        <v>0.01052279791110278</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.008965750473053735</v>
+        <v>0.01375311432339161</v>
       </c>
       <c r="BE19" t="n">
-        <v>0.00604704552532801</v>
+        <v>0.0107024721214607</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.005382537549829003</v>
+        <v>0.007661817987174247</v>
       </c>
       <c r="BG19" t="n">
-        <v>0.004706238677475871</v>
+        <v>0.007906963471225716</v>
       </c>
       <c r="BH19" t="n">
-        <v>0.003771252322505339</v>
+        <v>0.008096004644405</v>
       </c>
       <c r="BI19" t="n">
-        <v>0.009356443819612186</v>
+        <v>0.013792485209234</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.01070830126515099</v>
+        <v>0.01537140085152495</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.0160749787298216</v>
+        <v>0.01895803161588538</v>
       </c>
       <c r="BL19" t="n">
-        <v>1.059330077618756</v>
+        <v>1.064424268307152</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.01007391204155773</v>
+        <v>0.0146554188858051</v>
       </c>
       <c r="BN19" t="n">
-        <v>0.01955140612762371</v>
+        <v>0.02376833636711135</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.02792988612016988</v>
+        <v>0.03278546902137659</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.04558026210205898</v>
+        <v>0.04843517902050463</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.0179298755842165</v>
+        <v>0.02207975764744412</v>
       </c>
       <c r="BR19" t="n">
-        <v>0.01376307654997428</v>
+        <v>0.01770160399250953</v>
       </c>
       <c r="BS19" t="n">
-        <v>0.004149069697803179</v>
+        <v>0.007757492253852865</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.01150559267856773</v>
+        <v>0.01514562915594369</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.03485047104315478</v>
+        <v>0.03996362049981403</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.003284544231449195</v>
+        <v>0.009444785947581446</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.005623222861324753</v>
+        <v>0.0103674465943262</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.005174329074581947</v>
+        <v>0.009425764979525918</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.003810902747254962</v>
+        <v>0.008188071253020589</v>
       </c>
       <c r="BZ19" t="n">
-        <v>0.00686562485235731</v>
+        <v>0.01180278521137556</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.004104776901785336</v>
+        <v>0.01032603109849641</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.00545720478210621</v>
+        <v>0.01134534438883267</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.005797529757053567</v>
+        <v>0.01130566351479659</v>
       </c>
       <c r="CD19" t="n">
-        <v>0.003254149794028217</v>
+        <v>0.004597598994566101</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.005337111901205144</v>
+        <v>0.0114609084500354</v>
       </c>
       <c r="CF19" t="n">
-        <v>0.003672885193566902</v>
+        <v>0.009194451914421305</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.004273629575951946</v>
+        <v>0.005806742913178202</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.00634428451099551</v>
+        <v>0.01209879086741927</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.008986776069300683</v>
+        <v>0.01475468550381544</v>
       </c>
       <c r="CJ19" t="n">
-        <v>0.005452789423463542</v>
+        <v>0.0124423544779204</v>
       </c>
       <c r="CK19" t="n">
-        <v>0.002921737266574809</v>
+        <v>0.01044093830409454</v>
       </c>
       <c r="CL19" t="n">
-        <v>0.004736111331894494</v>
+        <v>0.01123514223944595</v>
       </c>
       <c r="CM19" t="n">
-        <v>0.009269538583024933</v>
+        <v>0.01455394438375249</v>
       </c>
       <c r="CN19" t="n">
-        <v>0.007146057021297826</v>
+        <v>0.01336182068558596</v>
       </c>
       <c r="CO19" t="n">
-        <v>0</v>
+        <v>0.01079500967288434</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>0.01053566639842822</v>
       </c>
     </row>
     <row r="20">
@@ -5742,142 +5742,142 @@
         </is>
       </c>
       <c r="AW20" t="n">
-        <v>0.0008890149630211835</v>
+        <v>0.002244706992696652</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.001295999042730449</v>
+        <v>0.002560875476925416</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.001675445081537261</v>
+        <v>0.003327989734083526</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.0009545965523661317</v>
+        <v>0.002492394394597048</v>
       </c>
       <c r="BA20" t="n">
-        <v>0.002767654343424744</v>
+        <v>0.005269330621421796</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.0008773743496298117</v>
+        <v>0.002690949488066608</v>
       </c>
       <c r="BC20" t="n">
-        <v>0.0008950729028882985</v>
+        <v>0.003095242146515086</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.0009107162691003259</v>
+        <v>0.003029945271370156</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.001074479458653436</v>
+        <v>0.003135303613426295</v>
       </c>
       <c r="BF20" t="n">
-        <v>0.0008818165143602718</v>
+        <v>0.001890788750048476</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.0007796229719739116</v>
+        <v>0.002196492260219061</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.0009518422356808973</v>
+        <v>0.002866286350380198</v>
       </c>
       <c r="BI20" t="n">
-        <v>0.000810307430554459</v>
+        <v>0.002774016031372922</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.001101080366494998</v>
+        <v>0.003165301134510924</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.000654546992190185</v>
+        <v>0.001930792016013237</v>
       </c>
       <c r="BL20" t="n">
-        <v>0.0009096882981186626</v>
+        <v>0.00316474076278125</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.03721604158094</v>
+        <v>1.039244143576518</v>
       </c>
       <c r="BN20" t="n">
-        <v>0.01212536217128276</v>
+        <v>0.0139920765350636</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.003718495544457664</v>
+        <v>0.005867923168689</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.00406830668120352</v>
+        <v>0.005332096717177871</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.001009890819125677</v>
+        <v>0.002846924873633696</v>
       </c>
       <c r="BR20" t="n">
-        <v>0.001273094339116326</v>
+        <v>0.003016567750243669</v>
       </c>
       <c r="BS20" t="n">
-        <v>0.0006605871022032374</v>
+        <v>0.002257932524921715</v>
       </c>
       <c r="BT20" t="n">
-        <v>0.002008199313643454</v>
+        <v>0.003619539314807308</v>
       </c>
       <c r="BU20" t="n">
-        <v>0.002872144320253167</v>
+        <v>0.005135589289184804</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.0008371721002452583</v>
+        <v>0.003564134853431135</v>
       </c>
       <c r="BW20" t="n">
-        <v>0.0008846410907202402</v>
+        <v>0.00298477319735423</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.001123726329881038</v>
+        <v>0.003005715364496122</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.0007197955816557336</v>
+        <v>0.002657442841240133</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.001100347198616939</v>
+        <v>0.00328588682935755</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.0008244773209276076</v>
+        <v>0.003578448553599317</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.0008623846116716846</v>
+        <v>0.003468895546308015</v>
       </c>
       <c r="CC20" t="n">
-        <v>0.003654922722003846</v>
+        <v>0.006093215939881296</v>
       </c>
       <c r="CD20" t="n">
-        <v>0.01266041090102999</v>
+        <v>0.01325511742383902</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.00226051801063058</v>
+        <v>0.004971347531007444</v>
       </c>
       <c r="CF20" t="n">
-        <v>0.001089077168584285</v>
+        <v>0.003533316774892193</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.0005455584831404144</v>
+        <v>0.00122422389266162</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.001704975056929479</v>
+        <v>0.004252330375121684</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.001269212727008844</v>
+        <v>0.003822501204388046</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0.001527048011995323</v>
+        <v>0.004621128478766455</v>
       </c>
       <c r="CK20" t="n">
-        <v>0.001100071795543135</v>
+        <v>0.004428606958268351</v>
       </c>
       <c r="CL20" t="n">
-        <v>0.002511940291579597</v>
+        <v>0.005388875326496361</v>
       </c>
       <c r="CM20" t="n">
-        <v>0.001710709478841297</v>
+        <v>0.004049964731369128</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.001226754053051188</v>
+        <v>0.003978294784112336</v>
       </c>
       <c r="CO20" t="n">
-        <v>0</v>
+        <v>0.004778641919382254</v>
       </c>
       <c r="CP20" t="n">
-        <v>0</v>
+        <v>0.004663838072013888</v>
       </c>
     </row>
     <row r="21">
@@ -6032,142 +6032,142 @@
         </is>
       </c>
       <c r="AW21" t="n">
-        <v>0.001575485353503198</v>
+        <v>0.00286299589465803</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.002149139883378112</v>
+        <v>0.003350402195641026</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.001412608730601001</v>
+        <v>0.002982042358083266</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.001247333208095965</v>
+        <v>0.002707790958601015</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.002415802038512547</v>
+        <v>0.004791662121756698</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.001241398246076143</v>
+        <v>0.002963763692506236</v>
       </c>
       <c r="BC21" t="n">
-        <v>0.0009205960010262958</v>
+        <v>0.003010112669625621</v>
       </c>
       <c r="BD21" t="n">
-        <v>0.002059838259262187</v>
+        <v>0.004072485394317344</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.001565575737733255</v>
+        <v>0.003522755366038453</v>
       </c>
       <c r="BF21" t="n">
-        <v>0.0009693543168728233</v>
+        <v>0.001927582558055369</v>
       </c>
       <c r="BG21" t="n">
-        <v>0.0009911774628995795</v>
+        <v>0.002336788489683344</v>
       </c>
       <c r="BH21" t="n">
-        <v>0.0008891716439582868</v>
+        <v>0.002707333087835205</v>
       </c>
       <c r="BI21" t="n">
-        <v>0.001042222404391615</v>
+        <v>0.002907170687605621</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.00160140564137535</v>
+        <v>0.003561811057882402</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.001960508012794421</v>
+        <v>0.00317256715698068</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.00199384596340365</v>
+        <v>0.004135485624592257</v>
       </c>
       <c r="BM21" t="n">
-        <v>0.007865655876302603</v>
+        <v>0.009791759032982301</v>
       </c>
       <c r="BN21" t="n">
-        <v>1.02448176875139</v>
+        <v>1.026254600905068</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.00311247603196076</v>
+        <v>0.005153803017050217</v>
       </c>
       <c r="BP21" t="n">
-        <v>0.003152468772199925</v>
+        <v>0.004352699324202899</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0.001158554066000688</v>
+        <v>0.002903198614958954</v>
       </c>
       <c r="BR21" t="n">
-        <v>0.001224372506344597</v>
+        <v>0.002880161834535145</v>
       </c>
       <c r="BS21" t="n">
-        <v>0.001134389577590384</v>
+        <v>0.002651400096644464</v>
       </c>
       <c r="BT21" t="n">
-        <v>0.002094180810596677</v>
+        <v>0.003624482082176426</v>
       </c>
       <c r="BU21" t="n">
-        <v>0.006280419266703376</v>
+        <v>0.008430029349991227</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.0007963235785343347</v>
+        <v>0.003386139859230398</v>
       </c>
       <c r="BW21" t="n">
-        <v>0.001189167791751528</v>
+        <v>0.003183678466684275</v>
       </c>
       <c r="BX21" t="n">
-        <v>0.002202980907709966</v>
+        <v>0.003990319526927764</v>
       </c>
       <c r="BY21" t="n">
-        <v>0.0007704223040538137</v>
+        <v>0.002610619942710647</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0.001750383030753563</v>
+        <v>0.003826005850018629</v>
       </c>
       <c r="CA21" t="n">
-        <v>0.001079701063780894</v>
+        <v>0.00369516749309286</v>
       </c>
       <c r="CB21" t="n">
-        <v>0.0009646169527675454</v>
+        <v>0.003440039268839552</v>
       </c>
       <c r="CC21" t="n">
-        <v>0.001507238576039583</v>
+        <v>0.003822903307944111</v>
       </c>
       <c r="CD21" t="n">
-        <v>0.003485038423287364</v>
+        <v>0.004049835516026384</v>
       </c>
       <c r="CE21" t="n">
-        <v>0.001782568701766651</v>
+        <v>0.004357063134395582</v>
       </c>
       <c r="CF21" t="n">
-        <v>0.0008842703694473055</v>
+        <v>0.003205582429519612</v>
       </c>
       <c r="CG21" t="n">
-        <v>0.0008819886302475002</v>
+        <v>0.001526522085891466</v>
       </c>
       <c r="CH21" t="n">
-        <v>0.001477114106509628</v>
+        <v>0.003896355905124027</v>
       </c>
       <c r="CI21" t="n">
-        <v>0.0024050454134882</v>
+        <v>0.004829921976362027</v>
       </c>
       <c r="CJ21" t="n">
-        <v>0.0009654009476774944</v>
+        <v>0.003903871580349665</v>
       </c>
       <c r="CK21" t="n">
-        <v>0.0009760938621781254</v>
+        <v>0.004137227817977154</v>
       </c>
       <c r="CL21" t="n">
-        <v>0.001609634947795496</v>
+        <v>0.004341880990843839</v>
       </c>
       <c r="CM21" t="n">
-        <v>0.001675666815128945</v>
+        <v>0.003897274473914378</v>
       </c>
       <c r="CN21" t="n">
-        <v>0.002169585075889954</v>
+        <v>0.004782743240215927</v>
       </c>
       <c r="CO21" t="n">
-        <v>0</v>
+        <v>0.00453831084710429</v>
       </c>
       <c r="CP21" t="n">
-        <v>0</v>
+        <v>0.004429280801624648</v>
       </c>
     </row>
     <row r="22">
@@ -6322,142 +6322,142 @@
         </is>
       </c>
       <c r="AW22" t="n">
-        <v>0.004418885605861385</v>
+        <v>0.006351674561493882</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.00708872655053441</v>
+        <v>0.008892041129906155</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.01529224320035165</v>
+        <v>0.01764825030463149</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.01529718331428903</v>
+        <v>0.01748959768303833</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.01600502775823017</v>
+        <v>0.01957162856050677</v>
       </c>
       <c r="BB22" t="n">
-        <v>0.004581870776812988</v>
+        <v>0.007167456530104917</v>
       </c>
       <c r="BC22" t="n">
-        <v>0.003778983972406521</v>
+        <v>0.006915730904246289</v>
       </c>
       <c r="BD22" t="n">
-        <v>0.005812208949613147</v>
+        <v>0.008833560643348282</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.005821918272507368</v>
+        <v>0.008760003087241544</v>
       </c>
       <c r="BF22" t="n">
-        <v>0.007033139662872366</v>
+        <v>0.008471615622744181</v>
       </c>
       <c r="BG22" t="n">
-        <v>0.00440830389360402</v>
+        <v>0.006428312311408654</v>
       </c>
       <c r="BH22" t="n">
-        <v>0.003209725380039286</v>
+        <v>0.005939118457574904</v>
       </c>
       <c r="BI22" t="n">
-        <v>0.004905577863116462</v>
+        <v>0.007705206549176547</v>
       </c>
       <c r="BJ22" t="n">
-        <v>0.006850368288233019</v>
+        <v>0.00979329560142485</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.006310802134367899</v>
+        <v>0.008130324734435567</v>
       </c>
       <c r="BL22" t="n">
-        <v>0.006813535263015899</v>
+        <v>0.01002852834600618</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.00477819821668121</v>
+        <v>0.007669631560054293</v>
       </c>
       <c r="BN22" t="n">
-        <v>0.005364694385970289</v>
+        <v>0.008026039902989987</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.052144623675358</v>
+        <v>1.055209029072829</v>
       </c>
       <c r="BP22" t="n">
-        <v>0.006324535995678833</v>
+        <v>0.008126301714073112</v>
       </c>
       <c r="BQ22" t="n">
-        <v>0.007502486840020981</v>
+        <v>0.01012151760361103</v>
       </c>
       <c r="BR22" t="n">
-        <v>0.006352684141580973</v>
+        <v>0.008838326956986851</v>
       </c>
       <c r="BS22" t="n">
-        <v>0.002960117509897792</v>
+        <v>0.005237427934227315</v>
       </c>
       <c r="BT22" t="n">
-        <v>0.006220483000529439</v>
+        <v>0.008517745276803114</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.01023673146506826</v>
+        <v>0.01346368961033393</v>
       </c>
       <c r="BV22" t="n">
-        <v>0.002026839434881237</v>
+        <v>0.005914627646663049</v>
       </c>
       <c r="BW22" t="n">
-        <v>0.002602451397188808</v>
+        <v>0.005596576945041343</v>
       </c>
       <c r="BX22" t="n">
-        <v>0.003775654796157492</v>
+        <v>0.006458777172849676</v>
       </c>
       <c r="BY22" t="n">
-        <v>0.0025173710932255</v>
+        <v>0.00527984453207341</v>
       </c>
       <c r="BZ22" t="n">
-        <v>0.003895153638735838</v>
+        <v>0.007011043359946176</v>
       </c>
       <c r="CA22" t="n">
-        <v>0.00290051451610594</v>
+        <v>0.00682680829531455</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.003299211528670828</v>
+        <v>0.007015273463774487</v>
       </c>
       <c r="CC22" t="n">
-        <v>0.007612557040846386</v>
+        <v>0.01108879360412787</v>
       </c>
       <c r="CD22" t="n">
-        <v>0.002327314704101355</v>
+        <v>0.003175178506474714</v>
       </c>
       <c r="CE22" t="n">
-        <v>0.002737659473931584</v>
+        <v>0.006602446787641157</v>
       </c>
       <c r="CF22" t="n">
-        <v>0.002004425126310488</v>
+        <v>0.005489139362715893</v>
       </c>
       <c r="CG22" t="n">
-        <v>0.001657294377575424</v>
+        <v>0.002624857053595872</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.003106031174222843</v>
+        <v>0.006737755870761927</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.004264820332348876</v>
+        <v>0.007905003841286068</v>
       </c>
       <c r="CJ22" t="n">
-        <v>0.003209496061037214</v>
+        <v>0.007620678264007784</v>
       </c>
       <c r="CK22" t="n">
-        <v>0.00170675553831636</v>
+        <v>0.006452196139962257</v>
       </c>
       <c r="CL22" t="n">
-        <v>0.003303454384696765</v>
+        <v>0.007405055736509982</v>
       </c>
       <c r="CM22" t="n">
-        <v>0.006341260048363628</v>
+        <v>0.009676299731066061</v>
       </c>
       <c r="CN22" t="n">
-        <v>0.00395138207053455</v>
+        <v>0.007874210721552753</v>
       </c>
       <c r="CO22" t="n">
-        <v>0</v>
+        <v>0.006812835159114616</v>
       </c>
       <c r="CP22" t="n">
-        <v>0</v>
+        <v>0.006649161106748298</v>
       </c>
     </row>
     <row r="23">
@@ -6612,142 +6612,142 @@
         </is>
       </c>
       <c r="AW23" t="n">
-        <v>0.002915181191105918</v>
+        <v>0.01248948971730948</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.003673571078506433</v>
+        <v>0.01260651230956601</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.003245120356353742</v>
+        <v>0.01491589219130607</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.002083718325256442</v>
+        <v>0.01294411336348165</v>
       </c>
       <c r="BA23" t="n">
-        <v>0.00161657371172569</v>
+        <v>0.01928417077207138</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.00299815371600425</v>
+        <v>0.01580617171032914</v>
       </c>
       <c r="BC23" t="n">
-        <v>0.002590006628593398</v>
+        <v>0.01812826951370416</v>
       </c>
       <c r="BD23" t="n">
-        <v>0.002871549263377275</v>
+        <v>0.01783818760104387</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.003093444676622587</v>
+        <v>0.01764761025711311</v>
       </c>
       <c r="BF23" t="n">
-        <v>0.002356672536636195</v>
+        <v>0.009482340658447571</v>
       </c>
       <c r="BG23" t="n">
-        <v>0.002149587502816363</v>
+        <v>0.01215594839453665</v>
       </c>
       <c r="BH23" t="n">
-        <v>0.001864303150103528</v>
+        <v>0.01538468846556013</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.004437673117670064</v>
+        <v>0.01830597918442196</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.003025300514691257</v>
+        <v>0.01760345400867648</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.002222723955944652</v>
+        <v>0.01123595361699016</v>
       </c>
       <c r="BL23" t="n">
-        <v>0.008150657863334585</v>
+        <v>0.02407652271084263</v>
       </c>
       <c r="BM23" t="n">
-        <v>0.002078562953363561</v>
+        <v>0.01640163471540544</v>
       </c>
       <c r="BN23" t="n">
-        <v>0.002733293496004315</v>
+        <v>0.01591659682589994</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.004889859024580316</v>
+        <v>0.02006976919493213</v>
       </c>
       <c r="BP23" t="n">
-        <v>1.147663297377429</v>
+        <v>1.156588566134565</v>
       </c>
       <c r="BQ23" t="n">
-        <v>0.01567196444506998</v>
+        <v>0.02864565642378053</v>
       </c>
       <c r="BR23" t="n">
-        <v>0.006484634491903738</v>
+        <v>0.018797572814158</v>
       </c>
       <c r="BS23" t="n">
-        <v>0.001186268794596324</v>
+        <v>0.01246720691716299</v>
       </c>
       <c r="BT23" t="n">
-        <v>0.003528683476440529</v>
+        <v>0.01490845555893115</v>
       </c>
       <c r="BU23" t="n">
-        <v>0.004005560040917156</v>
+        <v>0.0199906953004513</v>
       </c>
       <c r="BV23" t="n">
-        <v>0.003118126464426628</v>
+        <v>0.02237676498037124</v>
       </c>
       <c r="BW23" t="n">
-        <v>0.01057007847013286</v>
+        <v>0.02540184873547331</v>
       </c>
       <c r="BX23" t="n">
-        <v>0.005736401174020671</v>
+        <v>0.01902757886476081</v>
       </c>
       <c r="BY23" t="n">
-        <v>0.00450166157225158</v>
+        <v>0.01818591453835839</v>
       </c>
       <c r="BZ23" t="n">
-        <v>0.01457173644021399</v>
+        <v>0.03000668055946558</v>
       </c>
       <c r="CA23" t="n">
-        <v>0.01064959602910063</v>
+        <v>0.03009897662345289</v>
       </c>
       <c r="CB23" t="n">
-        <v>0.002228529182991906</v>
+        <v>0.02063650040275736</v>
       </c>
       <c r="CC23" t="n">
-        <v>0.002501160092040475</v>
+        <v>0.01972112674692802</v>
       </c>
       <c r="CD23" t="n">
-        <v>0.001116641230477262</v>
+        <v>0.005316639170483165</v>
       </c>
       <c r="CE23" t="n">
-        <v>0.002448484295812224</v>
+        <v>0.02159318502569818</v>
       </c>
       <c r="CF23" t="n">
-        <v>0.001763240996843688</v>
+        <v>0.01902520285138104</v>
       </c>
       <c r="CG23" t="n">
-        <v>0.001016341534663314</v>
+        <v>0.005809282611681943</v>
       </c>
       <c r="CH23" t="n">
-        <v>0.002757025389349853</v>
+        <v>0.02074722169379816</v>
       </c>
       <c r="CI23" t="n">
-        <v>0.003747335682885893</v>
+        <v>0.02177943375805197</v>
       </c>
       <c r="CJ23" t="n">
-        <v>0.003255002342092704</v>
+        <v>0.02510633756079883</v>
       </c>
       <c r="CK23" t="n">
-        <v>0.001416447135792645</v>
+        <v>0.02492357256742716</v>
       </c>
       <c r="CL23" t="n">
-        <v>0.002173019235413438</v>
+        <v>0.02249080751711565</v>
       </c>
       <c r="CM23" t="n">
-        <v>0.004679887853324475</v>
+        <v>0.02120041834180506</v>
       </c>
       <c r="CN23" t="n">
-        <v>0.004421871164182682</v>
+        <v>0.02385408681857545</v>
       </c>
       <c r="CO23" t="n">
-        <v>0</v>
+        <v>0.03374821941187311</v>
       </c>
       <c r="CP23" t="n">
-        <v>0</v>
+        <v>0.03293743980216849</v>
       </c>
     </row>
     <row r="24">
@@ -6902,142 +6902,142 @@
         </is>
       </c>
       <c r="AW24" t="n">
-        <v>0.002597231895425921</v>
+        <v>0.00502495681843045</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.01478929780448618</v>
+        <v>0.01705439339891209</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.00265444461966763</v>
+        <v>0.005613762629617739</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.002467730588980461</v>
+        <v>0.005221564104561646</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.001681923695678683</v>
+        <v>0.006161836328075385</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.004347459104788451</v>
+        <v>0.00759514476417702</v>
       </c>
       <c r="BC24" t="n">
-        <v>0.002818759903855779</v>
+        <v>0.006758744495237811</v>
       </c>
       <c r="BD24" t="n">
-        <v>0.003566027257878077</v>
+        <v>0.007361066952546859</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.00388607364850633</v>
+        <v>0.007576524025845706</v>
       </c>
       <c r="BF24" t="n">
-        <v>0.002911695985218559</v>
+        <v>0.004718527470232325</v>
       </c>
       <c r="BG24" t="n">
-        <v>0.00348843497765831</v>
+        <v>0.006025713952836666</v>
       </c>
       <c r="BH24" t="n">
-        <v>0.002879237842912073</v>
+        <v>0.006307556066533582</v>
       </c>
       <c r="BI24" t="n">
-        <v>0.003943436887818777</v>
+        <v>0.007459976195692828</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.004812478194875342</v>
+        <v>0.008509011106037662</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.002764029276695973</v>
+        <v>0.005049483335858243</v>
       </c>
       <c r="BL24" t="n">
-        <v>0.002408546514509999</v>
+        <v>0.006446814020187304</v>
       </c>
       <c r="BM24" t="n">
-        <v>0.003260611062006656</v>
+        <v>0.006892463764008478</v>
       </c>
       <c r="BN24" t="n">
-        <v>0.003415001363610368</v>
+        <v>0.00675784685202572</v>
       </c>
       <c r="BO24" t="n">
-        <v>0.00472311277104685</v>
+        <v>0.008572231080601261</v>
       </c>
       <c r="BP24" t="n">
-        <v>0.002981874255025236</v>
+        <v>0.00524502436627446</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.150610864011532</v>
+        <v>1.153900559060935</v>
       </c>
       <c r="BR24" t="n">
-        <v>0.003534239346501558</v>
+        <v>0.006656389333473753</v>
       </c>
       <c r="BS24" t="n">
-        <v>0.001384990321288017</v>
+        <v>0.004245459519671643</v>
       </c>
       <c r="BT24" t="n">
-        <v>0.002256800178445073</v>
+        <v>0.005142330368658024</v>
       </c>
       <c r="BU24" t="n">
-        <v>0.00193963137794019</v>
+        <v>0.005992927880863476</v>
       </c>
       <c r="BV24" t="n">
-        <v>0.003937345457041529</v>
+        <v>0.008820693072206905</v>
       </c>
       <c r="BW24" t="n">
-        <v>0.00821503170000043</v>
+        <v>0.0119758733552382</v>
       </c>
       <c r="BX24" t="n">
-        <v>0.02052037929659879</v>
+        <v>0.02389057812062671</v>
       </c>
       <c r="BY24" t="n">
-        <v>0.04239476842078356</v>
+        <v>0.04586463800850296</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0.01470617920583442</v>
+        <v>0.01861996560836512</v>
       </c>
       <c r="CA24" t="n">
-        <v>0.008186756815538127</v>
+        <v>0.01311847025225068</v>
       </c>
       <c r="CB24" t="n">
-        <v>0.004813188094883674</v>
+        <v>0.009480834890458072</v>
       </c>
       <c r="CC24" t="n">
-        <v>0.002796078572172169</v>
+        <v>0.007162487081670476</v>
       </c>
       <c r="CD24" t="n">
-        <v>0.001381924470866575</v>
+        <v>0.002446903696009965</v>
       </c>
       <c r="CE24" t="n">
-        <v>0.002341795430282279</v>
+        <v>0.007196252227679511</v>
       </c>
       <c r="CF24" t="n">
-        <v>0.002067876149491024</v>
+        <v>0.006444933239255713</v>
       </c>
       <c r="CG24" t="n">
-        <v>0.0009602602500238806</v>
+        <v>0.002175590054293748</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.002048488263585201</v>
+        <v>0.006610201291582993</v>
       </c>
       <c r="CI24" t="n">
-        <v>0.003275377199061722</v>
+        <v>0.007847715116868648</v>
       </c>
       <c r="CJ24" t="n">
-        <v>0.002844383882975153</v>
+        <v>0.008385152802860242</v>
       </c>
       <c r="CK24" t="n">
-        <v>0.001311950459319799</v>
+        <v>0.007272572484647599</v>
       </c>
       <c r="CL24" t="n">
-        <v>0.001733026807983801</v>
+        <v>0.006884939435075291</v>
       </c>
       <c r="CM24" t="n">
-        <v>0.01298483176044622</v>
+        <v>0.01717388661473385</v>
       </c>
       <c r="CN24" t="n">
-        <v>0.003816330119540398</v>
+        <v>0.00874369110067587</v>
       </c>
       <c r="CO24" t="n">
-        <v>0</v>
+        <v>0.008557421473205578</v>
       </c>
       <c r="CP24" t="n">
-        <v>0</v>
+        <v>0.008351834838916881</v>
       </c>
     </row>
     <row r="25">
@@ -7192,142 +7192,142 @@
         </is>
       </c>
       <c r="AW25" t="n">
-        <v>0.005836010791232385</v>
+        <v>0.01301420115869393</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.005459975149390669</v>
+        <v>0.01215731026475674</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.002811953901362771</v>
+        <v>0.01156193534777382</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.002347579547690431</v>
+        <v>0.01048999347104114</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.002160166898880289</v>
+        <v>0.01540617570334619</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.007901300947581682</v>
+        <v>0.01750391518771342</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.01848241857118134</v>
+        <v>0.03013199187078068</v>
       </c>
       <c r="BD25" t="n">
-        <v>0.0118024278256586</v>
+        <v>0.02302343442417051</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.01531833752566233</v>
+        <v>0.02623009902680786</v>
       </c>
       <c r="BF25" t="n">
-        <v>0.004737365859265714</v>
+        <v>0.01007972579405634</v>
       </c>
       <c r="BG25" t="n">
-        <v>0.007712467416729362</v>
+        <v>0.01521458239137305</v>
       </c>
       <c r="BH25" t="n">
-        <v>0.006784077141858279</v>
+        <v>0.01692077781012706</v>
       </c>
       <c r="BI25" t="n">
-        <v>0.01105824698804835</v>
+        <v>0.02145579588141376</v>
       </c>
       <c r="BJ25" t="n">
-        <v>0.01577561860775413</v>
+        <v>0.02670536467761414</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.006283680729470131</v>
+        <v>0.01304121085872847</v>
       </c>
       <c r="BL25" t="n">
-        <v>0.01395265211099615</v>
+        <v>0.02589282401260153</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.006891124066568444</v>
+        <v>0.01762962653631469</v>
       </c>
       <c r="BN25" t="n">
-        <v>0.005854847105069411</v>
+        <v>0.01573882574592739</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.00957908328321417</v>
+        <v>0.02095998715376845</v>
       </c>
       <c r="BP25" t="n">
-        <v>0.005088644162811065</v>
+        <v>0.01178022695901338</v>
       </c>
       <c r="BQ25" t="n">
-        <v>0.008212064462347434</v>
+        <v>0.01793889022079418</v>
       </c>
       <c r="BR25" t="n">
-        <v>1.028635240538054</v>
+        <v>1.037866676418573</v>
       </c>
       <c r="BS25" t="n">
-        <v>0.002941039770998002</v>
+        <v>0.01139874939521949</v>
       </c>
       <c r="BT25" t="n">
-        <v>0.05365030612962612</v>
+        <v>0.06218211499319869</v>
       </c>
       <c r="BU25" t="n">
-        <v>0.01564328373478123</v>
+        <v>0.02762789271500348</v>
       </c>
       <c r="BV25" t="n">
-        <v>0.00321760698662543</v>
+        <v>0.01765647461943961</v>
       </c>
       <c r="BW25" t="n">
-        <v>0.002589272895187426</v>
+        <v>0.01370916423352153</v>
       </c>
       <c r="BX25" t="n">
-        <v>0.00285310284258262</v>
+        <v>0.01281795862415431</v>
       </c>
       <c r="BY25" t="n">
-        <v>0.003147040423244198</v>
+        <v>0.01340659833892845</v>
       </c>
       <c r="BZ25" t="n">
-        <v>0.003175947501471448</v>
+        <v>0.01474805914753846</v>
       </c>
       <c r="CA25" t="n">
-        <v>0.002573834221747734</v>
+        <v>0.01715570779030633</v>
       </c>
       <c r="CB25" t="n">
-        <v>0.009736161236595074</v>
+        <v>0.02353725416488247</v>
       </c>
       <c r="CC25" t="n">
-        <v>0.00760080826617284</v>
+        <v>0.02051121306792162</v>
       </c>
       <c r="CD25" t="n">
-        <v>0.002092489085286909</v>
+        <v>0.005241372858333988</v>
       </c>
       <c r="CE25" t="n">
-        <v>0.002985352645181857</v>
+        <v>0.0173387971776084</v>
       </c>
       <c r="CF25" t="n">
-        <v>0.002316265336574934</v>
+        <v>0.01525815539251004</v>
       </c>
       <c r="CG25" t="n">
-        <v>0.00201324667144423</v>
+        <v>0.005606680429788773</v>
       </c>
       <c r="CH25" t="n">
-        <v>0.006382682541470916</v>
+        <v>0.01987055516098206</v>
       </c>
       <c r="CI25" t="n">
-        <v>0.003203282614715614</v>
+        <v>0.01672257044151016</v>
       </c>
       <c r="CJ25" t="n">
-        <v>0.01750582551918846</v>
+        <v>0.03388852757582309</v>
       </c>
       <c r="CK25" t="n">
-        <v>0.002181687388777007</v>
+        <v>0.01980579265739821</v>
       </c>
       <c r="CL25" t="n">
-        <v>0.01508065824171117</v>
+        <v>0.03031360709986425</v>
       </c>
       <c r="CM25" t="n">
-        <v>0.01865502122306226</v>
+        <v>0.03104103453078139</v>
       </c>
       <c r="CN25" t="n">
-        <v>0.009543184208285876</v>
+        <v>0.02411218862746015</v>
       </c>
       <c r="CO25" t="n">
-        <v>0</v>
+        <v>0.02530220776135198</v>
       </c>
       <c r="CP25" t="n">
-        <v>0</v>
+        <v>0.02469433823546532</v>
       </c>
     </row>
     <row r="26">
@@ -7482,142 +7482,142 @@
         </is>
       </c>
       <c r="AW26" t="n">
-        <v>0.03055602773331717</v>
+        <v>0.04469260810439266</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.006101619627066884</v>
+        <v>0.01929121356143335</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.01640431823358094</v>
+        <v>0.03363635160557297</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.0247607732401072</v>
+        <v>0.04079627563689259</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.01010295489754554</v>
+        <v>0.03618937201307892</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.01794978593706533</v>
+        <v>0.03686097678446848</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.01309496981645188</v>
+        <v>0.03603739970588922</v>
       </c>
       <c r="BD26" t="n">
-        <v>0.02854828928990126</v>
+        <v>0.05064670873880309</v>
       </c>
       <c r="BE26" t="n">
-        <v>0.04788649980948828</v>
+        <v>0.06937589832839394</v>
       </c>
       <c r="BF26" t="n">
-        <v>0.01428683269403007</v>
+        <v>0.02480796639532095</v>
       </c>
       <c r="BG26" t="n">
-        <v>0.02792849056476006</v>
+        <v>0.04270300139033515</v>
       </c>
       <c r="BH26" t="n">
-        <v>0.01211788335200728</v>
+        <v>0.03208089301863323</v>
       </c>
       <c r="BI26" t="n">
-        <v>0.02087706295825908</v>
+        <v>0.04135378175071797</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.03027029797151342</v>
+        <v>0.05179511492989429</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.02914058077346434</v>
+        <v>0.04244872152928086</v>
       </c>
       <c r="BL26" t="n">
-        <v>0.01460822983033292</v>
+        <v>0.0381229586255784</v>
       </c>
       <c r="BM26" t="n">
-        <v>0.008484283885407921</v>
+        <v>0.02963246963382296</v>
       </c>
       <c r="BN26" t="n">
-        <v>0.01020328144060459</v>
+        <v>0.02966858554787</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.01028301211447554</v>
+        <v>0.03269632995999679</v>
       </c>
       <c r="BP26" t="n">
-        <v>0.007898348181670123</v>
+        <v>0.02107661361706739</v>
       </c>
       <c r="BQ26" t="n">
-        <v>0.006181298576495423</v>
+        <v>0.02533710903159704</v>
       </c>
       <c r="BR26" t="n">
-        <v>0.01159084682686526</v>
+        <v>0.02977104665228938</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.003886539323539</v>
+        <v>1.020542978584331</v>
       </c>
       <c r="BT26" t="n">
-        <v>0.005738612372188804</v>
+        <v>0.02254098114987837</v>
       </c>
       <c r="BU26" t="n">
-        <v>0.007133347742322999</v>
+        <v>0.03073559000561063</v>
       </c>
       <c r="BV26" t="n">
-        <v>0.00955329948938388</v>
+        <v>0.03798890823052968</v>
       </c>
       <c r="BW26" t="n">
-        <v>0.008961296513314112</v>
+        <v>0.03086058164993505</v>
       </c>
       <c r="BX26" t="n">
-        <v>0.004713634669111993</v>
+        <v>0.02433821655271847</v>
       </c>
       <c r="BY26" t="n">
-        <v>0.005938400174290735</v>
+        <v>0.02614336237537868</v>
       </c>
       <c r="BZ26" t="n">
-        <v>0.007598361948406162</v>
+        <v>0.0303882404516613</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.007809202059751877</v>
+        <v>0.03652644374746254</v>
       </c>
       <c r="CB26" t="n">
-        <v>0.01290366531078993</v>
+        <v>0.04008325367526103</v>
       </c>
       <c r="CC26" t="n">
-        <v>0.01028917183404399</v>
+        <v>0.03571465733389177</v>
       </c>
       <c r="CD26" t="n">
-        <v>0.004615899602965402</v>
+        <v>0.01081724649655542</v>
       </c>
       <c r="CE26" t="n">
-        <v>0.005262562273049371</v>
+        <v>0.03352994051843538</v>
       </c>
       <c r="CF26" t="n">
-        <v>0.008431190621007617</v>
+        <v>0.03391868253243322</v>
       </c>
       <c r="CG26" t="n">
-        <v>0.006386164015775086</v>
+        <v>0.0134629985008624</v>
       </c>
       <c r="CH26" t="n">
-        <v>0.006536944128432708</v>
+        <v>0.03309968286337323</v>
       </c>
       <c r="CI26" t="n">
-        <v>0.006339773864791206</v>
+        <v>0.03296438106238059</v>
       </c>
       <c r="CJ26" t="n">
-        <v>0.01192009208834849</v>
+        <v>0.04418384833655442</v>
       </c>
       <c r="CK26" t="n">
-        <v>0.008737023127653834</v>
+        <v>0.04344557331148863</v>
       </c>
       <c r="CL26" t="n">
-        <v>0.009412973899135054</v>
+        <v>0.03941242986200552</v>
       </c>
       <c r="CM26" t="n">
-        <v>0.01601626044411708</v>
+        <v>0.04040902012843594</v>
       </c>
       <c r="CN26" t="n">
-        <v>0.01923421713652862</v>
+        <v>0.04792611458630941</v>
       </c>
       <c r="CO26" t="n">
-        <v>0</v>
+        <v>0.04982964720542686</v>
       </c>
       <c r="CP26" t="n">
-        <v>0</v>
+        <v>0.04863252147206977</v>
       </c>
     </row>
     <row r="27">
@@ -7772,142 +7772,142 @@
         </is>
       </c>
       <c r="AW27" t="n">
-        <v>0.002269569068536815</v>
+        <v>0.005753370757943962</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.00180509962121725</v>
+        <v>0.005055527123837135</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.004387903649994595</v>
+        <v>0.008634545015688538</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.001826208882542919</v>
+        <v>0.005777978608601727</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.001315341585469837</v>
+        <v>0.007744046522034404</v>
       </c>
       <c r="BB27" t="n">
-        <v>0.004120251332064267</v>
+        <v>0.008780702225668308</v>
       </c>
       <c r="BC27" t="n">
-        <v>0.004340105311300337</v>
+        <v>0.009994009856098407</v>
       </c>
       <c r="BD27" t="n">
-        <v>0.002923028041128166</v>
+        <v>0.008368935678510698</v>
       </c>
       <c r="BE27" t="n">
-        <v>0.006395112947323731</v>
+        <v>0.01169093420673425</v>
       </c>
       <c r="BF27" t="n">
-        <v>0.00353958407436178</v>
+        <v>0.006132399479566252</v>
       </c>
       <c r="BG27" t="n">
-        <v>0.009446702423780278</v>
+        <v>0.01308771491925034</v>
       </c>
       <c r="BH27" t="n">
-        <v>0.003037504930116384</v>
+        <v>0.007957164775473433</v>
       </c>
       <c r="BI27" t="n">
-        <v>0.005834687334290291</v>
+        <v>0.01088094503241394</v>
       </c>
       <c r="BJ27" t="n">
-        <v>0.004687210455716259</v>
+        <v>0.009991760192314398</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.002851586351385084</v>
+        <v>0.006131228388637869</v>
       </c>
       <c r="BL27" t="n">
-        <v>0.004634094832715576</v>
+        <v>0.01042903602446539</v>
       </c>
       <c r="BM27" t="n">
-        <v>0.002179191357098073</v>
+        <v>0.00739092455595367</v>
       </c>
       <c r="BN27" t="n">
-        <v>0.004507148234906048</v>
+        <v>0.009304154126972154</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.002833716954959758</v>
+        <v>0.008357227770574771</v>
       </c>
       <c r="BP27" t="n">
-        <v>0.002562919596199604</v>
+        <v>0.005810555317298682</v>
       </c>
       <c r="BQ27" t="n">
-        <v>0.003813965183825649</v>
+        <v>0.008534699836315659</v>
       </c>
       <c r="BR27" t="n">
-        <v>0.004669472499604255</v>
+        <v>0.009149778853972864</v>
       </c>
       <c r="BS27" t="n">
-        <v>0.001091783602275426</v>
+        <v>0.005196576254604839</v>
       </c>
       <c r="BT27" t="n">
-        <v>1.002797090633696</v>
+        <v>1.006937845978851</v>
       </c>
       <c r="BU27" t="n">
-        <v>0.00253027851478503</v>
+        <v>0.008346786419262259</v>
       </c>
       <c r="BV27" t="n">
-        <v>0.007839011722302393</v>
+        <v>0.01484664858859977</v>
       </c>
       <c r="BW27" t="n">
-        <v>0.004045134662234356</v>
+        <v>0.009441967881664822</v>
       </c>
       <c r="BX27" t="n">
-        <v>0.003171523091644481</v>
+        <v>0.008007781205374983</v>
       </c>
       <c r="BY27" t="n">
-        <v>0.005324276850137401</v>
+        <v>0.01030356318409276</v>
       </c>
       <c r="BZ27" t="n">
-        <v>0.005056131197604195</v>
+        <v>0.01067244116415543</v>
       </c>
       <c r="CA27" t="n">
-        <v>0.004019074083368171</v>
+        <v>0.01109611623080715</v>
       </c>
       <c r="CB27" t="n">
-        <v>0.005730492544593492</v>
+        <v>0.01242859727544302</v>
       </c>
       <c r="CC27" t="n">
-        <v>0.003070308838847597</v>
+        <v>0.009336134591135086</v>
       </c>
       <c r="CD27" t="n">
-        <v>0.001557782822427244</v>
+        <v>0.003086035215678771</v>
       </c>
       <c r="CE27" t="n">
-        <v>0.003009519227776774</v>
+        <v>0.009975697575114576</v>
       </c>
       <c r="CF27" t="n">
-        <v>0.00442450064223331</v>
+        <v>0.01070560717924657</v>
       </c>
       <c r="CG27" t="n">
-        <v>0.004518341526648207</v>
+        <v>0.006262348018150672</v>
       </c>
       <c r="CH27" t="n">
-        <v>0.002808250033346654</v>
+        <v>0.009354339091023492</v>
       </c>
       <c r="CI27" t="n">
-        <v>0.002722716319522832</v>
+        <v>0.00928405216595901</v>
       </c>
       <c r="CJ27" t="n">
-        <v>0.01394568656674808</v>
+        <v>0.0218967274531353</v>
       </c>
       <c r="CK27" t="n">
-        <v>0.003762676990530501</v>
+        <v>0.01231620992376542</v>
       </c>
       <c r="CL27" t="n">
-        <v>0.005047904865100613</v>
+        <v>0.01244093434050213</v>
       </c>
       <c r="CM27" t="n">
-        <v>0.006477631764188291</v>
+        <v>0.01248895382135335</v>
       </c>
       <c r="CN27" t="n">
-        <v>0.01117489048713591</v>
+        <v>0.01824568683137502</v>
       </c>
       <c r="CO27" t="n">
-        <v>0</v>
+        <v>0.01227995770971741</v>
       </c>
       <c r="CP27" t="n">
-        <v>0</v>
+        <v>0.01198493949860637</v>
       </c>
     </row>
     <row r="28">
@@ -8062,142 +8062,142 @@
         </is>
       </c>
       <c r="AW28" t="n">
-        <v>0.02260921901751531</v>
+        <v>0.03353322333918241</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.007211884664653651</v>
+        <v>0.0174041077736354</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.03064461342019879</v>
+        <v>0.04396062069250289</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.02303618587491912</v>
+        <v>0.03542757706603077</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.00608343606389599</v>
+        <v>0.02624164447262568</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.01425423162074783</v>
+        <v>0.02886780329948235</v>
       </c>
       <c r="BC28" t="n">
-        <v>0.01009131075195784</v>
+        <v>0.02782001151855566</v>
       </c>
       <c r="BD28" t="n">
-        <v>0.01465643554549915</v>
+        <v>0.03173292952248279</v>
       </c>
       <c r="BE28" t="n">
-        <v>0.01728362741100633</v>
+        <v>0.03388950210831775</v>
       </c>
       <c r="BF28" t="n">
-        <v>0.01719554261617829</v>
+        <v>0.02532572028325401</v>
       </c>
       <c r="BG28" t="n">
-        <v>0.0217733759755354</v>
+        <v>0.03319033933389677</v>
       </c>
       <c r="BH28" t="n">
-        <v>0.0138558321579368</v>
+        <v>0.02928219398996117</v>
       </c>
       <c r="BI28" t="n">
-        <v>0.01167881533432638</v>
+        <v>0.02750214450663913</v>
       </c>
       <c r="BJ28" t="n">
-        <v>0.01825533132057109</v>
+        <v>0.03488857552137897</v>
       </c>
       <c r="BK28" t="n">
-        <v>0.01311377402361065</v>
+        <v>0.02339760386886435</v>
       </c>
       <c r="BL28" t="n">
-        <v>0.009763035367744369</v>
+        <v>0.02793397856895001</v>
       </c>
       <c r="BM28" t="n">
-        <v>0.007887346040031683</v>
+        <v>0.02422954949001132</v>
       </c>
       <c r="BN28" t="n">
-        <v>0.01123136401557717</v>
+        <v>0.02627312522010491</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.0117168983073102</v>
+        <v>0.02903672917024929</v>
       </c>
       <c r="BP28" t="n">
-        <v>0.006347967111598428</v>
+        <v>0.01653143615358171</v>
       </c>
       <c r="BQ28" t="n">
-        <v>0.01101797946034281</v>
+        <v>0.02582058028060368</v>
       </c>
       <c r="BR28" t="n">
-        <v>0.01071075667977365</v>
+        <v>0.02475945701950051</v>
       </c>
       <c r="BS28" t="n">
-        <v>0.0525013225205563</v>
+        <v>0.06537254099718105</v>
       </c>
       <c r="BT28" t="n">
-        <v>0.03197337921845657</v>
+        <v>0.04495736433534386</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.007391675359862</v>
+        <v>1.025630244357265</v>
       </c>
       <c r="BV28" t="n">
-        <v>0.01507554606632245</v>
+        <v>0.0370490859623701</v>
       </c>
       <c r="BW28" t="n">
-        <v>0.0418474491716832</v>
+        <v>0.05877006264639206</v>
       </c>
       <c r="BX28" t="n">
-        <v>0.05523030947970957</v>
+        <v>0.07039515215595274</v>
       </c>
       <c r="BY28" t="n">
-        <v>0.01679450606713408</v>
+        <v>0.03240783606704076</v>
       </c>
       <c r="BZ28" t="n">
-        <v>0.06284020034232342</v>
+        <v>0.08045101743704397</v>
       </c>
       <c r="CA28" t="n">
-        <v>0.01292737639628636</v>
+        <v>0.03511854739155607</v>
       </c>
       <c r="CB28" t="n">
-        <v>0.01661132528049673</v>
+        <v>0.0376142788209523</v>
       </c>
       <c r="CC28" t="n">
-        <v>0.008928045703248563</v>
+        <v>0.02857552099006649</v>
       </c>
       <c r="CD28" t="n">
-        <v>0.006303117850038502</v>
+        <v>0.01109519192223368</v>
       </c>
       <c r="CE28" t="n">
-        <v>0.009654919202881728</v>
+        <v>0.03149845943744996</v>
       </c>
       <c r="CF28" t="n">
-        <v>0.0131332393689041</v>
+        <v>0.03282862994288957</v>
       </c>
       <c r="CG28" t="n">
-        <v>0.06304989443722059</v>
+        <v>0.06851849918246669</v>
       </c>
       <c r="CH28" t="n">
-        <v>0.009351015817128784</v>
+        <v>0.02987730047147961</v>
       </c>
       <c r="CI28" t="n">
-        <v>0.01013685792325174</v>
+        <v>0.03071095126510764</v>
       </c>
       <c r="CJ28" t="n">
-        <v>0.03115847783760898</v>
+        <v>0.05609020838609106</v>
       </c>
       <c r="CK28" t="n">
-        <v>0.02206497890740178</v>
+        <v>0.04888591737019952</v>
       </c>
       <c r="CL28" t="n">
-        <v>0.01374043425626149</v>
+        <v>0.03692243287147019</v>
       </c>
       <c r="CM28" t="n">
-        <v>0.0279610723543565</v>
+        <v>0.04681051155494966</v>
       </c>
       <c r="CN28" t="n">
-        <v>0.01564678995882054</v>
+        <v>0.03781837626264382</v>
       </c>
       <c r="CO28" t="n">
-        <v>0</v>
+        <v>0.03850572536856147</v>
       </c>
       <c r="CP28" t="n">
-        <v>0</v>
+        <v>0.03758064968961373</v>
       </c>
     </row>
     <row r="29">
@@ -8352,142 +8352,142 @@
         </is>
       </c>
       <c r="AW29" t="n">
-        <v>0.09576395874319876</v>
+        <v>0.1524552832336729</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.08651438410265064</v>
+        <v>0.1394080493316675</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.04665810417804778</v>
+        <v>0.1157629916316716</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.05111314680366325</v>
+        <v>0.1154196371911101</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.04733200973693264</v>
+        <v>0.1519452541476139</v>
       </c>
       <c r="BB29" t="n">
-        <v>0.1405775452296273</v>
+        <v>0.2164162861902782</v>
       </c>
       <c r="BC29" t="n">
-        <v>0.1370643015869943</v>
+        <v>0.2290693483041796</v>
       </c>
       <c r="BD29" t="n">
-        <v>0.08492794310735446</v>
+        <v>0.1735482908024447</v>
       </c>
       <c r="BE29" t="n">
-        <v>0.08808300420405513</v>
+        <v>0.1742610212747925</v>
       </c>
       <c r="BF29" t="n">
-        <v>0.04476838088980459</v>
+        <v>0.08696083401573458</v>
       </c>
       <c r="BG29" t="n">
-        <v>0.09297929945600154</v>
+        <v>0.1522288892022223</v>
       </c>
       <c r="BH29" t="n">
-        <v>0.1193172126131034</v>
+        <v>0.199374017661428</v>
       </c>
       <c r="BI29" t="n">
-        <v>0.09973178883201175</v>
+        <v>0.1818486996472091</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.09815877283614519</v>
+        <v>0.1844788269619927</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.05548696972780374</v>
+        <v>0.1088560382117613</v>
       </c>
       <c r="BL29" t="n">
-        <v>0.07281555344557671</v>
+        <v>0.1671156660219068</v>
       </c>
       <c r="BM29" t="n">
-        <v>0.06565086231063248</v>
+        <v>0.1504605283810277</v>
       </c>
       <c r="BN29" t="n">
-        <v>0.07092061671327692</v>
+        <v>0.1489814944138426</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.07708724326569094</v>
+        <v>0.1669704145514713</v>
       </c>
       <c r="BP29" t="n">
-        <v>0.0900636428596658</v>
+        <v>0.1429118778931053</v>
       </c>
       <c r="BQ29" t="n">
-        <v>0.05450943596200753</v>
+        <v>0.1313291644877375</v>
       </c>
       <c r="BR29" t="n">
-        <v>0.07555789743677838</v>
+        <v>0.1484651763225255</v>
       </c>
       <c r="BS29" t="n">
-        <v>0.02227339349212697</v>
+        <v>0.0890700004651608</v>
       </c>
       <c r="BT29" t="n">
-        <v>0.1172856610994282</v>
+        <v>0.184667482981444</v>
       </c>
       <c r="BU29" t="n">
-        <v>0.07762430588470977</v>
+        <v>0.1722753699842395</v>
       </c>
       <c r="BV29" t="n">
-        <v>1.032841095948476</v>
+        <v>1.146875203201658</v>
       </c>
       <c r="BW29" t="n">
-        <v>0.056099191097415</v>
+        <v>0.1439209589649677</v>
       </c>
       <c r="BX29" t="n">
-        <v>0.04528252847597285</v>
+        <v>0.1239821510402644</v>
       </c>
       <c r="BY29" t="n">
-        <v>0.05512394191300948</v>
+        <v>0.1361510388765233</v>
       </c>
       <c r="BZ29" t="n">
-        <v>0.0458916408092002</v>
+        <v>0.1372849172178303</v>
       </c>
       <c r="CA29" t="n">
-        <v>0.06027488318379982</v>
+        <v>0.1754384110140821</v>
       </c>
       <c r="CB29" t="n">
-        <v>0.1174807241602722</v>
+        <v>0.2264778665413557</v>
       </c>
       <c r="CC29" t="n">
-        <v>0.06169100703076247</v>
+        <v>0.1636537456113697</v>
       </c>
       <c r="CD29" t="n">
-        <v>0.03737117080363814</v>
+        <v>0.06224016739222113</v>
       </c>
       <c r="CE29" t="n">
-        <v>0.0456738068210503</v>
+        <v>0.1590332665021917</v>
       </c>
       <c r="CF29" t="n">
-        <v>0.03410973927009563</v>
+        <v>0.136321139514767</v>
       </c>
       <c r="CG29" t="n">
-        <v>0.01813007804218472</v>
+        <v>0.04651000512697942</v>
       </c>
       <c r="CH29" t="n">
-        <v>0.04355756172369845</v>
+        <v>0.150080978381049</v>
       </c>
       <c r="CI29" t="n">
-        <v>0.06365569993844249</v>
+        <v>0.1704272250491592</v>
       </c>
       <c r="CJ29" t="n">
-        <v>0.05829040074224343</v>
+        <v>0.1876763644432689</v>
       </c>
       <c r="CK29" t="n">
-        <v>0.02667870430348179</v>
+        <v>0.1658689207077044</v>
       </c>
       <c r="CL29" t="n">
-        <v>0.05437777362634118</v>
+        <v>0.1746833106010792</v>
       </c>
       <c r="CM29" t="n">
-        <v>0.0736888970658688</v>
+        <v>0.171510139416056</v>
       </c>
       <c r="CN29" t="n">
-        <v>0.06678812398474006</v>
+        <v>0.1818500149001016</v>
       </c>
       <c r="CO29" t="n">
-        <v>0</v>
+        <v>0.1998297059696754</v>
       </c>
       <c r="CP29" t="n">
-        <v>0</v>
+        <v>0.1950289237702897</v>
       </c>
     </row>
     <row r="30">
@@ -8642,142 +8642,142 @@
         </is>
       </c>
       <c r="AW30" t="n">
-        <v>0.05890453859050756</v>
+        <v>0.0714468920058151</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.03319040799777674</v>
+        <v>0.04489256963707251</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.02046957327581428</v>
+        <v>0.03575829565015289</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.02038940718631318</v>
+        <v>0.03461653517435237</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.02598186949991158</v>
+        <v>0.04912643871069416</v>
       </c>
       <c r="BB30" t="n">
-        <v>0.05708422079858265</v>
+        <v>0.07386273673994635</v>
       </c>
       <c r="BC30" t="n">
-        <v>0.03274721026071017</v>
+        <v>0.05310234964562117</v>
       </c>
       <c r="BD30" t="n">
-        <v>0.07632150801828039</v>
+        <v>0.09592781869401745</v>
       </c>
       <c r="BE30" t="n">
-        <v>0.04663823303999439</v>
+        <v>0.06570420400550282</v>
       </c>
       <c r="BF30" t="n">
-        <v>0.05895013027692626</v>
+        <v>0.06828476239780978</v>
       </c>
       <c r="BG30" t="n">
-        <v>0.03685799150830393</v>
+        <v>0.04996633393967456</v>
       </c>
       <c r="BH30" t="n">
-        <v>0.02717408239210365</v>
+        <v>0.04488580021208834</v>
       </c>
       <c r="BI30" t="n">
-        <v>0.03522089091758274</v>
+        <v>0.05338838525775391</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.05526885837476509</v>
+        <v>0.07436625353011689</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.04159324625108857</v>
+        <v>0.05340058581120102</v>
       </c>
       <c r="BL30" t="n">
-        <v>0.03255268790527276</v>
+        <v>0.05341558623523428</v>
       </c>
       <c r="BM30" t="n">
-        <v>0.01846777526208109</v>
+        <v>0.03723101310225276</v>
       </c>
       <c r="BN30" t="n">
-        <v>0.04002677346933803</v>
+        <v>0.05729691356271525</v>
       </c>
       <c r="BO30" t="n">
-        <v>0.03025217004693278</v>
+        <v>0.05013786702944569</v>
       </c>
       <c r="BP30" t="n">
-        <v>0.03777080467386004</v>
+        <v>0.04946291536490614</v>
       </c>
       <c r="BQ30" t="n">
-        <v>0.01535767247373169</v>
+        <v>0.03235322149463322</v>
       </c>
       <c r="BR30" t="n">
-        <v>0.03102589995375344</v>
+        <v>0.04715586104660253</v>
       </c>
       <c r="BS30" t="n">
-        <v>0.0126203399514852</v>
+        <v>0.02739837978613328</v>
       </c>
       <c r="BT30" t="n">
-        <v>0.01179809015908873</v>
+        <v>0.02670560257668189</v>
       </c>
       <c r="BU30" t="n">
-        <v>0.02736565891727097</v>
+        <v>0.04830620154422457</v>
       </c>
       <c r="BV30" t="n">
-        <v>0.02256234023142283</v>
+        <v>0.04779117528552056</v>
       </c>
       <c r="BW30" t="n">
-        <v>1.166357592315384</v>
+        <v>1.185787225686131</v>
       </c>
       <c r="BX30" t="n">
-        <v>0.05258723319086807</v>
+        <v>0.0699986888011267</v>
       </c>
       <c r="BY30" t="n">
-        <v>0.04028279451138988</v>
+        <v>0.05820917911197455</v>
       </c>
       <c r="BZ30" t="n">
-        <v>0.1291394606986156</v>
+        <v>0.1493592524004754</v>
       </c>
       <c r="CA30" t="n">
-        <v>0.1214099090886318</v>
+        <v>0.1468886164496446</v>
       </c>
       <c r="CB30" t="n">
-        <v>0.02022777582906749</v>
+        <v>0.0443422359036748</v>
       </c>
       <c r="CC30" t="n">
-        <v>0.01363064792293023</v>
+        <v>0.03618882087028265</v>
       </c>
       <c r="CD30" t="n">
-        <v>0.0071767068771652</v>
+        <v>0.01267870823454215</v>
       </c>
       <c r="CE30" t="n">
-        <v>0.008959977382557436</v>
+        <v>0.03403955382688777</v>
       </c>
       <c r="CF30" t="n">
-        <v>0.00889353385297453</v>
+        <v>0.03150672055242327</v>
       </c>
       <c r="CG30" t="n">
-        <v>0.005440959197231273</v>
+        <v>0.01171971663670448</v>
       </c>
       <c r="CH30" t="n">
-        <v>0.01105204769197271</v>
+        <v>0.0346192222240662</v>
       </c>
       <c r="CI30" t="n">
-        <v>0.01247877766352752</v>
+        <v>0.03610084355572616</v>
       </c>
       <c r="CJ30" t="n">
-        <v>0.01332722319640819</v>
+        <v>0.04195249343490998</v>
       </c>
       <c r="CK30" t="n">
-        <v>0.03708255085461456</v>
+        <v>0.06787690787106142</v>
       </c>
       <c r="CL30" t="n">
-        <v>0.008134358997401012</v>
+        <v>0.03475068126747</v>
       </c>
       <c r="CM30" t="n">
-        <v>0.01547001785040925</v>
+        <v>0.03711192874431783</v>
       </c>
       <c r="CN30" t="n">
-        <v>0.01622425445095564</v>
+        <v>0.04168047572404519</v>
       </c>
       <c r="CO30" t="n">
-        <v>0</v>
+        <v>0.04421020002045999</v>
       </c>
       <c r="CP30" t="n">
-        <v>0</v>
+        <v>0.04314807794877104</v>
       </c>
     </row>
     <row r="31">
@@ -8932,142 +8932,142 @@
         </is>
       </c>
       <c r="AW31" t="n">
-        <v>0.001001796508020074</v>
+        <v>0.00146638506296186</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.000827160729858119</v>
+        <v>0.001260627256089178</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.0005265175711574837</v>
+        <v>0.001092835964492756</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.0002505480437668245</v>
+        <v>0.0007775433064635336</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.0005522595363531882</v>
+        <v>0.001409570888404894</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.001335954713041099</v>
+        <v>0.001957457410114858</v>
       </c>
       <c r="BC31" t="n">
-        <v>0.001492068243416815</v>
+        <v>0.002246054714642602</v>
       </c>
       <c r="BD31" t="n">
-        <v>0.001264324670307939</v>
+        <v>0.001990573344935726</v>
       </c>
       <c r="BE31" t="n">
-        <v>0.0005959149081381651</v>
+        <v>0.0013021485475616</v>
       </c>
       <c r="BF31" t="n">
-        <v>0.001554914810027368</v>
+        <v>0.00190068430833074</v>
       </c>
       <c r="BG31" t="n">
-        <v>0.001458777002047842</v>
+        <v>0.001944330682941568</v>
       </c>
       <c r="BH31" t="n">
-        <v>0.001060412275109379</v>
+        <v>0.001716482241809611</v>
       </c>
       <c r="BI31" t="n">
-        <v>0.001567301391743384</v>
+        <v>0.00224025403969795</v>
       </c>
       <c r="BJ31" t="n">
-        <v>0.001337969563296534</v>
+        <v>0.002045367204280612</v>
       </c>
       <c r="BK31" t="n">
-        <v>0.001771065220860093</v>
+        <v>0.002208427703186949</v>
       </c>
       <c r="BL31" t="n">
-        <v>0.001315619261539684</v>
+        <v>0.002088413925034387</v>
       </c>
       <c r="BM31" t="n">
-        <v>0.001207790660711757</v>
+        <v>0.001902810587638338</v>
       </c>
       <c r="BN31" t="n">
-        <v>0.001399777138710361</v>
+        <v>0.002039490369867752</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.001314781661128319</v>
+        <v>0.002051379245265951</v>
       </c>
       <c r="BP31" t="n">
-        <v>0.002002961250057294</v>
+        <v>0.002436055473310715</v>
       </c>
       <c r="BQ31" t="n">
-        <v>0.001168190236394834</v>
+        <v>0.00179773218108491</v>
       </c>
       <c r="BR31" t="n">
-        <v>0.0009556340912463829</v>
+        <v>0.001553113293693991</v>
       </c>
       <c r="BS31" t="n">
-        <v>0.0002886599323994048</v>
+        <v>0.0008360618389085872</v>
       </c>
       <c r="BT31" t="n">
-        <v>0.0002821512066423354</v>
+        <v>0.000834348981855203</v>
       </c>
       <c r="BU31" t="n">
-        <v>0.0005559426002093308</v>
+        <v>0.001331613330941542</v>
       </c>
       <c r="BV31" t="n">
-        <v>0.0003044766929035959</v>
+        <v>0.001238992539534325</v>
       </c>
       <c r="BW31" t="n">
-        <v>0.0008020254735900606</v>
+        <v>0.001521729742148386</v>
       </c>
       <c r="BX31" t="n">
-        <v>1.001775699929404</v>
+        <v>1.00242064771022</v>
       </c>
       <c r="BY31" t="n">
-        <v>0.001615006891651467</v>
+        <v>0.002279028454522736</v>
       </c>
       <c r="BZ31" t="n">
-        <v>0.0003916479759211696</v>
+        <v>0.001140620955467896</v>
       </c>
       <c r="CA31" t="n">
-        <v>0.000523820467943211</v>
+        <v>0.001467591978973251</v>
       </c>
       <c r="CB31" t="n">
-        <v>0.0006709317076397385</v>
+        <v>0.001564169347203453</v>
       </c>
       <c r="CC31" t="n">
-        <v>0.0003810876191250875</v>
+        <v>0.001216677928591771</v>
       </c>
       <c r="CD31" t="n">
-        <v>0.0004600923578218126</v>
+        <v>0.0006638951670132503</v>
       </c>
       <c r="CE31" t="n">
-        <v>0.000199087643757279</v>
+        <v>0.001128074716040139</v>
       </c>
       <c r="CF31" t="n">
-        <v>0.0001628133285940664</v>
+        <v>0.001000441434217663</v>
       </c>
       <c r="CG31" t="n">
-        <v>0.0001017698841787795</v>
+        <v>0.0003343449639141897</v>
       </c>
       <c r="CH31" t="n">
-        <v>0.0001935618934655664</v>
+        <v>0.00106652721324066</v>
       </c>
       <c r="CI31" t="n">
-        <v>0.0002447608575098854</v>
+        <v>0.001119759439849476</v>
       </c>
       <c r="CJ31" t="n">
-        <v>0.0003160249089003488</v>
+        <v>0.001376350072333607</v>
       </c>
       <c r="CK31" t="n">
-        <v>0.0001605522967404173</v>
+        <v>0.001301223855968817</v>
       </c>
       <c r="CL31" t="n">
-        <v>0.0003063817599338872</v>
+        <v>0.001292292321680964</v>
       </c>
       <c r="CM31" t="n">
-        <v>0.0003804605411852195</v>
+        <v>0.001182111058871045</v>
       </c>
       <c r="CN31" t="n">
-        <v>0.0003584583817474707</v>
+        <v>0.001301396972611044</v>
       </c>
       <c r="CO31" t="n">
-        <v>0</v>
+        <v>0.001637615546387406</v>
       </c>
       <c r="CP31" t="n">
-        <v>0</v>
+        <v>0.00159827286944964</v>
       </c>
     </row>
     <row r="32">
@@ -9222,142 +9222,142 @@
         </is>
       </c>
       <c r="AW32" t="n">
-        <v>0.003309479372081914</v>
+        <v>0.005360364461554501</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.003593931693062925</v>
+        <v>0.005507431339097359</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.002582245923364001</v>
+        <v>0.005082208387852421</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.002333137666645552</v>
+        <v>0.004659511648507413</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.002404693661628633</v>
+        <v>0.006189218808139701</v>
       </c>
       <c r="BB32" t="n">
-        <v>0.004413744768734718</v>
+        <v>0.007157313461801821</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.004384265234939792</v>
+        <v>0.007712671832676103</v>
       </c>
       <c r="BD32" t="n">
-        <v>0.004213132543242337</v>
+        <v>0.007419093090914436</v>
       </c>
       <c r="BE32" t="n">
-        <v>0.003867652794605725</v>
+        <v>0.006985258739416337</v>
       </c>
       <c r="BF32" t="n">
-        <v>0.003990377346727736</v>
+        <v>0.00551674621854305</v>
       </c>
       <c r="BG32" t="n">
-        <v>0.004104402366920262</v>
+        <v>0.006247836150837414</v>
       </c>
       <c r="BH32" t="n">
-        <v>0.003827809720663578</v>
+        <v>0.006723972568508338</v>
       </c>
       <c r="BI32" t="n">
-        <v>0.004394889977506099</v>
+        <v>0.007365579928712604</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.004380843143310597</v>
+        <v>0.00750358747007111</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.004245141746748554</v>
+        <v>0.006175839746425411</v>
       </c>
       <c r="BL32" t="n">
-        <v>0.003944032297998508</v>
+        <v>0.007355465997186094</v>
       </c>
       <c r="BM32" t="n">
-        <v>0.00424138053176588</v>
+        <v>0.007309484534454147</v>
       </c>
       <c r="BN32" t="n">
-        <v>0.00445903532553794</v>
+        <v>0.00728299281085184</v>
       </c>
       <c r="BO32" t="n">
-        <v>0.004299437551955041</v>
+        <v>0.007551082445442978</v>
       </c>
       <c r="BP32" t="n">
-        <v>0.004233992079183552</v>
+        <v>0.006145848226648164</v>
       </c>
       <c r="BQ32" t="n">
-        <v>0.003250284300042276</v>
+        <v>0.006029341540753325</v>
       </c>
       <c r="BR32" t="n">
-        <v>0.004636683220375894</v>
+        <v>0.00727420232095579</v>
       </c>
       <c r="BS32" t="n">
-        <v>0.001430149793079606</v>
+        <v>0.003846607099371237</v>
       </c>
       <c r="BT32" t="n">
-        <v>0.003858350416670095</v>
+        <v>0.006295978661227068</v>
       </c>
       <c r="BU32" t="n">
-        <v>0.003177832185511645</v>
+        <v>0.006601962029171547</v>
       </c>
       <c r="BV32" t="n">
-        <v>0.002321481181237425</v>
+        <v>0.00644681874141681</v>
       </c>
       <c r="BW32" t="n">
-        <v>0.003877558832116568</v>
+        <v>0.007054629677955623</v>
       </c>
       <c r="BX32" t="n">
-        <v>0.008867977957148308</v>
+        <v>0.01171504289900457</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.009446094460142</v>
+        <v>1.012377358926077</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0.003112433287361101</v>
+        <v>0.006418708269452967</v>
       </c>
       <c r="CA32" t="n">
-        <v>0.01084218373674831</v>
+        <v>0.01500837960888522</v>
       </c>
       <c r="CB32" t="n">
-        <v>0.002849877084888932</v>
+        <v>0.006792995650447347</v>
       </c>
       <c r="CC32" t="n">
-        <v>0.003801606297631768</v>
+        <v>0.007490245822571718</v>
       </c>
       <c r="CD32" t="n">
-        <v>0.002863826622036218</v>
+        <v>0.003763496099722167</v>
       </c>
       <c r="CE32" t="n">
-        <v>0.003729237418855436</v>
+        <v>0.00783016869361842</v>
       </c>
       <c r="CF32" t="n">
-        <v>0.002966230380876864</v>
+        <v>0.00666386557673712</v>
       </c>
       <c r="CG32" t="n">
-        <v>0.001532328839356385</v>
+        <v>0.002559010960856383</v>
       </c>
       <c r="CH32" t="n">
-        <v>0.005261339089889125</v>
+        <v>0.009114967292541994</v>
       </c>
       <c r="CI32" t="n">
-        <v>0.003961355635593525</v>
+        <v>0.007823959496023915</v>
       </c>
       <c r="CJ32" t="n">
-        <v>0.003077314028690898</v>
+        <v>0.007758025691831929</v>
       </c>
       <c r="CK32" t="n">
-        <v>0.001943488706934583</v>
+        <v>0.006978882428805548</v>
       </c>
       <c r="CL32" t="n">
-        <v>0.00217770078672301</v>
+        <v>0.006529915771644418</v>
       </c>
       <c r="CM32" t="n">
-        <v>0.004377411056838542</v>
+        <v>0.007916226372458727</v>
       </c>
       <c r="CN32" t="n">
-        <v>0.003810959350884199</v>
+        <v>0.00797347837060631</v>
       </c>
       <c r="CO32" t="n">
-        <v>0</v>
+        <v>0.007229109005483947</v>
       </c>
       <c r="CP32" t="n">
-        <v>0</v>
+        <v>0.007055434237448144</v>
       </c>
     </row>
     <row r="33">
@@ -9512,142 +9512,142 @@
         </is>
       </c>
       <c r="AW33" t="n">
-        <v>0.01372441856078584</v>
+        <v>0.01909530804740648</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.02547080993966361</v>
+        <v>0.03048191230921742</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.01049247535666555</v>
+        <v>0.01703941559548703</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.01038652470390921</v>
+        <v>0.0164788687485689</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.005953570545701893</v>
+        <v>0.01586454333768552</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.02792931963699271</v>
+        <v>0.0351142196223961</v>
       </c>
       <c r="BC33" t="n">
-        <v>0.01607135611086615</v>
+        <v>0.02478783861626966</v>
       </c>
       <c r="BD33" t="n">
-        <v>0.02629462971421103</v>
+        <v>0.03469044861620552</v>
       </c>
       <c r="BE33" t="n">
-        <v>0.02167151693517369</v>
+        <v>0.02983595144121193</v>
       </c>
       <c r="BF33" t="n">
-        <v>0.0186560193634517</v>
+        <v>0.02265329769387541</v>
       </c>
       <c r="BG33" t="n">
-        <v>0.02301174329611222</v>
+        <v>0.02862500073037863</v>
       </c>
       <c r="BH33" t="n">
-        <v>0.01577538177880351</v>
+        <v>0.02335989768897129</v>
       </c>
       <c r="BI33" t="n">
-        <v>0.02601494533770161</v>
+        <v>0.03379463397498537</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0.02890544241473219</v>
+        <v>0.03708333339462878</v>
       </c>
       <c r="BK33" t="n">
-        <v>0.01513143644665479</v>
+        <v>0.02018757812983929</v>
       </c>
       <c r="BL33" t="n">
-        <v>0.01437983032077021</v>
+        <v>0.0233137454793137</v>
       </c>
       <c r="BM33" t="n">
-        <v>0.01554096939920771</v>
+        <v>0.02357576745614555</v>
       </c>
       <c r="BN33" t="n">
-        <v>0.02046788546808403</v>
+        <v>0.02786330886181328</v>
       </c>
       <c r="BO33" t="n">
-        <v>0.01850623652324163</v>
+        <v>0.02702169429428097</v>
       </c>
       <c r="BP33" t="n">
-        <v>0.01139857320569152</v>
+        <v>0.01640537155585622</v>
       </c>
       <c r="BQ33" t="n">
-        <v>0.01396313934398689</v>
+        <v>0.02124097728501476</v>
       </c>
       <c r="BR33" t="n">
-        <v>0.01828690608005699</v>
+        <v>0.02519408175790475</v>
       </c>
       <c r="BS33" t="n">
-        <v>0.003584662654240395</v>
+        <v>0.009912918297547523</v>
       </c>
       <c r="BT33" t="n">
-        <v>0.0110500985503236</v>
+        <v>0.01743379697310914</v>
       </c>
       <c r="BU33" t="n">
-        <v>0.008436308826008649</v>
+        <v>0.01740347284340678</v>
       </c>
       <c r="BV33" t="n">
-        <v>0.02059814705175046</v>
+        <v>0.0314016446462581</v>
       </c>
       <c r="BW33" t="n">
-        <v>0.05921718996373585</v>
+        <v>0.0675373520692364</v>
       </c>
       <c r="BX33" t="n">
-        <v>0.216246028031086</v>
+        <v>0.2237019655882089</v>
       </c>
       <c r="BY33" t="n">
-        <v>0.1422015941087003</v>
+        <v>0.149878034677413</v>
       </c>
       <c r="BZ33" t="n">
-        <v>1.018232585853704</v>
+        <v>1.0268911097429</v>
       </c>
       <c r="CA33" t="n">
-        <v>0.02863601628700369</v>
+        <v>0.03954651425869492</v>
       </c>
       <c r="CB33" t="n">
-        <v>0.009269294879764531</v>
+        <v>0.01959559456226042</v>
       </c>
       <c r="CC33" t="n">
-        <v>0.009102718394234675</v>
+        <v>0.01876258444237492</v>
       </c>
       <c r="CD33" t="n">
-        <v>0.003733096577014202</v>
+        <v>0.006089164873546391</v>
       </c>
       <c r="CE33" t="n">
-        <v>0.005958278714796765</v>
+        <v>0.01669786075283404</v>
       </c>
       <c r="CF33" t="n">
-        <v>0.00501814687121983</v>
+        <v>0.01470157092103407</v>
       </c>
       <c r="CG33" t="n">
-        <v>0.002687277728218325</v>
+        <v>0.005375968694265454</v>
       </c>
       <c r="CH33" t="n">
-        <v>0.007415874220243223</v>
+        <v>0.01750781516087178</v>
       </c>
       <c r="CI33" t="n">
-        <v>0.00760757254735123</v>
+        <v>0.01772301907892696</v>
       </c>
       <c r="CJ33" t="n">
-        <v>0.01119713701987761</v>
+        <v>0.0234550568762903</v>
       </c>
       <c r="CK33" t="n">
-        <v>0.004892646145255457</v>
+        <v>0.01807941284447954</v>
       </c>
       <c r="CL33" t="n">
-        <v>0.004230894051713474</v>
+        <v>0.01562854174344176</v>
       </c>
       <c r="CM33" t="n">
-        <v>0.009968049121346497</v>
+        <v>0.01923555322058608</v>
       </c>
       <c r="CN33" t="n">
-        <v>0.008059702232923795</v>
+        <v>0.01896057120683262</v>
       </c>
       <c r="CO33" t="n">
-        <v>0</v>
+        <v>0.01893170209998119</v>
       </c>
       <c r="CP33" t="n">
-        <v>0</v>
+        <v>0.01847687994025958</v>
       </c>
     </row>
     <row r="34">
@@ -9802,142 +9802,142 @@
         </is>
       </c>
       <c r="AW34" t="n">
-        <v>0.002386445609673707</v>
+        <v>0.005101789474051041</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.002180059817180131</v>
+        <v>0.004713507229723355</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.003053099934211401</v>
+        <v>0.006363016113312377</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.002256707830498366</v>
+        <v>0.00533679522804249</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.001971458485623171</v>
+        <v>0.006982118121752878</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.00460117348933995</v>
+        <v>0.008233620989913126</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.007819148619190159</v>
+        <v>0.01222591352264973</v>
       </c>
       <c r="BD34" t="n">
-        <v>0.003704712235164089</v>
+        <v>0.00794936023969754</v>
       </c>
       <c r="BE34" t="n">
-        <v>0.005379940978710703</v>
+        <v>0.009507608695074462</v>
       </c>
       <c r="BF34" t="n">
-        <v>0.002063890587963087</v>
+        <v>0.00408478213968143</v>
       </c>
       <c r="BG34" t="n">
-        <v>0.005003415593074253</v>
+        <v>0.007841292665628944</v>
       </c>
       <c r="BH34" t="n">
-        <v>0.003853091380060701</v>
+        <v>0.00768757145868627</v>
       </c>
       <c r="BI34" t="n">
-        <v>0.004550923642340687</v>
+        <v>0.008484076588540309</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0.004903206238930953</v>
+        <v>0.009037677102858714</v>
       </c>
       <c r="BK34" t="n">
-        <v>0.00206369001903828</v>
+        <v>0.004619907817050712</v>
       </c>
       <c r="BL34" t="n">
-        <v>0.004636490300337049</v>
+        <v>0.009153181952818291</v>
       </c>
       <c r="BM34" t="n">
-        <v>0.003787375282714301</v>
+        <v>0.007849503103397586</v>
       </c>
       <c r="BN34" t="n">
-        <v>0.004257092298471781</v>
+        <v>0.00799597346269219</v>
       </c>
       <c r="BO34" t="n">
-        <v>0.004513100531309402</v>
+        <v>0.008818233986122777</v>
       </c>
       <c r="BP34" t="n">
-        <v>0.002158525017596756</v>
+        <v>0.004689796460466891</v>
       </c>
       <c r="BQ34" t="n">
-        <v>0.00182330311892583</v>
+        <v>0.00550273697216952</v>
       </c>
       <c r="BR34" t="n">
-        <v>0.006368858789645383</v>
+        <v>0.009860898077316733</v>
       </c>
       <c r="BS34" t="n">
-        <v>0.002328508443793744</v>
+        <v>0.005527864933267341</v>
       </c>
       <c r="BT34" t="n">
-        <v>0.004764788051630808</v>
+        <v>0.007992174574389541</v>
       </c>
       <c r="BU34" t="n">
-        <v>0.003482476426962297</v>
+        <v>0.008015977601425592</v>
       </c>
       <c r="BV34" t="n">
-        <v>0.0105812697387168</v>
+        <v>0.01604316035853651</v>
       </c>
       <c r="BW34" t="n">
-        <v>0.002962655673877896</v>
+        <v>0.007169054107521825</v>
       </c>
       <c r="BX34" t="n">
-        <v>0.00440667711649834</v>
+        <v>0.008176152237769654</v>
       </c>
       <c r="BY34" t="n">
-        <v>0.004681225473538795</v>
+        <v>0.008562179615387329</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0.006637329496438697</v>
+        <v>0.01101479244287621</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.015506710497088</v>
+        <v>1.021022696964233</v>
       </c>
       <c r="CB34" t="n">
-        <v>0.003246416232270872</v>
+        <v>0.008467051390457538</v>
       </c>
       <c r="CC34" t="n">
-        <v>0.007958684199320597</v>
+        <v>0.01284239258130564</v>
       </c>
       <c r="CD34" t="n">
-        <v>0.006388308142586574</v>
+        <v>0.007579458250772464</v>
       </c>
       <c r="CE34" t="n">
-        <v>0.003494624428639324</v>
+        <v>0.00892420145970761</v>
       </c>
       <c r="CF34" t="n">
-        <v>0.01150035340493179</v>
+        <v>0.01639597193242659</v>
       </c>
       <c r="CG34" t="n">
-        <v>0.004171769737303659</v>
+        <v>0.005531082852207546</v>
       </c>
       <c r="CH34" t="n">
-        <v>0.00462294974286676</v>
+        <v>0.009725100882088245</v>
       </c>
       <c r="CI34" t="n">
-        <v>0.007740180367746637</v>
+        <v>0.01285421515535</v>
       </c>
       <c r="CJ34" t="n">
-        <v>0.004099646816442641</v>
+        <v>0.01029684516786169</v>
       </c>
       <c r="CK34" t="n">
-        <v>0.002282305437919932</v>
+        <v>0.008949097993773282</v>
       </c>
       <c r="CL34" t="n">
-        <v>0.003948687035192516</v>
+        <v>0.009710960268548818</v>
       </c>
       <c r="CM34" t="n">
-        <v>0.005762209840862523</v>
+        <v>0.01044755301477234</v>
       </c>
       <c r="CN34" t="n">
-        <v>0.007825032525331474</v>
+        <v>0.01333615089006785</v>
       </c>
       <c r="CO34" t="n">
-        <v>0</v>
+        <v>0.009571241647675031</v>
       </c>
       <c r="CP34" t="n">
-        <v>0</v>
+        <v>0.009341298625414119</v>
       </c>
     </row>
     <row r="35">
@@ -10092,142 +10092,142 @@
         </is>
       </c>
       <c r="AW35" t="n">
-        <v>0.004287459077421066</v>
+        <v>0.03190532152960161</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.005724479646324498</v>
+        <v>0.03149226658755455</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.005761814238310166</v>
+        <v>0.03942709360196821</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.004084838003832464</v>
+        <v>0.03541252036555612</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.005091261709813505</v>
+        <v>0.05605486541422188</v>
       </c>
       <c r="BB35" t="n">
-        <v>0.00916304603815608</v>
+        <v>0.04610880335151271</v>
       </c>
       <c r="BC35" t="n">
-        <v>0.007933044680613177</v>
+        <v>0.05275441281726048</v>
       </c>
       <c r="BD35" t="n">
-        <v>0.00557441958059414</v>
+        <v>0.04874689076740994</v>
       </c>
       <c r="BE35" t="n">
-        <v>0.005402759000697561</v>
+        <v>0.04738541936809144</v>
       </c>
       <c r="BF35" t="n">
-        <v>0.003559463930894507</v>
+        <v>0.02411402633396221</v>
       </c>
       <c r="BG35" t="n">
-        <v>0.005557956439014546</v>
+        <v>0.03442210866453203</v>
       </c>
       <c r="BH35" t="n">
-        <v>0.009985795522027474</v>
+        <v>0.04898643362772527</v>
       </c>
       <c r="BI35" t="n">
-        <v>0.005685210019911137</v>
+        <v>0.04568945349588028</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0.006697224298003745</v>
+        <v>0.04874907972983475</v>
       </c>
       <c r="BK35" t="n">
-        <v>0.002966725952764766</v>
+        <v>0.02896611132324789</v>
       </c>
       <c r="BL35" t="n">
-        <v>0.005573146459077732</v>
+        <v>0.05151258360868675</v>
       </c>
       <c r="BM35" t="n">
-        <v>0.007769507791378707</v>
+        <v>0.04908555946593631</v>
       </c>
       <c r="BN35" t="n">
-        <v>0.007044788404483839</v>
+        <v>0.04507308643080649</v>
       </c>
       <c r="BO35" t="n">
-        <v>0.006972640466554277</v>
+        <v>0.05076031139587937</v>
       </c>
       <c r="BP35" t="n">
-        <v>0.003192762699526692</v>
+        <v>0.02893841777306962</v>
       </c>
       <c r="BQ35" t="n">
-        <v>0.005281047304006089</v>
+        <v>0.04270470454090757</v>
       </c>
       <c r="BR35" t="n">
-        <v>0.01035501236196057</v>
+        <v>0.04587267257058152</v>
       </c>
       <c r="BS35" t="n">
-        <v>0.002984671577569403</v>
+        <v>0.03552544426605356</v>
       </c>
       <c r="BT35" t="n">
-        <v>0.008885932079535848</v>
+        <v>0.04171179926892458</v>
       </c>
       <c r="BU35" t="n">
-        <v>0.004564241965126939</v>
+        <v>0.0506746493819193</v>
       </c>
       <c r="BV35" t="n">
-        <v>0.01133002801237427</v>
+        <v>0.06688311867097751</v>
       </c>
       <c r="BW35" t="n">
-        <v>0.005197820632101248</v>
+        <v>0.04798125402464711</v>
       </c>
       <c r="BX35" t="n">
-        <v>0.00585286807326754</v>
+        <v>0.04419233836354712</v>
       </c>
       <c r="BY35" t="n">
-        <v>0.02681793439348663</v>
+        <v>0.06629126190789038</v>
       </c>
       <c r="BZ35" t="n">
-        <v>0.01756803144244999</v>
+        <v>0.06209136829501884</v>
       </c>
       <c r="CA35" t="n">
-        <v>0.007573040461701251</v>
+        <v>0.06367634197583398</v>
       </c>
       <c r="CB35" t="n">
-        <v>1.007934786797668</v>
+        <v>1.061034059270431</v>
       </c>
       <c r="CC35" t="n">
-        <v>0.01445071353180657</v>
+        <v>0.06412309135462546</v>
       </c>
       <c r="CD35" t="n">
-        <v>0.00529414306927801</v>
+        <v>0.01740937469034625</v>
       </c>
       <c r="CE35" t="n">
-        <v>0.01222583606940874</v>
+        <v>0.06745026402669403</v>
       </c>
       <c r="CF35" t="n">
-        <v>0.009678240279020277</v>
+        <v>0.0594717566304761</v>
       </c>
       <c r="CG35" t="n">
-        <v>0.004933127881606228</v>
+        <v>0.01875875163753868</v>
       </c>
       <c r="CH35" t="n">
-        <v>0.01626130351584966</v>
+        <v>0.06815547066788659</v>
       </c>
       <c r="CI35" t="n">
-        <v>0.01352645741517972</v>
+        <v>0.06554149359259005</v>
       </c>
       <c r="CJ35" t="n">
-        <v>0.007939076715889525</v>
+        <v>0.0709710093943752</v>
       </c>
       <c r="CK35" t="n">
-        <v>0.006827316294645282</v>
+        <v>0.07463550892184348</v>
       </c>
       <c r="CL35" t="n">
-        <v>0.00948077847705156</v>
+        <v>0.06808907176119124</v>
       </c>
       <c r="CM35" t="n">
-        <v>0.01559288246535233</v>
+        <v>0.06324768045093908</v>
       </c>
       <c r="CN35" t="n">
-        <v>0.01419675648690238</v>
+        <v>0.07025054435213779</v>
       </c>
       <c r="CO35" t="n">
-        <v>0</v>
+        <v>0.09734945131256408</v>
       </c>
       <c r="CP35" t="n">
-        <v>0</v>
+        <v>0.09501069236422113</v>
       </c>
     </row>
     <row r="36">
@@ -10382,142 +10382,142 @@
         </is>
       </c>
       <c r="AW36" t="n">
-        <v>0.003453722247241761</v>
+        <v>0.01239820677102831</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.003292974529339083</v>
+        <v>0.01163828263952065</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.004925873703396843</v>
+        <v>0.01582891048904842</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.002847649610956051</v>
+        <v>0.01299361838517645</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.002896862066063923</v>
+        <v>0.01940223663658868</v>
       </c>
       <c r="BB36" t="n">
-        <v>0.006413104270818129</v>
+        <v>0.01837857607664938</v>
       </c>
       <c r="BC36" t="n">
-        <v>0.005382793235321814</v>
+        <v>0.01989890701231429</v>
       </c>
       <c r="BD36" t="n">
-        <v>0.003943361741638358</v>
+        <v>0.01792545398547911</v>
       </c>
       <c r="BE36" t="n">
-        <v>0.003923514538562913</v>
+        <v>0.0175202676027702</v>
       </c>
       <c r="BF36" t="n">
-        <v>0.002897989341750548</v>
+        <v>0.009554911673295001</v>
       </c>
       <c r="BG36" t="n">
-        <v>0.004118634074618116</v>
+        <v>0.01346674938659716</v>
       </c>
       <c r="BH36" t="n">
-        <v>0.006687855636537187</v>
+        <v>0.01931883330753617</v>
       </c>
       <c r="BI36" t="n">
-        <v>0.003862978423068998</v>
+        <v>0.01681898967398113</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0.004730963457842754</v>
+        <v>0.01835012644548462</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.002228826377086719</v>
+        <v>0.01064914132640271</v>
       </c>
       <c r="BL36" t="n">
-        <v>0.003523871346629808</v>
+        <v>0.01840208957686435</v>
       </c>
       <c r="BM36" t="n">
-        <v>0.005412409294685535</v>
+        <v>0.01879327051908011</v>
       </c>
       <c r="BN36" t="n">
-        <v>0.004691645605638096</v>
+        <v>0.01700771545902856</v>
       </c>
       <c r="BO36" t="n">
-        <v>0.004284045741205256</v>
+        <v>0.01846538021769306</v>
       </c>
       <c r="BP36" t="n">
-        <v>0.002579491413362693</v>
+        <v>0.0109176317657805</v>
       </c>
       <c r="BQ36" t="n">
-        <v>0.003798295897588405</v>
+        <v>0.01591854320342322</v>
       </c>
       <c r="BR36" t="n">
-        <v>0.005534282048407178</v>
+        <v>0.01703724186679227</v>
       </c>
       <c r="BS36" t="n">
-        <v>0.003480166638982951</v>
+        <v>0.01401901403197596</v>
       </c>
       <c r="BT36" t="n">
-        <v>0.007842750196286342</v>
+        <v>0.01847392998305431</v>
       </c>
       <c r="BU36" t="n">
-        <v>0.003643273962396051</v>
+        <v>0.01857686363607581</v>
       </c>
       <c r="BV36" t="n">
-        <v>0.0135889387497462</v>
+        <v>0.03158069175035381</v>
       </c>
       <c r="BW36" t="n">
-        <v>0.003921859885141147</v>
+        <v>0.01777795604452603</v>
       </c>
       <c r="BX36" t="n">
-        <v>0.003277069974011538</v>
+        <v>0.01569391791998659</v>
       </c>
       <c r="BY36" t="n">
-        <v>0.005566104769053113</v>
+        <v>0.01835017043185627</v>
       </c>
       <c r="BZ36" t="n">
-        <v>0.005739313060807753</v>
+        <v>0.02015890466079759</v>
       </c>
       <c r="CA36" t="n">
-        <v>0.005998753976839596</v>
+        <v>0.02416870152420563</v>
       </c>
       <c r="CB36" t="n">
-        <v>0.006818178739601376</v>
+        <v>0.02401522364774031</v>
       </c>
       <c r="CC36" t="n">
-        <v>1.131438137034676</v>
+        <v>1.147525327542817</v>
       </c>
       <c r="CD36" t="n">
-        <v>0.04402590157932285</v>
+        <v>0.04794961225477298</v>
       </c>
       <c r="CE36" t="n">
-        <v>0.04289770419366472</v>
+        <v>0.06078301454504217</v>
       </c>
       <c r="CF36" t="n">
-        <v>0.0124865073066828</v>
+        <v>0.02861293045625368</v>
       </c>
       <c r="CG36" t="n">
-        <v>0.003441542733388319</v>
+        <v>0.007919191136871827</v>
       </c>
       <c r="CH36" t="n">
-        <v>0.01041014495157579</v>
+        <v>0.02721689731229436</v>
       </c>
       <c r="CI36" t="n">
-        <v>0.009720911670562941</v>
+        <v>0.02656680938978742</v>
       </c>
       <c r="CJ36" t="n">
-        <v>0.008138126213147898</v>
+        <v>0.02855202129004792</v>
       </c>
       <c r="CK36" t="n">
-        <v>0.01080305184964378</v>
+        <v>0.03276381476495131</v>
       </c>
       <c r="CL36" t="n">
-        <v>0.004907016989104232</v>
+        <v>0.02388824600902575</v>
       </c>
       <c r="CM36" t="n">
-        <v>0.01219250264884785</v>
+        <v>0.0276262678000897</v>
       </c>
       <c r="CN36" t="n">
-        <v>0.00826113797719252</v>
+        <v>0.02641504974094042</v>
       </c>
       <c r="CO36" t="n">
-        <v>0</v>
+        <v>0.03152816993610569</v>
       </c>
       <c r="CP36" t="n">
-        <v>0</v>
+        <v>0.03077072560982804</v>
       </c>
     </row>
     <row r="37">
@@ -10672,142 +10672,142 @@
         </is>
       </c>
       <c r="AW37" t="n">
-        <v>0.007528991415045132</v>
+        <v>0.02475980134581482</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.003644750435664083</v>
+        <v>0.0197212965438097</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.007622955293871536</v>
+        <v>0.02862675422964525</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.004638742329930915</v>
+        <v>0.02418411233389248</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.005484232890218405</v>
+        <v>0.03728047238334388</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.007432619220186739</v>
+        <v>0.03048311138325887</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.007989126321181959</v>
+        <v>0.03595321936193968</v>
       </c>
       <c r="BD37" t="n">
-        <v>0.006936456757728205</v>
+        <v>0.03387180146623658</v>
       </c>
       <c r="BE37" t="n">
-        <v>0.006186690254629656</v>
+        <v>0.03237971089231142</v>
       </c>
       <c r="BF37" t="n">
-        <v>0.0046321233367253</v>
+        <v>0.01745613383321615</v>
       </c>
       <c r="BG37" t="n">
-        <v>0.005761013060083474</v>
+        <v>0.02376938433327106</v>
       </c>
       <c r="BH37" t="n">
-        <v>0.007498298292053009</v>
+        <v>0.0318308324822562</v>
       </c>
       <c r="BI37" t="n">
-        <v>0.005473124167694443</v>
+        <v>0.03043180867675694</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0.007491511826725813</v>
+        <v>0.03372770332911615</v>
       </c>
       <c r="BK37" t="n">
-        <v>0.003585346767535169</v>
+        <v>0.01980638734992311</v>
       </c>
       <c r="BL37" t="n">
-        <v>0.005736108666652209</v>
+        <v>0.03439776599882401</v>
       </c>
       <c r="BM37" t="n">
-        <v>0.008072173897664131</v>
+        <v>0.0338492967552643</v>
       </c>
       <c r="BN37" t="n">
-        <v>0.007219352087703219</v>
+        <v>0.03094524240295801</v>
       </c>
       <c r="BO37" t="n">
-        <v>0.006870402213043915</v>
+        <v>0.03418957060997098</v>
       </c>
       <c r="BP37" t="n">
-        <v>0.003538197370925423</v>
+        <v>0.0196009353863488</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0.005232243962890823</v>
+        <v>0.02858089833032576</v>
       </c>
       <c r="BR37" t="n">
-        <v>0.008460832175347379</v>
+        <v>0.03062033323376797</v>
       </c>
       <c r="BS37" t="n">
-        <v>0.00484181998722117</v>
+        <v>0.02514403816817173</v>
       </c>
       <c r="BT37" t="n">
-        <v>0.01028533788154064</v>
+        <v>0.03076542678532139</v>
       </c>
       <c r="BU37" t="n">
-        <v>0.006011467460289434</v>
+        <v>0.03477979330030646</v>
       </c>
       <c r="BV37" t="n">
-        <v>0.01178046668243261</v>
+        <v>0.04644009133161078</v>
       </c>
       <c r="BW37" t="n">
-        <v>0.009301137697318522</v>
+        <v>0.03599376136611725</v>
       </c>
       <c r="BX37" t="n">
-        <v>0.007016706104102517</v>
+        <v>0.03093673708267811</v>
       </c>
       <c r="BY37" t="n">
-        <v>0.01413559417470026</v>
+        <v>0.03876303972423847</v>
       </c>
       <c r="BZ37" t="n">
-        <v>0.01739649206323343</v>
+        <v>0.04517464311017209</v>
       </c>
       <c r="CA37" t="n">
-        <v>0.01073218469528842</v>
+        <v>0.04573508640618308</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.00947140625202467</v>
+        <v>0.04260009146524581</v>
       </c>
       <c r="CC37" t="n">
-        <v>0.01913830898214846</v>
+        <v>0.05012895145335081</v>
       </c>
       <c r="CD37" t="n">
-        <v>1.087888944363746</v>
+        <v>1.095447648578865</v>
       </c>
       <c r="CE37" t="n">
-        <v>0.02750375211400384</v>
+        <v>0.0619583237998128</v>
       </c>
       <c r="CF37" t="n">
-        <v>0.0261311547813108</v>
+        <v>0.05719737569258432</v>
       </c>
       <c r="CG37" t="n">
-        <v>0.008177756341934262</v>
+        <v>0.01680357579212842</v>
       </c>
       <c r="CH37" t="n">
-        <v>0.01487578217845954</v>
+        <v>0.04725260106734283</v>
       </c>
       <c r="CI37" t="n">
-        <v>0.01665542132007084</v>
+        <v>0.04910765050568989</v>
       </c>
       <c r="CJ37" t="n">
-        <v>0.01111983510728934</v>
+        <v>0.05044551621069078</v>
       </c>
       <c r="CK37" t="n">
-        <v>0.005841275060801007</v>
+        <v>0.04814686916430196</v>
       </c>
       <c r="CL37" t="n">
-        <v>0.01241976414879844</v>
+        <v>0.04898553254214788</v>
       </c>
       <c r="CM37" t="n">
-        <v>0.01174359555127412</v>
+        <v>0.04147546809574178</v>
       </c>
       <c r="CN37" t="n">
-        <v>0.01434814314180249</v>
+        <v>0.04932015324134938</v>
       </c>
       <c r="CO37" t="n">
-        <v>0</v>
+        <v>0.06073641272331957</v>
       </c>
       <c r="CP37" t="n">
-        <v>0</v>
+        <v>0.0592772588520683</v>
       </c>
     </row>
     <row r="38">
@@ -10962,142 +10962,142 @@
         </is>
       </c>
       <c r="AW38" t="n">
-        <v>0.006894028577343736</v>
+        <v>0.01312342558745772</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.005294096811593346</v>
+        <v>0.01110619668742132</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.01882422318930476</v>
+        <v>0.02641765627905736</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.008961580531745037</v>
+        <v>0.01602775269390358</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.006173003491090919</v>
+        <v>0.01766819147280272</v>
       </c>
       <c r="BB38" t="n">
-        <v>0.009105767530969143</v>
+        <v>0.01743913476902812</v>
       </c>
       <c r="BC38" t="n">
-        <v>0.008423445433049914</v>
+        <v>0.01853321034128973</v>
       </c>
       <c r="BD38" t="n">
-        <v>0.007939326176808209</v>
+        <v>0.01767717114565911</v>
       </c>
       <c r="BE38" t="n">
-        <v>0.007505070941300483</v>
+        <v>0.01697454597479011</v>
       </c>
       <c r="BF38" t="n">
-        <v>0.00939069295868389</v>
+        <v>0.01402691452722754</v>
       </c>
       <c r="BG38" t="n">
-        <v>0.008242039645314598</v>
+        <v>0.01475254580358236</v>
       </c>
       <c r="BH38" t="n">
-        <v>0.0100694971744558</v>
+        <v>0.01886635677316053</v>
       </c>
       <c r="BI38" t="n">
-        <v>0.006848174200876004</v>
+        <v>0.01587140382744685</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0.009329787405879744</v>
+        <v>0.01881486985751281</v>
       </c>
       <c r="BK38" t="n">
-        <v>0.005644340079449746</v>
+        <v>0.01150867855865386</v>
       </c>
       <c r="BL38" t="n">
-        <v>0.006538078779346162</v>
+        <v>0.01690003176979199</v>
       </c>
       <c r="BM38" t="n">
-        <v>0.008972943485910843</v>
+        <v>0.01829206038776518</v>
       </c>
       <c r="BN38" t="n">
-        <v>0.008263247642882327</v>
+        <v>0.01684078931306304</v>
       </c>
       <c r="BO38" t="n">
-        <v>0.007700030335114278</v>
+        <v>0.01757663779665431</v>
       </c>
       <c r="BP38" t="n">
-        <v>0.004926175759800342</v>
+        <v>0.01073328364210829</v>
       </c>
       <c r="BQ38" t="n">
-        <v>0.008223548592127648</v>
+        <v>0.01666470941341627</v>
       </c>
       <c r="BR38" t="n">
-        <v>0.009585521145370068</v>
+        <v>0.0175967713531992</v>
       </c>
       <c r="BS38" t="n">
-        <v>0.01374217345622459</v>
+        <v>0.02108196640520559</v>
       </c>
       <c r="BT38" t="n">
-        <v>0.01798277708066021</v>
+        <v>0.02538687503639581</v>
       </c>
       <c r="BU38" t="n">
-        <v>0.008352436084942455</v>
+        <v>0.01875295258380804</v>
       </c>
       <c r="BV38" t="n">
-        <v>0.0169375487968137</v>
+        <v>0.02946792682481967</v>
       </c>
       <c r="BW38" t="n">
-        <v>0.01065797449165243</v>
+        <v>0.02030806933586415</v>
       </c>
       <c r="BX38" t="n">
-        <v>0.006496701292313751</v>
+        <v>0.01514442998634831</v>
       </c>
       <c r="BY38" t="n">
-        <v>0.0129809117461954</v>
+        <v>0.02188438966101362</v>
       </c>
       <c r="BZ38" t="n">
-        <v>0.01176829051570305</v>
+        <v>0.0218108324376175</v>
       </c>
       <c r="CA38" t="n">
-        <v>0.01879856109573665</v>
+        <v>0.03145304293026647</v>
       </c>
       <c r="CB38" t="n">
-        <v>0.01035674131347881</v>
+        <v>0.02233364393415723</v>
       </c>
       <c r="CC38" t="n">
-        <v>0.01869171971672866</v>
+        <v>0.02989566290496369</v>
       </c>
       <c r="CD38" t="n">
-        <v>0.03156477740664434</v>
+        <v>0.03429745042823664</v>
       </c>
       <c r="CE38" t="n">
-        <v>1.099741915925836</v>
+        <v>1.112198161842696</v>
       </c>
       <c r="CF38" t="n">
-        <v>0.05720456230558656</v>
+        <v>0.06843582911415633</v>
       </c>
       <c r="CG38" t="n">
-        <v>0.0078258717310396</v>
+        <v>0.0109443353499127</v>
       </c>
       <c r="CH38" t="n">
-        <v>0.02840099493500289</v>
+        <v>0.04010607784136411</v>
       </c>
       <c r="CI38" t="n">
-        <v>0.01566933209423251</v>
+        <v>0.02740167783263153</v>
       </c>
       <c r="CJ38" t="n">
-        <v>0.02051037658203354</v>
+        <v>0.03472765837380606</v>
       </c>
       <c r="CK38" t="n">
-        <v>0.006838667108036171</v>
+        <v>0.0221332668673217</v>
       </c>
       <c r="CL38" t="n">
-        <v>0.007319792539760794</v>
+        <v>0.02053929233212352</v>
       </c>
       <c r="CM38" t="n">
-        <v>0.01603301290498593</v>
+        <v>0.0267818772170957</v>
       </c>
       <c r="CN38" t="n">
-        <v>0.01382315351378919</v>
+        <v>0.02646646720752118</v>
       </c>
       <c r="CO38" t="n">
-        <v>0</v>
+        <v>0.0219578318920494</v>
       </c>
       <c r="CP38" t="n">
-        <v>0</v>
+        <v>0.02143030887952767</v>
       </c>
     </row>
     <row r="39">
@@ -11252,142 +11252,142 @@
         </is>
       </c>
       <c r="AW39" t="n">
-        <v>0.06118403879225044</v>
+        <v>0.126708888180462</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.04964586921847716</v>
+        <v>0.1107813159357996</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.08920096311511827</v>
+        <v>0.1690736311659215</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.04892970273996919</v>
+        <v>0.1232562974207824</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.03859884254990834</v>
+        <v>0.1595127062782795</v>
       </c>
       <c r="BB39" t="n">
-        <v>0.05756963944269843</v>
+        <v>0.1452254161228365</v>
       </c>
       <c r="BC39" t="n">
-        <v>0.0586809310856635</v>
+        <v>0.1650220138400791</v>
       </c>
       <c r="BD39" t="n">
-        <v>0.07057201145088218</v>
+        <v>0.1730009983839262</v>
       </c>
       <c r="BE39" t="n">
-        <v>0.06024339007922683</v>
+        <v>0.1598494874827834</v>
       </c>
       <c r="BF39" t="n">
-        <v>0.05700305659723517</v>
+        <v>0.1057698504804912</v>
       </c>
       <c r="BG39" t="n">
-        <v>0.05471959514911573</v>
+        <v>0.123201333392624</v>
       </c>
       <c r="BH39" t="n">
-        <v>0.0559342419677701</v>
+        <v>0.1484653327552913</v>
       </c>
       <c r="BI39" t="n">
-        <v>0.04799239071244766</v>
+        <v>0.1429045886854397</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0.0620814128523111</v>
+        <v>0.1618516792310553</v>
       </c>
       <c r="BK39" t="n">
-        <v>0.04269715232584723</v>
+        <v>0.1043820786497695</v>
       </c>
       <c r="BL39" t="n">
-        <v>0.04974935280954215</v>
+        <v>0.1587431138371873</v>
       </c>
       <c r="BM39" t="n">
-        <v>0.05168925258934069</v>
+        <v>0.149713785370559</v>
       </c>
       <c r="BN39" t="n">
-        <v>0.04702164252225512</v>
+        <v>0.1372458046919119</v>
       </c>
       <c r="BO39" t="n">
-        <v>0.05015547587805025</v>
+        <v>0.1540440569611261</v>
       </c>
       <c r="BP39" t="n">
-        <v>0.04195559920552223</v>
+        <v>0.1030385368881795</v>
       </c>
       <c r="BQ39" t="n">
-        <v>0.03988902823244012</v>
+        <v>0.1286786479305574</v>
       </c>
       <c r="BR39" t="n">
-        <v>0.05743950632646367</v>
+        <v>0.1417070465758653</v>
       </c>
       <c r="BS39" t="n">
-        <v>0.04220966471816327</v>
+        <v>0.1194143807993169</v>
       </c>
       <c r="BT39" t="n">
-        <v>0.06027493464042526</v>
+        <v>0.1381560526069719</v>
       </c>
       <c r="BU39" t="n">
-        <v>0.05613585485374156</v>
+        <v>0.1655352519448745</v>
       </c>
       <c r="BV39" t="n">
-        <v>0.09533053001659508</v>
+        <v>0.2271331959454797</v>
       </c>
       <c r="BW39" t="n">
-        <v>0.05913257680665254</v>
+        <v>0.1606385508555532</v>
       </c>
       <c r="BX39" t="n">
-        <v>0.05012313873148444</v>
+        <v>0.1410855736680822</v>
       </c>
       <c r="BY39" t="n">
-        <v>0.07214723141396163</v>
+        <v>0.1657998029955338</v>
       </c>
       <c r="BZ39" t="n">
-        <v>0.06962179800188964</v>
+        <v>0.1752557856639161</v>
       </c>
       <c r="CA39" t="n">
-        <v>0.05225637571857648</v>
+        <v>0.1853644462023122</v>
       </c>
       <c r="CB39" t="n">
-        <v>0.08160675220713327</v>
+        <v>0.2075876038181417</v>
       </c>
       <c r="CC39" t="n">
-        <v>0.06516416201916016</v>
+        <v>0.183014523582445</v>
       </c>
       <c r="CD39" t="n">
-        <v>0.04884087383391652</v>
+        <v>0.07758490602135747</v>
       </c>
       <c r="CE39" t="n">
-        <v>0.04430892278544996</v>
+        <v>0.1753318189533449</v>
       </c>
       <c r="CF39" t="n">
-        <v>1.198875167777363</v>
+        <v>1.317012936950769</v>
       </c>
       <c r="CG39" t="n">
-        <v>0.08734728331948265</v>
+        <v>0.120149311929558</v>
       </c>
       <c r="CH39" t="n">
-        <v>0.04540887804842781</v>
+        <v>0.1685305531111342</v>
       </c>
       <c r="CI39" t="n">
-        <v>0.05837663891426942</v>
+        <v>0.1817850821762528</v>
       </c>
       <c r="CJ39" t="n">
-        <v>0.04090764500283344</v>
+        <v>0.190454261890976</v>
       </c>
       <c r="CK39" t="n">
-        <v>0.01335025968660405</v>
+        <v>0.1742288076508834</v>
       </c>
       <c r="CL39" t="n">
-        <v>0.0282502508170584</v>
+        <v>0.1673015476722274</v>
       </c>
       <c r="CM39" t="n">
-        <v>0.06158664495225732</v>
+        <v>0.1746501909105245</v>
       </c>
       <c r="CN39" t="n">
-        <v>0.0617728913908361</v>
+        <v>0.194763488105837</v>
       </c>
       <c r="CO39" t="n">
-        <v>0</v>
+        <v>0.2309667573413944</v>
       </c>
       <c r="CP39" t="n">
-        <v>0</v>
+        <v>0.2254179271916735</v>
       </c>
     </row>
     <row r="40">
@@ -11542,142 +11542,142 @@
         </is>
       </c>
       <c r="AW40" t="n">
-        <v>0.008940524661645187</v>
+        <v>0.1122553081560341</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.007289541521676288</v>
+        <v>0.1036834363631843</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.009433224202889327</v>
+        <v>0.1353705973343801</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.007713513279484992</v>
+        <v>0.1249062441139787</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.006516782092550391</v>
+        <v>0.1971649067231758</v>
       </c>
       <c r="BB40" t="n">
-        <v>0.0124247762176859</v>
+        <v>0.1506339850032957</v>
       </c>
       <c r="BC40" t="n">
-        <v>0.01614676482236209</v>
+        <v>0.1838175957195013</v>
       </c>
       <c r="BD40" t="n">
-        <v>0.01061512139207771</v>
+        <v>0.1721176461188403</v>
       </c>
       <c r="BE40" t="n">
-        <v>0.01263924198920442</v>
+        <v>0.1696908412534807</v>
       </c>
       <c r="BF40" t="n">
-        <v>0.006700054486259418</v>
+        <v>0.08359196341555382</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.009661536552615804</v>
+        <v>0.1176385258323554</v>
       </c>
       <c r="BH40" t="n">
-        <v>0.01360281821397782</v>
+        <v>0.1594990652175199</v>
       </c>
       <c r="BI40" t="n">
-        <v>0.01199211375762949</v>
+        <v>0.161642716179623</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0.01170601648394331</v>
+        <v>0.1690164653646075</v>
       </c>
       <c r="BK40" t="n">
-        <v>0.006176316592703575</v>
+        <v>0.1034365906341715</v>
       </c>
       <c r="BL40" t="n">
-        <v>0.01160068334916265</v>
+        <v>0.1834540630661439</v>
       </c>
       <c r="BM40" t="n">
-        <v>0.0123774926044276</v>
+        <v>0.1669353966055348</v>
       </c>
       <c r="BN40" t="n">
-        <v>0.01029119809580777</v>
+        <v>0.1525500490134833</v>
       </c>
       <c r="BO40" t="n">
-        <v>0.01230909615653194</v>
+        <v>0.1761130020388131</v>
       </c>
       <c r="BP40" t="n">
-        <v>0.007363566895700439</v>
+        <v>0.1036746693370949</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0.00735918411830958</v>
+        <v>0.1473561535323356</v>
       </c>
       <c r="BR40" t="n">
-        <v>0.02007386809105081</v>
+        <v>0.1529407538261278</v>
       </c>
       <c r="BS40" t="n">
-        <v>0.008587560597062734</v>
+        <v>0.1303183024628375</v>
       </c>
       <c r="BT40" t="n">
-        <v>0.01838372579484128</v>
+        <v>0.1411809686140261</v>
       </c>
       <c r="BU40" t="n">
-        <v>0.01158821854775132</v>
+        <v>0.1840811755009726</v>
       </c>
       <c r="BV40" t="n">
-        <v>0.04445383873920274</v>
+        <v>0.2522706291868864</v>
       </c>
       <c r="BW40" t="n">
-        <v>0.01164650705364456</v>
+        <v>0.1716936926658856</v>
       </c>
       <c r="BX40" t="n">
-        <v>0.01298240581625926</v>
+        <v>0.1564053111619642</v>
       </c>
       <c r="BY40" t="n">
-        <v>0.01280103791247257</v>
+        <v>0.1604655536951463</v>
       </c>
       <c r="BZ40" t="n">
-        <v>0.02475764071980795</v>
+        <v>0.1913135758627073</v>
       </c>
       <c r="CA40" t="n">
-        <v>0.02278722935514079</v>
+        <v>0.2326622860974631</v>
       </c>
       <c r="CB40" t="n">
-        <v>0.03299293172409323</v>
+        <v>0.2316303117433398</v>
       </c>
       <c r="CC40" t="n">
-        <v>0.02848329660537971</v>
+        <v>0.2143011153921061</v>
       </c>
       <c r="CD40" t="n">
-        <v>0.02968314149623038</v>
+        <v>0.07500462624481612</v>
       </c>
       <c r="CE40" t="n">
-        <v>0.02899269124681113</v>
+        <v>0.2355799978454771</v>
       </c>
       <c r="CF40" t="n">
-        <v>0.02481686760121839</v>
+        <v>0.2110878496579343</v>
       </c>
       <c r="CG40" t="n">
-        <v>1.019147639260608</v>
+        <v>1.070867475561924</v>
       </c>
       <c r="CH40" t="n">
-        <v>0.03268267577128833</v>
+        <v>0.2268119156144325</v>
       </c>
       <c r="CI40" t="n">
-        <v>0.02754604682674636</v>
+        <v>0.2221274417636909</v>
       </c>
       <c r="CJ40" t="n">
-        <v>0.02381578759921413</v>
+        <v>0.2596099403576396</v>
       </c>
       <c r="CK40" t="n">
-        <v>0.009965615088323616</v>
+        <v>0.2636271268202599</v>
       </c>
       <c r="CL40" t="n">
-        <v>0.02291778233580409</v>
+        <v>0.2421636831404285</v>
       </c>
       <c r="CM40" t="n">
-        <v>0.04356058458746429</v>
+        <v>0.2218309031131838</v>
       </c>
       <c r="CN40" t="n">
-        <v>0.06287749450893314</v>
+        <v>0.272567327216459</v>
       </c>
       <c r="CO40" t="n">
-        <v>0</v>
+        <v>0.3641714670376678</v>
       </c>
       <c r="CP40" t="n">
-        <v>0</v>
+        <v>0.3554224780522968</v>
       </c>
     </row>
     <row r="41">
@@ -11832,142 +11832,142 @@
         </is>
       </c>
       <c r="AW41" t="n">
-        <v>0.03996502726143636</v>
+        <v>0.05731641891094457</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.02130596036730053</v>
+        <v>0.03749501062173342</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.07909712551887947</v>
+        <v>0.1002479096623068</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.03826409212304813</v>
+        <v>0.05794624120576035</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.06373510128724015</v>
+        <v>0.0957538518070038</v>
       </c>
       <c r="BB41" t="n">
-        <v>0.04449245613052641</v>
+        <v>0.06770425632113525</v>
       </c>
       <c r="BC41" t="n">
-        <v>0.03450007596746075</v>
+        <v>0.06265986256037109</v>
       </c>
       <c r="BD41" t="n">
-        <v>0.0367891883241748</v>
+        <v>0.06391302737350735</v>
       </c>
       <c r="BE41" t="n">
-        <v>0.03374126570880197</v>
+        <v>0.06011758588145251</v>
       </c>
       <c r="BF41" t="n">
-        <v>0.03933223595812716</v>
+        <v>0.05224598926026677</v>
       </c>
       <c r="BG41" t="n">
-        <v>0.03628595254896158</v>
+        <v>0.05442034693821437</v>
       </c>
       <c r="BH41" t="n">
-        <v>0.06310785183709998</v>
+        <v>0.08761066582295451</v>
       </c>
       <c r="BI41" t="n">
-        <v>0.02849875271716028</v>
+        <v>0.05363209884036903</v>
       </c>
       <c r="BJ41" t="n">
-        <v>0.04268268204668003</v>
+        <v>0.06910247519503028</v>
       </c>
       <c r="BK41" t="n">
-        <v>0.02420549910869355</v>
+        <v>0.04054005501398334</v>
       </c>
       <c r="BL41" t="n">
-        <v>0.02450391867718863</v>
+        <v>0.05336615113710511</v>
       </c>
       <c r="BM41" t="n">
-        <v>0.05169802371076911</v>
+        <v>0.07765553563834289</v>
       </c>
       <c r="BN41" t="n">
-        <v>0.02946852255807394</v>
+        <v>0.05336044735715799</v>
       </c>
       <c r="BO41" t="n">
-        <v>0.02966566303350278</v>
+        <v>0.0571760117808048</v>
       </c>
       <c r="BP41" t="n">
-        <v>0.01562687596744455</v>
+        <v>0.03180202149971294</v>
       </c>
       <c r="BQ41" t="n">
-        <v>0.04220991517886536</v>
+        <v>0.06572196412178279</v>
       </c>
       <c r="BR41" t="n">
-        <v>0.03202167342323726</v>
+        <v>0.05433624732702892</v>
       </c>
       <c r="BS41" t="n">
-        <v>0.04643917370766021</v>
+        <v>0.06688346741334232</v>
       </c>
       <c r="BT41" t="n">
-        <v>0.03340285471538672</v>
+        <v>0.05402626388849075</v>
       </c>
       <c r="BU41" t="n">
-        <v>0.07923194861454014</v>
+        <v>0.1082015960516821</v>
       </c>
       <c r="BV41" t="n">
-        <v>0.06894199545064952</v>
+        <v>0.1038441691806789</v>
       </c>
       <c r="BW41" t="n">
-        <v>0.02496686399785597</v>
+        <v>0.05184628343844701</v>
       </c>
       <c r="BX41" t="n">
-        <v>0.02028743973452311</v>
+        <v>0.04437486379904558</v>
       </c>
       <c r="BY41" t="n">
-        <v>0.03033353187876016</v>
+        <v>0.05513332102238561</v>
       </c>
       <c r="BZ41" t="n">
-        <v>0.02890180541768712</v>
+        <v>0.05687434878919302</v>
       </c>
       <c r="CA41" t="n">
-        <v>0.02158804314159108</v>
+        <v>0.05683589619639202</v>
       </c>
       <c r="CB41" t="n">
-        <v>0.03185446413627199</v>
+        <v>0.06521498487078367</v>
       </c>
       <c r="CC41" t="n">
-        <v>0.05018521097177928</v>
+        <v>0.08139272687777681</v>
       </c>
       <c r="CD41" t="n">
-        <v>0.03941311693189541</v>
+        <v>0.04702471718320535</v>
       </c>
       <c r="CE41" t="n">
-        <v>0.03043744100528115</v>
+        <v>0.06513312680522447</v>
       </c>
       <c r="CF41" t="n">
-        <v>0.05961866981144945</v>
+        <v>0.09090229305768245</v>
       </c>
       <c r="CG41" t="n">
-        <v>0.02354355263965675</v>
+        <v>0.03222973583009364</v>
       </c>
       <c r="CH41" t="n">
-        <v>1.084435515348252</v>
+        <v>1.117038908175597</v>
       </c>
       <c r="CI41" t="n">
-        <v>0.05189556378045037</v>
+        <v>0.08457489462802385</v>
       </c>
       <c r="CJ41" t="n">
-        <v>0.05413369701797899</v>
+        <v>0.09373458040363321</v>
       </c>
       <c r="CK41" t="n">
-        <v>0.01795960234538246</v>
+        <v>0.06056125225065658</v>
       </c>
       <c r="CL41" t="n">
-        <v>0.02240151546337971</v>
+        <v>0.05922317218801366</v>
       </c>
       <c r="CM41" t="n">
-        <v>0.03879226315681465</v>
+        <v>0.06873220022681137</v>
       </c>
       <c r="CN41" t="n">
-        <v>0.04834640292670532</v>
+        <v>0.08356314818974644</v>
       </c>
       <c r="CO41" t="n">
-        <v>0</v>
+        <v>0.06116144794021398</v>
       </c>
       <c r="CP41" t="n">
-        <v>0</v>
+        <v>0.05969208286691207</v>
       </c>
     </row>
     <row r="42">
@@ -12122,142 +12122,142 @@
         </is>
       </c>
       <c r="AW42" t="n">
-        <v>0.01995548547048522</v>
+        <v>0.03575676260842864</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.01755630853416476</v>
+        <v>0.03229908391712014</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.04425971631485789</v>
+        <v>0.06352096110063775</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.0204194942803269</v>
+        <v>0.03834330688328137</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.0347662981236006</v>
+        <v>0.06392460201029747</v>
       </c>
       <c r="BB42" t="n">
-        <v>0.025732573996051</v>
+        <v>0.04687071064186715</v>
       </c>
       <c r="BC42" t="n">
-        <v>0.02255708654628824</v>
+        <v>0.04820117326209532</v>
       </c>
       <c r="BD42" t="n">
-        <v>0.02120080251971571</v>
+        <v>0.04590148973379415</v>
       </c>
       <c r="BE42" t="n">
-        <v>0.02241721937357996</v>
+        <v>0.04643716851345147</v>
       </c>
       <c r="BF42" t="n">
-        <v>0.02248405157208335</v>
+        <v>0.03424413392973813</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.02477316339355021</v>
+        <v>0.04128749246072164</v>
       </c>
       <c r="BH42" t="n">
-        <v>0.02928188285711477</v>
+        <v>0.05159569850203668</v>
       </c>
       <c r="BI42" t="n">
-        <v>0.02320447107166531</v>
+        <v>0.04609248925019183</v>
       </c>
       <c r="BJ42" t="n">
-        <v>0.02591089296117537</v>
+        <v>0.04997043134846391</v>
       </c>
       <c r="BK42" t="n">
-        <v>0.01549796622295425</v>
+        <v>0.03037324827515953</v>
       </c>
       <c r="BL42" t="n">
-        <v>0.02126876522163449</v>
+        <v>0.04755254367186688</v>
       </c>
       <c r="BM42" t="n">
-        <v>0.02481700656386916</v>
+        <v>0.04845556236758708</v>
       </c>
       <c r="BN42" t="n">
-        <v>0.02133990047901349</v>
+        <v>0.04309740170629574</v>
       </c>
       <c r="BO42" t="n">
-        <v>0.01932399736837614</v>
+        <v>0.04437666481421264</v>
       </c>
       <c r="BP42" t="n">
-        <v>0.02166057583148981</v>
+        <v>0.03639068869302414</v>
       </c>
       <c r="BQ42" t="n">
-        <v>0.02024960771381005</v>
+        <v>0.04166116990619808</v>
       </c>
       <c r="BR42" t="n">
-        <v>0.03178063565038427</v>
+        <v>0.05210170116439598</v>
       </c>
       <c r="BS42" t="n">
-        <v>0.01784892251928748</v>
+        <v>0.03646679232814233</v>
       </c>
       <c r="BT42" t="n">
-        <v>0.04741912739087644</v>
+        <v>0.06620011109846609</v>
       </c>
       <c r="BU42" t="n">
-        <v>0.02982607522289102</v>
+        <v>0.05620767256040296</v>
       </c>
       <c r="BV42" t="n">
-        <v>0.04936547615136733</v>
+        <v>0.08114960799306163</v>
       </c>
       <c r="BW42" t="n">
-        <v>0.03896367803371961</v>
+        <v>0.0634417812583587</v>
       </c>
       <c r="BX42" t="n">
-        <v>0.02695473167154985</v>
+        <v>0.04889026692260703</v>
       </c>
       <c r="BY42" t="n">
-        <v>0.03464476400990201</v>
+        <v>0.05722902405869713</v>
       </c>
       <c r="BZ42" t="n">
-        <v>0.04003121813075497</v>
+        <v>0.06550478929983373</v>
       </c>
       <c r="CA42" t="n">
-        <v>0.04426394206862007</v>
+        <v>0.07636287141600764</v>
       </c>
       <c r="CB42" t="n">
-        <v>0.03749783963543519</v>
+        <v>0.0678780445342778</v>
       </c>
       <c r="CC42" t="n">
-        <v>0.05455112942237734</v>
+        <v>0.08297067164574826</v>
       </c>
       <c r="CD42" t="n">
-        <v>0.04647016885240139</v>
+        <v>0.05340177453934912</v>
       </c>
       <c r="CE42" t="n">
-        <v>0.07024330632437249</v>
+        <v>0.101839397167694</v>
       </c>
       <c r="CF42" t="n">
-        <v>0.0624151087787418</v>
+        <v>0.0909039591705631</v>
       </c>
       <c r="CG42" t="n">
-        <v>0.02879226297856822</v>
+        <v>0.03670245200752307</v>
       </c>
       <c r="CH42" t="n">
-        <v>0.05255129424143976</v>
+        <v>0.08224201047380161</v>
       </c>
       <c r="CI42" t="n">
-        <v>1.061900912150467</v>
+        <v>1.091660782357747</v>
       </c>
       <c r="CJ42" t="n">
-        <v>0.04055957178125661</v>
+        <v>0.07662264648580552</v>
       </c>
       <c r="CK42" t="n">
-        <v>0.02109044608170896</v>
+        <v>0.05988620899712653</v>
       </c>
       <c r="CL42" t="n">
-        <v>0.02494843961534132</v>
+        <v>0.0584805743476381</v>
       </c>
       <c r="CM42" t="n">
-        <v>0.04714272555009872</v>
+        <v>0.07440793013379055</v>
       </c>
       <c r="CN42" t="n">
-        <v>0.05016089441514227</v>
+        <v>0.08223149503543546</v>
       </c>
       <c r="CO42" t="n">
-        <v>0</v>
+        <v>0.05569749150861973</v>
       </c>
       <c r="CP42" t="n">
-        <v>0</v>
+        <v>0.05435939453005743</v>
       </c>
     </row>
     <row r="43">
@@ -12412,142 +12412,142 @@
         </is>
       </c>
       <c r="AW43" t="n">
-        <v>0.006836374116016664</v>
+        <v>0.01471691708641122</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.006309749380194671</v>
+        <v>0.0136623876444316</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.008013362583068062</v>
+        <v>0.01761948909249666</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.005324464052257451</v>
+        <v>0.01426357537710738</v>
       </c>
       <c r="BA43" t="n">
-        <v>0.005762948354251117</v>
+        <v>0.02030501762605457</v>
       </c>
       <c r="BB43" t="n">
-        <v>0.01311001963018474</v>
+        <v>0.02365220509387865</v>
       </c>
       <c r="BC43" t="n">
-        <v>0.009338439155537732</v>
+        <v>0.02212786911972507</v>
       </c>
       <c r="BD43" t="n">
-        <v>0.008832755424088134</v>
+        <v>0.02115168542509408</v>
       </c>
       <c r="BE43" t="n">
-        <v>0.01000282469134837</v>
+        <v>0.02198225139787127</v>
       </c>
       <c r="BF43" t="n">
-        <v>0.006348980607732703</v>
+        <v>0.01221406566040455</v>
       </c>
       <c r="BG43" t="n">
-        <v>0.01211899264861159</v>
+        <v>0.02035515474519125</v>
       </c>
       <c r="BH43" t="n">
-        <v>0.01119995231688251</v>
+        <v>0.02232848208622722</v>
       </c>
       <c r="BI43" t="n">
-        <v>0.009658737478124733</v>
+        <v>0.02107363826041211</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0.01081325640015834</v>
+        <v>0.02281242738195164</v>
       </c>
       <c r="BK43" t="n">
-        <v>0.006463841635701883</v>
+        <v>0.01388256471648697</v>
       </c>
       <c r="BL43" t="n">
-        <v>0.008337758356850637</v>
+        <v>0.02144622064715544</v>
       </c>
       <c r="BM43" t="n">
-        <v>0.007927861237875715</v>
+        <v>0.01971707632112652</v>
       </c>
       <c r="BN43" t="n">
-        <v>0.00788704738190818</v>
+        <v>0.01873812744671402</v>
       </c>
       <c r="BO43" t="n">
-        <v>0.008641368780802938</v>
+        <v>0.02113584125960253</v>
       </c>
       <c r="BP43" t="n">
-        <v>0.005771342273040383</v>
+        <v>0.01311766538038834</v>
       </c>
       <c r="BQ43" t="n">
-        <v>0.006654533917724746</v>
+        <v>0.01733308442015272</v>
       </c>
       <c r="BR43" t="n">
-        <v>0.008666980132756227</v>
+        <v>0.01880166915753305</v>
       </c>
       <c r="BS43" t="n">
-        <v>0.00362356525292809</v>
+        <v>0.01290882249922862</v>
       </c>
       <c r="BT43" t="n">
-        <v>0.009222052827383564</v>
+        <v>0.01858865957960229</v>
       </c>
       <c r="BU43" t="n">
-        <v>0.007982422936568834</v>
+        <v>0.02113967026733543</v>
       </c>
       <c r="BV43" t="n">
-        <v>0.01040597226725993</v>
+        <v>0.02625761606595594</v>
       </c>
       <c r="BW43" t="n">
-        <v>0.00888593236687772</v>
+        <v>0.02109385344892188</v>
       </c>
       <c r="BX43" t="n">
-        <v>0.01342448388445455</v>
+        <v>0.02436435454272334</v>
       </c>
       <c r="BY43" t="n">
-        <v>0.01227012721900061</v>
+        <v>0.02353353524705949</v>
       </c>
       <c r="BZ43" t="n">
-        <v>0.009223730904216002</v>
+        <v>0.02192811995168617</v>
       </c>
       <c r="CA43" t="n">
-        <v>0.007729664138558031</v>
+        <v>0.02373830633991048</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.01093981822136321</v>
+        <v>0.0260912840215435</v>
       </c>
       <c r="CC43" t="n">
-        <v>0.01398827237282261</v>
+        <v>0.02816190034827411</v>
       </c>
       <c r="CD43" t="n">
-        <v>0.00766190902044541</v>
+        <v>0.01111889645209123</v>
       </c>
       <c r="CE43" t="n">
-        <v>0.0109520852350984</v>
+        <v>0.0267099476796079</v>
       </c>
       <c r="CF43" t="n">
-        <v>0.01212966194176572</v>
+        <v>0.02633785585735637</v>
       </c>
       <c r="CG43" t="n">
-        <v>0.006315140814837143</v>
+        <v>0.01026017538403245</v>
       </c>
       <c r="CH43" t="n">
-        <v>0.008537374392418074</v>
+        <v>0.02334497273072379</v>
       </c>
       <c r="CI43" t="n">
-        <v>0.007325895106134378</v>
+        <v>0.02216798248391206</v>
       </c>
       <c r="CJ43" t="n">
-        <v>1.020951161789923</v>
+        <v>1.03893683518662</v>
       </c>
       <c r="CK43" t="n">
-        <v>0.005007766514785925</v>
+        <v>0.02435630866458708</v>
       </c>
       <c r="CL43" t="n">
-        <v>0.009564742703756061</v>
+        <v>0.02628816488919326</v>
       </c>
       <c r="CM43" t="n">
-        <v>0.01364905820948138</v>
+        <v>0.02724698541768344</v>
       </c>
       <c r="CN43" t="n">
-        <v>0.01621340311004203</v>
+        <v>0.03220791697548751</v>
       </c>
       <c r="CO43" t="n">
-        <v>0</v>
+        <v>0.02777791132609621</v>
       </c>
       <c r="CP43" t="n">
-        <v>0</v>
+        <v>0.02711056458911671</v>
       </c>
     </row>
     <row r="44">
@@ -12702,142 +12702,142 @@
         </is>
       </c>
       <c r="AW44" t="n">
-        <v>0.001228407108729885</v>
+        <v>0.007868822531812791</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.00121573399247459</v>
+        <v>0.00741131882890166</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.002155652516035123</v>
+        <v>0.01025010373201542</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.00116145441527504</v>
+        <v>0.00869385579081333</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.001642375540947548</v>
+        <v>0.01389602118932461</v>
       </c>
       <c r="BB44" t="n">
-        <v>0.001810091469105932</v>
+        <v>0.01069329802087587</v>
       </c>
       <c r="BC44" t="n">
-        <v>0.001562095200912251</v>
+        <v>0.01233890693909838</v>
       </c>
       <c r="BD44" t="n">
-        <v>0.001497174461245015</v>
+        <v>0.01187752681537513</v>
       </c>
       <c r="BE44" t="n">
-        <v>0.001452970707740401</v>
+        <v>0.01154724595762248</v>
       </c>
       <c r="BF44" t="n">
-        <v>0.001374762703488114</v>
+        <v>0.006316884253712369</v>
       </c>
       <c r="BG44" t="n">
-        <v>0.001523006506033712</v>
+        <v>0.00846307878513965</v>
       </c>
       <c r="BH44" t="n">
-        <v>0.00210071053113058</v>
+        <v>0.01147799087770219</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.001420242150583984</v>
+        <v>0.0110388285211456</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0.001668622525317797</v>
+        <v>0.01177953497780326</v>
       </c>
       <c r="BK44" t="n">
-        <v>0.0009864972348000466</v>
+        <v>0.007237767401119562</v>
       </c>
       <c r="BL44" t="n">
-        <v>0.001147337932589084</v>
+        <v>0.01219297723592793</v>
       </c>
       <c r="BM44" t="n">
-        <v>0.001674845788350889</v>
+        <v>0.0116088422095316</v>
       </c>
       <c r="BN44" t="n">
-        <v>0.001387154859402957</v>
+        <v>0.01053064658200904</v>
       </c>
       <c r="BO44" t="n">
-        <v>0.001383834609208222</v>
+        <v>0.01191210506762713</v>
       </c>
       <c r="BP44" t="n">
-        <v>0.0007978949622154017</v>
+        <v>0.006988158431147587</v>
       </c>
       <c r="BQ44" t="n">
-        <v>0.001238713441564798</v>
+        <v>0.0102368258456067</v>
       </c>
       <c r="BR44" t="n">
-        <v>0.001854818280599361</v>
+        <v>0.01039465437579011</v>
       </c>
       <c r="BS44" t="n">
-        <v>0.001166417481329833</v>
+        <v>0.008990493266115427</v>
       </c>
       <c r="BT44" t="n">
-        <v>0.001644974264090973</v>
+        <v>0.009537597928862598</v>
       </c>
       <c r="BU44" t="n">
-        <v>0.002600390038093328</v>
+        <v>0.01368713728746017</v>
       </c>
       <c r="BV44" t="n">
-        <v>0.002615530473926583</v>
+        <v>0.01597266847285908</v>
       </c>
       <c r="BW44" t="n">
-        <v>0.002280922569515718</v>
+        <v>0.01256773500636565</v>
       </c>
       <c r="BX44" t="n">
-        <v>0.003778292991781168</v>
+        <v>0.01299660270960295</v>
       </c>
       <c r="BY44" t="n">
-        <v>0.006056783164626533</v>
+        <v>0.01554771655170168</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0.001901404610123655</v>
+        <v>0.01260655795915015</v>
       </c>
       <c r="CA44" t="n">
-        <v>0.002515431925773112</v>
+        <v>0.01600486215613126</v>
       </c>
       <c r="CB44" t="n">
-        <v>0.002064471732440531</v>
+        <v>0.01483161576804917</v>
       </c>
       <c r="CC44" t="n">
-        <v>0.005011297395693435</v>
+        <v>0.01695448178829313</v>
       </c>
       <c r="CD44" t="n">
-        <v>0.002076533008925867</v>
+        <v>0.004989509023998001</v>
       </c>
       <c r="CE44" t="n">
-        <v>0.00767118572221527</v>
+        <v>0.02094930034000802</v>
       </c>
       <c r="CF44" t="n">
-        <v>0.003874212869656826</v>
+        <v>0.0158465237073347</v>
       </c>
       <c r="CG44" t="n">
-        <v>0.001061469568731758</v>
+        <v>0.004385690817990191</v>
       </c>
       <c r="CH44" t="n">
-        <v>0.003546856028834133</v>
+        <v>0.01602424556327367</v>
       </c>
       <c r="CI44" t="n">
-        <v>0.002491123236738285</v>
+        <v>0.01499757441711991</v>
       </c>
       <c r="CJ44" t="n">
-        <v>0.006691038942065109</v>
+        <v>0.02184638337285369</v>
       </c>
       <c r="CK44" t="n">
-        <v>1.002203364315689</v>
+        <v>1.018507108637417</v>
       </c>
       <c r="CL44" t="n">
-        <v>0.002087653737061553</v>
+        <v>0.01617938206391618</v>
       </c>
       <c r="CM44" t="n">
-        <v>0.002431777790341269</v>
+        <v>0.01388985699814779</v>
       </c>
       <c r="CN44" t="n">
-        <v>0.00241092221481834</v>
+        <v>0.0158884474254321</v>
       </c>
       <c r="CO44" t="n">
-        <v>0</v>
+        <v>0.02340661950373243</v>
       </c>
       <c r="CP44" t="n">
-        <v>0</v>
+        <v>0.02284429028588149</v>
       </c>
     </row>
     <row r="45">
@@ -12992,142 +12992,142 @@
         </is>
       </c>
       <c r="AW45" t="n">
-        <v>0.001787583036547335</v>
+        <v>0.01991303192530533</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.001954776081377499</v>
+        <v>0.0188660307444912</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.002010672080684194</v>
+        <v>0.02410500691518785</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.001461605477155078</v>
+        <v>0.02202178845416295</v>
       </c>
       <c r="BA45" t="n">
-        <v>0.001488348821595644</v>
+        <v>0.03493547731427298</v>
       </c>
       <c r="BB45" t="n">
-        <v>0.00302781509818838</v>
+        <v>0.02727510929045959</v>
       </c>
       <c r="BC45" t="n">
-        <v>0.002386475249950634</v>
+        <v>0.03180248884230103</v>
       </c>
       <c r="BD45" t="n">
-        <v>0.002394721634567737</v>
+        <v>0.03072857336740609</v>
       </c>
       <c r="BE45" t="n">
-        <v>0.002444081439456379</v>
+        <v>0.02999706697629336</v>
       </c>
       <c r="BF45" t="n">
-        <v>0.001682711151236984</v>
+        <v>0.01517255566446342</v>
       </c>
       <c r="BG45" t="n">
-        <v>0.002671776158822211</v>
+        <v>0.02161515806561567</v>
       </c>
       <c r="BH45" t="n">
-        <v>0.003454972328864464</v>
+        <v>0.02905087330917222</v>
       </c>
       <c r="BI45" t="n">
-        <v>0.00257596160988821</v>
+        <v>0.02883052318982902</v>
       </c>
       <c r="BJ45" t="n">
-        <v>0.002861708311077714</v>
+        <v>0.03046010618226826</v>
       </c>
       <c r="BK45" t="n">
-        <v>0.001708007328164569</v>
+        <v>0.01877125874697982</v>
       </c>
       <c r="BL45" t="n">
-        <v>0.002086590138427215</v>
+        <v>0.03223638617985856</v>
       </c>
       <c r="BM45" t="n">
-        <v>0.00194908456328128</v>
+        <v>0.02906457853784669</v>
       </c>
       <c r="BN45" t="n">
-        <v>0.002073906338097994</v>
+        <v>0.02703166595457933</v>
       </c>
       <c r="BO45" t="n">
-        <v>0.002307681918143949</v>
+        <v>0.03104528580625993</v>
       </c>
       <c r="BP45" t="n">
-        <v>0.001452046032912715</v>
+        <v>0.0183487756748641</v>
       </c>
       <c r="BQ45" t="n">
-        <v>0.00169423155181658</v>
+        <v>0.026255168794963</v>
       </c>
       <c r="BR45" t="n">
-        <v>0.002242229249578028</v>
+        <v>0.02555227128756363</v>
       </c>
       <c r="BS45" t="n">
-        <v>0.0009325723428820807</v>
+        <v>0.02228889972654761</v>
       </c>
       <c r="BT45" t="n">
-        <v>0.002294441863308507</v>
+        <v>0.02383787517573877</v>
       </c>
       <c r="BU45" t="n">
-        <v>0.001948131861254722</v>
+        <v>0.03221013473421383</v>
       </c>
       <c r="BV45" t="n">
-        <v>0.002462040128901497</v>
+        <v>0.03892122327852108</v>
       </c>
       <c r="BW45" t="n">
-        <v>0.002802831981862941</v>
+        <v>0.03088136038299723</v>
       </c>
       <c r="BX45" t="n">
-        <v>0.006767357426359042</v>
+        <v>0.0319293376618588</v>
       </c>
       <c r="BY45" t="n">
-        <v>0.005301434256964143</v>
+        <v>0.0312075586563577</v>
       </c>
       <c r="BZ45" t="n">
-        <v>0.002092027445943982</v>
+        <v>0.03131244477098123</v>
       </c>
       <c r="CA45" t="n">
-        <v>0.002233558871453693</v>
+        <v>0.03905384233277216</v>
       </c>
       <c r="CB45" t="n">
-        <v>0.002411195897318339</v>
+        <v>0.0372599518755099</v>
       </c>
       <c r="CC45" t="n">
-        <v>0.00278329933304093</v>
+        <v>0.03538300349079318</v>
       </c>
       <c r="CD45" t="n">
-        <v>0.001947842569283767</v>
+        <v>0.009899001421760383</v>
       </c>
       <c r="CE45" t="n">
-        <v>0.003156230306709092</v>
+        <v>0.03939971396094975</v>
       </c>
       <c r="CF45" t="n">
-        <v>0.003421030453916522</v>
+        <v>0.03610023715148588</v>
       </c>
       <c r="CG45" t="n">
-        <v>0.001344505987181475</v>
+        <v>0.01041818564567243</v>
       </c>
       <c r="CH45" t="n">
-        <v>0.002147385209938279</v>
+        <v>0.03620523729633841</v>
       </c>
       <c r="CI45" t="n">
-        <v>0.002075880466152643</v>
+        <v>0.03621305821888314</v>
       </c>
       <c r="CJ45" t="n">
-        <v>0.09896066951710118</v>
+        <v>0.1403281749169741</v>
       </c>
       <c r="CK45" t="n">
-        <v>0.001305041777920527</v>
+        <v>0.04580717990795884</v>
       </c>
       <c r="CL45" t="n">
-        <v>1.043099936218969</v>
+        <v>1.081564231789213</v>
       </c>
       <c r="CM45" t="n">
-        <v>0.002740458751108175</v>
+        <v>0.03401603652934576</v>
       </c>
       <c r="CN45" t="n">
-        <v>0.002920164481250117</v>
+        <v>0.03970795241131818</v>
       </c>
       <c r="CO45" t="n">
-        <v>0</v>
+        <v>0.06388990122496609</v>
       </c>
       <c r="CP45" t="n">
-        <v>0</v>
+        <v>0.06235498678853155</v>
       </c>
     </row>
     <row r="46">
@@ -13282,142 +13282,142 @@
         </is>
       </c>
       <c r="AW46" t="n">
-        <v>0.0008091940693941903</v>
+        <v>0.01011825440949807</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.0008034882889916362</v>
+        <v>0.009488949876838459</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.001023162684084293</v>
+        <v>0.01237060557563229</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.0006406513573405595</v>
+        <v>0.0112001682615124</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.0008220458937118933</v>
+        <v>0.01800017699835215</v>
       </c>
       <c r="BB46" t="n">
-        <v>0.001863593865641059</v>
+        <v>0.01431677646572009</v>
       </c>
       <c r="BC46" t="n">
-        <v>0.001394375613096731</v>
+        <v>0.01650216395958825</v>
       </c>
       <c r="BD46" t="n">
-        <v>0.0009519078628044344</v>
+        <v>0.01550390804041894</v>
       </c>
       <c r="BE46" t="n">
-        <v>0.001086494791705644</v>
+        <v>0.01523744942386981</v>
       </c>
       <c r="BF46" t="n">
-        <v>0.0006151493337773698</v>
+        <v>0.007543406797797012</v>
       </c>
       <c r="BG46" t="n">
-        <v>0.0010219666664854</v>
+        <v>0.01075110972375596</v>
       </c>
       <c r="BH46" t="n">
-        <v>0.002280841549389801</v>
+        <v>0.01542665593155356</v>
       </c>
       <c r="BI46" t="n">
-        <v>0.001034359762033993</v>
+        <v>0.01451845604293936</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0.001222174553717949</v>
+        <v>0.01539645253435623</v>
       </c>
       <c r="BK46" t="n">
-        <v>0.0004982518102907123</v>
+        <v>0.009261777504522419</v>
       </c>
       <c r="BL46" t="n">
-        <v>0.0009264400059870725</v>
+        <v>0.01641109212765607</v>
       </c>
       <c r="BM46" t="n">
-        <v>0.001259731842030314</v>
+        <v>0.01518599491612784</v>
       </c>
       <c r="BN46" t="n">
-        <v>0.001115777397947993</v>
+        <v>0.01393384836819212</v>
       </c>
       <c r="BO46" t="n">
-        <v>0.001053299482178199</v>
+        <v>0.01581266297526113</v>
       </c>
       <c r="BP46" t="n">
-        <v>0.0006779324857715365</v>
+        <v>0.009355934159148316</v>
       </c>
       <c r="BQ46" t="n">
-        <v>0.0009497366655816169</v>
+        <v>0.01356400339128815</v>
       </c>
       <c r="BR46" t="n">
-        <v>0.00154054658995</v>
+        <v>0.01351236528496467</v>
       </c>
       <c r="BS46" t="n">
-        <v>0.0005573993062346182</v>
+        <v>0.01152580850137803</v>
       </c>
       <c r="BT46" t="n">
-        <v>0.002126713945007597</v>
+        <v>0.01319121898812432</v>
       </c>
       <c r="BU46" t="n">
-        <v>0.0009335369313994466</v>
+        <v>0.01647581742804963</v>
       </c>
       <c r="BV46" t="n">
-        <v>0.002172017070597941</v>
+        <v>0.02089711116198978</v>
       </c>
       <c r="BW46" t="n">
-        <v>0.0008635906317767778</v>
+        <v>0.01528445914387189</v>
       </c>
       <c r="BX46" t="n">
-        <v>0.0008478850265493717</v>
+        <v>0.01377084178896359</v>
       </c>
       <c r="BY46" t="n">
-        <v>0.001580309524587209</v>
+        <v>0.01488545174160388</v>
       </c>
       <c r="BZ46" t="n">
-        <v>0.001601997489010533</v>
+        <v>0.01660932942937979</v>
       </c>
       <c r="CA46" t="n">
-        <v>0.001299154599947703</v>
+        <v>0.02020970642047309</v>
       </c>
       <c r="CB46" t="n">
-        <v>0.003687405844169355</v>
+        <v>0.02158539966322176</v>
       </c>
       <c r="CC46" t="n">
-        <v>0.02399686008285799</v>
+        <v>0.04073976200691874</v>
       </c>
       <c r="CD46" t="n">
-        <v>0.00261982456739833</v>
+        <v>0.006703465087736793</v>
       </c>
       <c r="CE46" t="n">
-        <v>0.003423059810475396</v>
+        <v>0.02203737266659214</v>
       </c>
       <c r="CF46" t="n">
-        <v>0.002381755836405393</v>
+        <v>0.01916548951833824</v>
       </c>
       <c r="CG46" t="n">
-        <v>0.001238733414276175</v>
+        <v>0.005898890079419789</v>
       </c>
       <c r="CH46" t="n">
-        <v>0.00244103467364543</v>
+        <v>0.01993282768094989</v>
       </c>
       <c r="CI46" t="n">
-        <v>0.003498383114932152</v>
+        <v>0.02103091703954687</v>
       </c>
       <c r="CJ46" t="n">
-        <v>0.002871391718786694</v>
+        <v>0.02411735402573056</v>
       </c>
       <c r="CK46" t="n">
-        <v>0.001243657971553889</v>
+        <v>0.02409953821257291</v>
       </c>
       <c r="CL46" t="n">
-        <v>0.001115381277296671</v>
+        <v>0.02087028227867683</v>
       </c>
       <c r="CM46" t="n">
-        <v>1.048295585219734</v>
+        <v>1.064358428269641</v>
       </c>
       <c r="CN46" t="n">
-        <v>0.002736526594177871</v>
+        <v>0.02163038901500616</v>
       </c>
       <c r="CO46" t="n">
-        <v>0</v>
+        <v>0.0328132533035015</v>
       </c>
       <c r="CP46" t="n">
-        <v>0</v>
+        <v>0.03202493566274348</v>
       </c>
     </row>
     <row r="47">
@@ -13572,142 +13572,142 @@
         </is>
       </c>
       <c r="AW47" t="n">
-        <v>0.00437864938203059</v>
+        <v>0.01126845469240285</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.006303826870779221</v>
+        <v>0.01273209537315242</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.005562465462770302</v>
+        <v>0.01396091486979831</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.00703565081772338</v>
+        <v>0.0148509418334992</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.004462634438014877</v>
+        <v>0.01717648251537095</v>
       </c>
       <c r="BB47" t="n">
-        <v>0.005299440830525672</v>
+        <v>0.01451626835923224</v>
       </c>
       <c r="BC47" t="n">
-        <v>0.004450887914734</v>
+        <v>0.01563243756365118</v>
       </c>
       <c r="BD47" t="n">
-        <v>0.004616021677155923</v>
+        <v>0.01538622236737378</v>
       </c>
       <c r="BE47" t="n">
-        <v>0.003995009994133222</v>
+        <v>0.01446838956301393</v>
       </c>
       <c r="BF47" t="n">
-        <v>0.003795545213695398</v>
+        <v>0.008923274901039557</v>
       </c>
       <c r="BG47" t="n">
-        <v>0.004720274506926494</v>
+        <v>0.01192099069656999</v>
       </c>
       <c r="BH47" t="n">
-        <v>0.004310088591239257</v>
+        <v>0.01403954553215207</v>
       </c>
       <c r="BI47" t="n">
-        <v>0.004319380796286226</v>
+        <v>0.01429920633909885</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0.005125675712413224</v>
+        <v>0.01561631731680576</v>
       </c>
       <c r="BK47" t="n">
-        <v>0.003705255292278835</v>
+        <v>0.01019130046330279</v>
       </c>
       <c r="BL47" t="n">
-        <v>0.003267354929136949</v>
+        <v>0.01472782833025271</v>
       </c>
       <c r="BM47" t="n">
-        <v>0.003193608983013485</v>
+        <v>0.01350069023247153</v>
       </c>
       <c r="BN47" t="n">
-        <v>0.003539039958680608</v>
+        <v>0.01302592802396207</v>
       </c>
       <c r="BO47" t="n">
-        <v>0.003753887123300047</v>
+        <v>0.0146775611846095</v>
       </c>
       <c r="BP47" t="n">
-        <v>0.002451668640299867</v>
+        <v>0.008874415923940691</v>
       </c>
       <c r="BQ47" t="n">
-        <v>0.002610417851915382</v>
+        <v>0.01194646667940157</v>
       </c>
       <c r="BR47" t="n">
-        <v>0.00400231313172814</v>
+        <v>0.01286287445652514</v>
       </c>
       <c r="BS47" t="n">
-        <v>0.001711569457740092</v>
+        <v>0.009829489114300377</v>
       </c>
       <c r="BT47" t="n">
-        <v>0.002569236392537754</v>
+        <v>0.01075827833851096</v>
       </c>
       <c r="BU47" t="n">
-        <v>0.004118130010972408</v>
+        <v>0.01562125522327721</v>
       </c>
       <c r="BV47" t="n">
-        <v>0.004208806989374634</v>
+        <v>0.01806759058241901</v>
       </c>
       <c r="BW47" t="n">
-        <v>0.008584479559943941</v>
+        <v>0.01925762731329757</v>
       </c>
       <c r="BX47" t="n">
-        <v>0.01458217139604738</v>
+        <v>0.02414668734872828</v>
       </c>
       <c r="BY47" t="n">
-        <v>0.01108061309775305</v>
+        <v>0.02092799147461688</v>
       </c>
       <c r="BZ47" t="n">
-        <v>0.007469881641590298</v>
+        <v>0.01857708167249283</v>
       </c>
       <c r="CA47" t="n">
-        <v>0.004980495390319421</v>
+        <v>0.018976539630556</v>
       </c>
       <c r="CB47" t="n">
-        <v>0.004534745030896031</v>
+        <v>0.01778137663003562</v>
       </c>
       <c r="CC47" t="n">
-        <v>0.008404655234734515</v>
+        <v>0.0207963822590486</v>
       </c>
       <c r="CD47" t="n">
-        <v>0.004282787003137023</v>
+        <v>0.007305163818278102</v>
       </c>
       <c r="CE47" t="n">
-        <v>0.008255766097514798</v>
+        <v>0.02203255847821309</v>
       </c>
       <c r="CF47" t="n">
-        <v>0.008783744384921643</v>
+        <v>0.02120569173781251</v>
       </c>
       <c r="CG47" t="n">
-        <v>0.003346466240101702</v>
+        <v>0.006795533166905495</v>
       </c>
       <c r="CH47" t="n">
-        <v>0.007323994914188879</v>
+        <v>0.02026998988539709</v>
       </c>
       <c r="CI47" t="n">
-        <v>0.009802098715594841</v>
+        <v>0.02277824678262352</v>
       </c>
       <c r="CJ47" t="n">
-        <v>0.004498209463267437</v>
+        <v>0.02022273359120078</v>
       </c>
       <c r="CK47" t="n">
-        <v>0.005213139482067831</v>
+        <v>0.02212919323020027</v>
       </c>
       <c r="CL47" t="n">
-        <v>0.01081392339137605</v>
+        <v>0.02543488585724707</v>
       </c>
       <c r="CM47" t="n">
-        <v>0.009636128119449616</v>
+        <v>0.02152453116998655</v>
       </c>
       <c r="CN47" t="n">
-        <v>1.010630267719667</v>
+        <v>1.024613959830853</v>
       </c>
       <c r="CO47" t="n">
-        <v>0</v>
+        <v>0.02428568712645513</v>
       </c>
       <c r="CP47" t="n">
-        <v>0</v>
+        <v>0.02370223886539314</v>
       </c>
     </row>
     <row r="48">
@@ -13862,142 +13862,142 @@
         </is>
       </c>
       <c r="AW48" t="n">
-        <v>-0</v>
+        <v>0.001336072042239337</v>
       </c>
       <c r="AX48" t="n">
-        <v>5.417753095991103e-17</v>
+        <v>0.001246570757681518</v>
       </c>
       <c r="AY48" t="n">
-        <v>-0</v>
+        <v>0.00162862852365349</v>
       </c>
       <c r="AZ48" t="n">
-        <v>5.417753095991103e-17</v>
+        <v>0.001515542364081449</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.083550619198221e-16</v>
+        <v>0.002465471257926739</v>
       </c>
       <c r="BB48" t="n">
-        <v>-0</v>
+        <v>0.001787328527368981</v>
       </c>
       <c r="BC48" t="n">
-        <v>5.417753095991103e-17</v>
+        <v>0.002168327725072154</v>
       </c>
       <c r="BD48" t="n">
-        <v>-0</v>
+        <v>0.002088558875508975</v>
       </c>
       <c r="BE48" t="n">
-        <v>5.417753095991103e-17</v>
+        <v>0.002030999280730975</v>
       </c>
       <c r="BF48" t="n">
-        <v>-0</v>
+        <v>0.0009943700825779968</v>
       </c>
       <c r="BG48" t="n">
-        <v>-0</v>
+        <v>0.001396363924913723</v>
       </c>
       <c r="BH48" t="n">
-        <v>-0</v>
+        <v>0.001886737697124092</v>
       </c>
       <c r="BI48" t="n">
-        <v>-0</v>
+        <v>0.001935289212614584</v>
       </c>
       <c r="BJ48" t="n">
-        <v>-0</v>
+        <v>0.00203434673715389</v>
       </c>
       <c r="BK48" t="n">
-        <v>-0</v>
+        <v>0.001257774817622287</v>
       </c>
       <c r="BL48" t="n">
-        <v>-0</v>
+        <v>0.002222416659438393</v>
       </c>
       <c r="BM48" t="n">
-        <v>5.417753095991103e-17</v>
+        <v>0.001998750686577309</v>
       </c>
       <c r="BN48" t="n">
-        <v>-0</v>
+        <v>0.001839698705679653</v>
       </c>
       <c r="BO48" t="n">
-        <v>5.417753095991103e-17</v>
+        <v>0.002118320453827493</v>
       </c>
       <c r="BP48" t="n">
-        <v>-0</v>
+        <v>0.001245500082146364</v>
       </c>
       <c r="BQ48" t="n">
-        <v>5.417753095991103e-17</v>
+        <v>0.001810447938871021</v>
       </c>
       <c r="BR48" t="n">
-        <v>-0</v>
+        <v>0.001718241333581098</v>
       </c>
       <c r="BS48" t="n">
-        <v>-0</v>
+        <v>0.001574228153870592</v>
       </c>
       <c r="BT48" t="n">
-        <v>-0</v>
+        <v>0.001588020198519763</v>
       </c>
       <c r="BU48" t="n">
-        <v>-0</v>
+        <v>0.002230687704832768</v>
       </c>
       <c r="BV48" t="n">
-        <v>1.083550619198221e-16</v>
+        <v>0.002687497318717617</v>
       </c>
       <c r="BW48" t="n">
-        <v>-0</v>
+        <v>0.002069738355955773</v>
       </c>
       <c r="BX48" t="n">
-        <v>5.417753095991103e-17</v>
+        <v>0.001854752316831281</v>
       </c>
       <c r="BY48" t="n">
-        <v>5.417753095991103e-17</v>
+        <v>0.00190960503903839</v>
       </c>
       <c r="BZ48" t="n">
-        <v>-0</v>
+        <v>0.002153909836393783</v>
       </c>
       <c r="CA48" t="n">
-        <v>-0</v>
+        <v>0.002714114923272709</v>
       </c>
       <c r="CB48" t="n">
-        <v>-0</v>
+        <v>0.002568788715525869</v>
       </c>
       <c r="CC48" t="n">
-        <v>-0</v>
+        <v>0.002403005496733373</v>
       </c>
       <c r="CD48" t="n">
-        <v>-0</v>
+        <v>0.0005860997491094791</v>
       </c>
       <c r="CE48" t="n">
-        <v>-0</v>
+        <v>0.002671597570961283</v>
       </c>
       <c r="CF48" t="n">
-        <v>-0</v>
+        <v>0.002408865827221759</v>
       </c>
       <c r="CG48" t="n">
-        <v>-0</v>
+        <v>0.0006688435572740327</v>
       </c>
       <c r="CH48" t="n">
-        <v>-0</v>
+        <v>0.002510489217157251</v>
       </c>
       <c r="CI48" t="n">
-        <v>1.083550619198221e-16</v>
+        <v>0.002516336509859782</v>
       </c>
       <c r="CJ48" t="n">
-        <v>-0</v>
+        <v>0.003049301993079714</v>
       </c>
       <c r="CK48" t="n">
-        <v>-0</v>
+        <v>0.003280363589356121</v>
       </c>
       <c r="CL48" t="n">
-        <v>-0</v>
+        <v>0.002835299155967794</v>
       </c>
       <c r="CM48" t="n">
-        <v>-0</v>
+        <v>0.002305400838944307</v>
       </c>
       <c r="CN48" t="n">
-        <v>-0</v>
+        <v>0.002711719596620782</v>
       </c>
       <c r="CO48" t="n">
-        <v>1</v>
+        <v>1.004709483959928</v>
       </c>
       <c r="CP48" t="n">
-        <v>-0</v>
+        <v>0.004596341588761041</v>
       </c>
     </row>
     <row r="49">
@@ -14007,142 +14007,142 @@
         </is>
       </c>
       <c r="AW49" t="n">
-        <v>0.2906816250355083</v>
+        <v>0.4249092184338787</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.2712093376022341</v>
+        <v>0.3964452436870001</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.3543314812884747</v>
+        <v>0.5179505679535568</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.3297279662127897</v>
+        <v>0.4819859267064244</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.536398614053255</v>
+        <v>0.7840905521239693</v>
       </c>
       <c r="BB49" t="n">
-        <v>0.3888589420201885</v>
+        <v>0.5684217195174948</v>
       </c>
       <c r="BC49" t="n">
-        <v>0.471750779005227</v>
+        <v>0.6895903887223636</v>
       </c>
       <c r="BD49" t="n">
-        <v>0.4543959223169873</v>
+        <v>0.6642216073605175</v>
       </c>
       <c r="BE49" t="n">
-        <v>0.4418730073711536</v>
+        <v>0.645916005823103</v>
       </c>
       <c r="BF49" t="n">
-        <v>0.2163394655021805</v>
+        <v>0.3162381976903614</v>
       </c>
       <c r="BG49" t="n">
-        <v>0.3037989883798285</v>
+        <v>0.4440837658648266</v>
       </c>
       <c r="BH49" t="n">
-        <v>0.4104868319050853</v>
+        <v>0.6000366858444612</v>
       </c>
       <c r="BI49" t="n">
-        <v>0.421049910073425</v>
+        <v>0.6154774598810621</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0.4426012945008995</v>
+        <v>0.6469805929467576</v>
       </c>
       <c r="BK49" t="n">
-        <v>0.2736469414496542</v>
+        <v>0.4000084560005826</v>
       </c>
       <c r="BL49" t="n">
-        <v>0.4835186020274574</v>
+        <v>0.7067922207350796</v>
       </c>
       <c r="BM49" t="n">
-        <v>0.434856863437786</v>
+        <v>0.6356600282229274</v>
       </c>
       <c r="BN49" t="n">
-        <v>0.4002528250245995</v>
+        <v>0.5850769378228828</v>
       </c>
       <c r="BO49" t="n">
-        <v>0.4608709803046813</v>
+        <v>0.6736866426152537</v>
       </c>
       <c r="BP49" t="n">
-        <v>0.2709763967917169</v>
+        <v>0.3961047381675124</v>
       </c>
       <c r="BQ49" t="n">
-        <v>0.3938889014032108</v>
+        <v>0.5757743552746847</v>
       </c>
       <c r="BR49" t="n">
-        <v>0.3738280326646279</v>
+        <v>0.5464500109657706</v>
       </c>
       <c r="BS49" t="n">
-        <v>0.342495901027012</v>
+        <v>0.5006496905486115</v>
       </c>
       <c r="BT49" t="n">
-        <v>0.3454965580458206</v>
+        <v>0.5050359562043589</v>
       </c>
       <c r="BU49" t="n">
-        <v>0.485318086516297</v>
+        <v>0.7094226503249903</v>
       </c>
       <c r="BV49" t="n">
-        <v>0.5847035662643303</v>
+        <v>0.8547012055768204</v>
       </c>
       <c r="BW49" t="n">
-        <v>0.4503012485009227</v>
+        <v>0.6582361425045496</v>
       </c>
       <c r="BX49" t="n">
-        <v>0.4035279539202405</v>
+        <v>0.5898644177991181</v>
       </c>
       <c r="BY49" t="n">
-        <v>0.4154619499359475</v>
+        <v>0.607309156245202</v>
       </c>
       <c r="BZ49" t="n">
-        <v>0.4686139606465528</v>
+        <v>0.6850050867205928</v>
       </c>
       <c r="CA49" t="n">
-        <v>0.5904946076917545</v>
+        <v>0.8631663670280972</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.5588768079829185</v>
+        <v>0.8169484660471208</v>
       </c>
       <c r="CC49" t="n">
-        <v>0.5228082922751587</v>
+        <v>0.7642246489926985</v>
       </c>
       <c r="CD49" t="n">
-        <v>0.1275144020067215</v>
+        <v>0.1863965253707414</v>
       </c>
       <c r="CE49" t="n">
-        <v>0.5812443482211856</v>
+        <v>0.8496446298991339</v>
       </c>
       <c r="CF49" t="n">
-        <v>0.5240832911792034</v>
+        <v>0.7660884021203878</v>
       </c>
       <c r="CG49" t="n">
-        <v>0.1455165035839573</v>
+        <v>0.2127114288683951</v>
       </c>
       <c r="CH49" t="n">
-        <v>0.5461929164046287</v>
+        <v>0.7984075539527536</v>
       </c>
       <c r="CI49" t="n">
-        <v>0.5474650787514733</v>
+        <v>0.8002671606907189</v>
       </c>
       <c r="CJ49" t="n">
-        <v>0.6634193595480214</v>
+        <v>0.9697654659974447</v>
       </c>
       <c r="CK49" t="n">
-        <v>0.7136901220260259</v>
+        <v>1.043249678809296</v>
       </c>
       <c r="CL49" t="n">
-        <v>0.6168599746591283</v>
+        <v>0.9017064277232331</v>
       </c>
       <c r="CM49" t="n">
-        <v>0.5015729998356739</v>
+        <v>0.7331835692114289</v>
       </c>
       <c r="CN49" t="n">
-        <v>0.5899734700422411</v>
+        <v>0.8624045844719271</v>
       </c>
       <c r="CO49" t="n">
-        <v>1.024615744714052</v>
+        <v>1.497750933614437</v>
       </c>
       <c r="CP49" t="n">
-        <v>1</v>
+        <v>1.461768415468208</v>
       </c>
     </row>
   </sheetData>
